--- a/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
+++ b/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="492">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 1: Core Benchmarks</t>
   </si>
@@ -4031,7 +4031,9 @@
       <c r="OU4" s="5"/>
       <c r="OV4" s="5"/>
       <c r="OW4" s="5"/>
-      <c r="OX4" s="5"/>
+      <c r="OX4" s="5" t="n">
+        <v>674.99</v>
+      </c>
       <c r="OY4" s="5"/>
       <c r="OZ4" s="5"/>
       <c r="PA4" s="5"/>
@@ -4474,7 +4476,9 @@
       <c r="OU5" s="5"/>
       <c r="OV5" s="5"/>
       <c r="OW5" s="5"/>
-      <c r="OX5" s="5"/>
+      <c r="OX5" s="5" t="n">
+        <v>231.39</v>
+      </c>
       <c r="OY5" s="5"/>
       <c r="OZ5" s="5"/>
       <c r="PA5" s="5"/>
@@ -4917,7 +4921,9 @@
       <c r="OU6" s="5"/>
       <c r="OV6" s="5"/>
       <c r="OW6" s="5"/>
-      <c r="OX6" s="5"/>
+      <c r="OX6" s="5" t="n">
+        <v>38.5</v>
+      </c>
       <c r="OY6" s="5"/>
       <c r="OZ6" s="5"/>
       <c r="PA6" s="5"/>
@@ -5360,7 +5366,9 @@
       <c r="OU7" s="5"/>
       <c r="OV7" s="5"/>
       <c r="OW7" s="5"/>
-      <c r="OX7" s="5"/>
+      <c r="OX7" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY7" s="5"/>
       <c r="OZ7" s="5"/>
       <c r="PA7" s="5"/>
@@ -5803,7 +5811,9 @@
       <c r="OU8" s="5"/>
       <c r="OV8" s="5"/>
       <c r="OW8" s="5"/>
-      <c r="OX8" s="5"/>
+      <c r="OX8" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY8" s="5"/>
       <c r="OZ8" s="5"/>
       <c r="PA8" s="5"/>
@@ -6246,7 +6256,9 @@
       <c r="OU9" s="5"/>
       <c r="OV9" s="5"/>
       <c r="OW9" s="5"/>
-      <c r="OX9" s="5"/>
+      <c r="OX9" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY9" s="5"/>
       <c r="OZ9" s="5"/>
       <c r="PA9" s="5"/>
@@ -6689,7 +6701,9 @@
       <c r="OU10" s="5"/>
       <c r="OV10" s="5"/>
       <c r="OW10" s="5"/>
-      <c r="OX10" s="5"/>
+      <c r="OX10" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY10" s="5"/>
       <c r="OZ10" s="5"/>
       <c r="PA10" s="5"/>
@@ -7132,7 +7146,9 @@
       <c r="OU11" s="5"/>
       <c r="OV11" s="5"/>
       <c r="OW11" s="5"/>
-      <c r="OX11" s="5"/>
+      <c r="OX11" s="5" t="n">
+        <v>166.28</v>
+      </c>
       <c r="OY11" s="5"/>
       <c r="OZ11" s="5"/>
       <c r="PA11" s="5"/>
@@ -7575,7 +7591,9 @@
       <c r="OU12" s="5"/>
       <c r="OV12" s="5"/>
       <c r="OW12" s="5"/>
-      <c r="OX12" s="5"/>
+      <c r="OX12" s="5" t="n">
+        <v>145.14</v>
+      </c>
       <c r="OY12" s="5"/>
       <c r="OZ12" s="5"/>
       <c r="PA12" s="5"/>
@@ -8018,7 +8036,9 @@
       <c r="OU13" s="5"/>
       <c r="OV13" s="5"/>
       <c r="OW13" s="5"/>
-      <c r="OX13" s="5"/>
+      <c r="OX13" s="5" t="n">
+        <v>47.79</v>
+      </c>
       <c r="OY13" s="5"/>
       <c r="OZ13" s="5"/>
       <c r="PA13" s="5"/>
@@ -8461,7 +8481,9 @@
       <c r="OU14" s="5"/>
       <c r="OV14" s="5"/>
       <c r="OW14" s="5"/>
-      <c r="OX14" s="5"/>
+      <c r="OX14" s="5" t="n">
+        <v>35.16</v>
+      </c>
       <c r="OY14" s="5"/>
       <c r="OZ14" s="5"/>
       <c r="PA14" s="5"/>
@@ -8904,7 +8926,9 @@
       <c r="OU15" s="5"/>
       <c r="OV15" s="5"/>
       <c r="OW15" s="5"/>
-      <c r="OX15" s="5"/>
+      <c r="OX15" s="5" t="n">
+        <v>5.84</v>
+      </c>
       <c r="OY15" s="5"/>
       <c r="OZ15" s="5"/>
       <c r="PA15" s="5"/>
@@ -9347,7 +9371,9 @@
       <c r="OU16" s="5"/>
       <c r="OV16" s="5"/>
       <c r="OW16" s="5"/>
-      <c r="OX16" s="5"/>
+      <c r="OX16" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY16" s="5"/>
       <c r="OZ16" s="5"/>
       <c r="PA16" s="5"/>
@@ -9790,7 +9816,9 @@
       <c r="OU17" s="5"/>
       <c r="OV17" s="5"/>
       <c r="OW17" s="5"/>
-      <c r="OX17" s="5"/>
+      <c r="OX17" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY17" s="5"/>
       <c r="OZ17" s="5"/>
       <c r="PA17" s="5"/>
@@ -10233,7 +10261,9 @@
       <c r="OU18" s="5"/>
       <c r="OV18" s="5"/>
       <c r="OW18" s="5"/>
-      <c r="OX18" s="5"/>
+      <c r="OX18" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY18" s="5"/>
       <c r="OZ18" s="5"/>
       <c r="PA18" s="5"/>
@@ -10676,7 +10706,9 @@
       <c r="OU19" s="5"/>
       <c r="OV19" s="5"/>
       <c r="OW19" s="5"/>
-      <c r="OX19" s="5"/>
+      <c r="OX19" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY19" s="5"/>
       <c r="OZ19" s="5"/>
       <c r="PA19" s="5"/>
@@ -11119,7 +11151,9 @@
       <c r="OU20" s="5"/>
       <c r="OV20" s="5"/>
       <c r="OW20" s="5"/>
-      <c r="OX20" s="5"/>
+      <c r="OX20" s="5" t="n">
+        <v>261.28</v>
+      </c>
       <c r="OY20" s="5"/>
       <c r="OZ20" s="5"/>
       <c r="PA20" s="5"/>
@@ -11562,7 +11596,9 @@
       <c r="OU21" s="5"/>
       <c r="OV21" s="5"/>
       <c r="OW21" s="5"/>
-      <c r="OX21" s="5"/>
+      <c r="OX21" s="5" t="n">
+        <v>162.79</v>
+      </c>
       <c r="OY21" s="5"/>
       <c r="OZ21" s="5"/>
       <c r="PA21" s="5"/>
@@ -12005,7 +12041,9 @@
       <c r="OU22" s="5"/>
       <c r="OV22" s="5"/>
       <c r="OW22" s="5"/>
-      <c r="OX22" s="5"/>
+      <c r="OX22" s="5" t="n">
+        <v>25.13</v>
+      </c>
       <c r="OY22" s="5"/>
       <c r="OZ22" s="5"/>
       <c r="PA22" s="5"/>
@@ -12448,7 +12486,9 @@
       <c r="OU23" s="5"/>
       <c r="OV23" s="5"/>
       <c r="OW23" s="5"/>
-      <c r="OX23" s="5"/>
+      <c r="OX23" s="5" t="n">
+        <v>45.7</v>
+      </c>
       <c r="OY23" s="5"/>
       <c r="OZ23" s="5"/>
       <c r="PA23" s="5"/>
@@ -12891,7 +12931,9 @@
       <c r="OU24" s="5"/>
       <c r="OV24" s="5"/>
       <c r="OW24" s="5"/>
-      <c r="OX24" s="5"/>
+      <c r="OX24" s="5" t="n">
+        <v>2672.97</v>
+      </c>
       <c r="OY24" s="5"/>
       <c r="OZ24" s="5"/>
       <c r="PA24" s="5"/>
@@ -13334,7 +13376,9 @@
       <c r="OU25" s="5"/>
       <c r="OV25" s="5"/>
       <c r="OW25" s="5"/>
-      <c r="OX25" s="5"/>
+      <c r="OX25" s="5" t="n">
+        <v>834.68</v>
+      </c>
       <c r="OY25" s="5"/>
       <c r="OZ25" s="5"/>
       <c r="PA25" s="5"/>
@@ -13777,7 +13821,9 @@
       <c r="OU26" s="5"/>
       <c r="OV26" s="5"/>
       <c r="OW26" s="5"/>
-      <c r="OX26" s="5"/>
+      <c r="OX26" s="5" t="n">
+        <v>621.48</v>
+      </c>
       <c r="OY26" s="5"/>
       <c r="OZ26" s="5"/>
       <c r="PA26" s="5"/>
@@ -14220,7 +14266,9 @@
       <c r="OU27" s="5"/>
       <c r="OV27" s="5"/>
       <c r="OW27" s="5"/>
-      <c r="OX27" s="5"/>
+      <c r="OX27" s="5" t="n">
+        <v>3.42</v>
+      </c>
       <c r="OY27" s="5"/>
       <c r="OZ27" s="5"/>
       <c r="PA27" s="5"/>
@@ -14663,7 +14711,9 @@
       <c r="OU28" s="5"/>
       <c r="OV28" s="5"/>
       <c r="OW28" s="5"/>
-      <c r="OX28" s="5"/>
+      <c r="OX28" s="5" t="n">
+        <v>4.79</v>
+      </c>
       <c r="OY28" s="5"/>
       <c r="OZ28" s="5"/>
       <c r="PA28" s="5"/>
@@ -15106,7 +15156,9 @@
       <c r="OU29" s="5"/>
       <c r="OV29" s="5"/>
       <c r="OW29" s="5"/>
-      <c r="OX29" s="5"/>
+      <c r="OX29" s="5" t="n">
+        <v>7.98</v>
+      </c>
       <c r="OY29" s="5"/>
       <c r="OZ29" s="5"/>
       <c r="PA29" s="5"/>
@@ -15549,7 +15601,9 @@
       <c r="OU30" s="5"/>
       <c r="OV30" s="5"/>
       <c r="OW30" s="5"/>
-      <c r="OX30" s="5"/>
+      <c r="OX30" s="5" t="n">
+        <v>1.6</v>
+      </c>
       <c r="OY30" s="5"/>
       <c r="OZ30" s="5"/>
       <c r="PA30" s="5"/>
@@ -15992,7 +16046,9 @@
       <c r="OU31" s="5"/>
       <c r="OV31" s="5"/>
       <c r="OW31" s="5"/>
-      <c r="OX31" s="5"/>
+      <c r="OX31" s="5" t="n">
+        <v>0.1</v>
+      </c>
       <c r="OY31" s="5"/>
       <c r="OZ31" s="5"/>
       <c r="PA31" s="5"/>
@@ -16435,7 +16491,9 @@
       <c r="OU32" s="5"/>
       <c r="OV32" s="5"/>
       <c r="OW32" s="5"/>
-      <c r="OX32" s="5"/>
+      <c r="OX32" s="5" t="n">
+        <v>695.65</v>
+      </c>
       <c r="OY32" s="5"/>
       <c r="OZ32" s="5"/>
       <c r="PA32" s="5"/>
@@ -16878,7 +16936,9 @@
       <c r="OU33" s="5"/>
       <c r="OV33" s="5"/>
       <c r="OW33" s="5"/>
-      <c r="OX33" s="5"/>
+      <c r="OX33" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY33" s="5"/>
       <c r="OZ33" s="5"/>
       <c r="PA33" s="5"/>
@@ -17321,7 +17381,9 @@
       <c r="OU34" s="5"/>
       <c r="OV34" s="5"/>
       <c r="OW34" s="5"/>
-      <c r="OX34" s="5"/>
+      <c r="OX34" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY34" s="5"/>
       <c r="OZ34" s="5"/>
       <c r="PA34" s="5"/>
@@ -17764,7 +17826,9 @@
       <c r="OU35" s="5"/>
       <c r="OV35" s="5"/>
       <c r="OW35" s="5"/>
-      <c r="OX35" s="5"/>
+      <c r="OX35" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY35" s="5"/>
       <c r="OZ35" s="5"/>
       <c r="PA35" s="5"/>
@@ -18207,7 +18271,9 @@
       <c r="OU36" s="5"/>
       <c r="OV36" s="5"/>
       <c r="OW36" s="5"/>
-      <c r="OX36" s="5"/>
+      <c r="OX36" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY36" s="5"/>
       <c r="OZ36" s="5"/>
       <c r="PA36" s="5"/>
@@ -18650,7 +18716,9 @@
       <c r="OU37" s="5"/>
       <c r="OV37" s="5"/>
       <c r="OW37" s="5"/>
-      <c r="OX37" s="5"/>
+      <c r="OX37" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY37" s="5"/>
       <c r="OZ37" s="5"/>
       <c r="PA37" s="5"/>
@@ -19093,7 +19161,9 @@
       <c r="OU38" s="5"/>
       <c r="OV38" s="5"/>
       <c r="OW38" s="5"/>
-      <c r="OX38" s="5"/>
+      <c r="OX38" s="5" t="n">
+        <v>235.85</v>
+      </c>
       <c r="OY38" s="5"/>
       <c r="OZ38" s="5"/>
       <c r="PA38" s="5"/>
@@ -19536,7 +19606,9 @@
       <c r="OU39" s="5"/>
       <c r="OV39" s="5"/>
       <c r="OW39" s="5"/>
-      <c r="OX39" s="5"/>
+      <c r="OX39" s="5" t="n">
+        <v>2969.01</v>
+      </c>
       <c r="OY39" s="5"/>
       <c r="OZ39" s="5"/>
       <c r="PA39" s="5"/>
@@ -19979,7 +20051,9 @@
       <c r="OU40" s="5"/>
       <c r="OV40" s="5"/>
       <c r="OW40" s="5"/>
-      <c r="OX40" s="5"/>
+      <c r="OX40" s="5" t="n">
+        <v>12.59</v>
+      </c>
       <c r="OY40" s="5"/>
       <c r="OZ40" s="5"/>
       <c r="PA40" s="5"/>
@@ -20422,7 +20496,9 @@
       <c r="OU41" s="5"/>
       <c r="OV41" s="5"/>
       <c r="OW41" s="5"/>
-      <c r="OX41" s="5"/>
+      <c r="OX41" s="5" t="n">
+        <v>30.94</v>
+      </c>
       <c r="OY41" s="5"/>
       <c r="OZ41" s="5"/>
       <c r="PA41" s="5"/>
@@ -20865,7 +20941,9 @@
       <c r="OU42" s="5"/>
       <c r="OV42" s="5"/>
       <c r="OW42" s="5"/>
-      <c r="OX42" s="5"/>
+      <c r="OX42" s="5" t="n">
+        <v>117.15</v>
+      </c>
       <c r="OY42" s="5"/>
       <c r="OZ42" s="5"/>
       <c r="PA42" s="5"/>
@@ -21308,7 +21386,9 @@
       <c r="OU43" s="5"/>
       <c r="OV43" s="5"/>
       <c r="OW43" s="5"/>
-      <c r="OX43" s="5"/>
+      <c r="OX43" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY43" s="5"/>
       <c r="OZ43" s="5"/>
       <c r="PA43" s="5"/>
@@ -21751,7 +21831,9 @@
       <c r="OU44" s="5"/>
       <c r="OV44" s="5"/>
       <c r="OW44" s="5"/>
-      <c r="OX44" s="5"/>
+      <c r="OX44" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY44" s="5"/>
       <c r="OZ44" s="5"/>
       <c r="PA44" s="5"/>
@@ -22194,7 +22276,9 @@
       <c r="OU45" s="5"/>
       <c r="OV45" s="5"/>
       <c r="OW45" s="5"/>
-      <c r="OX45" s="5"/>
+      <c r="OX45" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY45" s="5"/>
       <c r="OZ45" s="5"/>
       <c r="PA45" s="5"/>
@@ -22637,7 +22721,9 @@
       <c r="OU46" s="5"/>
       <c r="OV46" s="5"/>
       <c r="OW46" s="5"/>
-      <c r="OX46" s="5"/>
+      <c r="OX46" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY46" s="5"/>
       <c r="OZ46" s="5"/>
       <c r="PA46" s="5"/>
@@ -23080,7 +23166,9 @@
       <c r="OU47" s="5"/>
       <c r="OV47" s="5"/>
       <c r="OW47" s="5"/>
-      <c r="OX47" s="5"/>
+      <c r="OX47" s="5" t="n">
+        <v>357.64</v>
+      </c>
       <c r="OY47" s="5"/>
       <c r="OZ47" s="5"/>
       <c r="PA47" s="5"/>
@@ -23523,7 +23611,9 @@
       <c r="OU48" s="5"/>
       <c r="OV48" s="5"/>
       <c r="OW48" s="5"/>
-      <c r="OX48" s="5"/>
+      <c r="OX48" s="5" t="n">
+        <v>376.35</v>
+      </c>
       <c r="OY48" s="5"/>
       <c r="OZ48" s="5"/>
       <c r="PA48" s="5"/>
@@ -23966,7 +24056,9 @@
       <c r="OU49" s="5"/>
       <c r="OV49" s="5"/>
       <c r="OW49" s="5"/>
-      <c r="OX49" s="5"/>
+      <c r="OX49" s="5" t="n">
+        <v>2.657</v>
+      </c>
       <c r="OY49" s="5"/>
       <c r="OZ49" s="5"/>
       <c r="PA49" s="5"/>
@@ -24409,7 +24501,9 @@
       <c r="OU50" s="5"/>
       <c r="OV50" s="5"/>
       <c r="OW50" s="5"/>
-      <c r="OX50" s="5"/>
+      <c r="OX50" s="5" t="n">
+        <v>10.01</v>
+      </c>
       <c r="OY50" s="5"/>
       <c r="OZ50" s="5"/>
       <c r="PA50" s="5"/>
@@ -24852,7 +24946,9 @@
       <c r="OU51" s="5"/>
       <c r="OV51" s="5"/>
       <c r="OW51" s="5"/>
-      <c r="OX51" s="5"/>
+      <c r="OX51" s="5" t="n">
+        <v>9.73</v>
+      </c>
       <c r="OY51" s="5"/>
       <c r="OZ51" s="5"/>
       <c r="PA51" s="5"/>
@@ -25295,7 +25391,9 @@
       <c r="OU52" s="5"/>
       <c r="OV52" s="5"/>
       <c r="OW52" s="5"/>
-      <c r="OX52" s="5"/>
+      <c r="OX52" s="5" t="n">
+        <v>0.28</v>
+      </c>
       <c r="OY52" s="5"/>
       <c r="OZ52" s="5"/>
       <c r="PA52" s="5"/>
@@ -25738,7 +25836,9 @@
       <c r="OU53" s="5"/>
       <c r="OV53" s="5"/>
       <c r="OW53" s="5"/>
-      <c r="OX53" s="5"/>
+      <c r="OX53" s="5" t="n">
+        <v>72.73</v>
+      </c>
       <c r="OY53" s="5"/>
       <c r="OZ53" s="5"/>
       <c r="PA53" s="5"/>
@@ -26181,7 +26281,9 @@
       <c r="OU54" s="5"/>
       <c r="OV54" s="5"/>
       <c r="OW54" s="5"/>
-      <c r="OX54" s="5"/>
+      <c r="OX54" s="5" t="n">
+        <v>119.52</v>
+      </c>
       <c r="OY54" s="5"/>
       <c r="OZ54" s="5"/>
       <c r="PA54" s="5"/>
@@ -26624,7 +26726,9 @@
       <c r="OU55" s="5"/>
       <c r="OV55" s="5"/>
       <c r="OW55" s="5"/>
-      <c r="OX55" s="5"/>
+      <c r="OX55" s="5" t="n">
+        <v>175.93</v>
+      </c>
       <c r="OY55" s="5"/>
       <c r="OZ55" s="5"/>
       <c r="PA55" s="5"/>
@@ -27067,7 +27171,9 @@
       <c r="OU56" s="5"/>
       <c r="OV56" s="5"/>
       <c r="OW56" s="5"/>
-      <c r="OX56" s="5"/>
+      <c r="OX56" s="5" t="n">
+        <v>224.77</v>
+      </c>
       <c r="OY56" s="5"/>
       <c r="OZ56" s="5"/>
       <c r="PA56" s="5"/>
@@ -27510,7 +27616,9 @@
       <c r="OU57" s="5"/>
       <c r="OV57" s="5"/>
       <c r="OW57" s="5"/>
-      <c r="OX57" s="5"/>
+      <c r="OX57" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="OY57" s="5"/>
       <c r="OZ57" s="5"/>
       <c r="PA57" s="5"/>
@@ -27953,7 +28061,9 @@
       <c r="OU58" s="5"/>
       <c r="OV58" s="5"/>
       <c r="OW58" s="5"/>
-      <c r="OX58" s="5"/>
+      <c r="OX58" s="5" t="n">
+        <v>248.5</v>
+      </c>
       <c r="OY58" s="5"/>
       <c r="OZ58" s="5"/>
       <c r="PA58" s="5"/>

--- a/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
+++ b/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="496">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 1: Core Benchmarks</t>
   </si>
@@ -265,6 +265,9 @@
     <t xml:space="preserve">ESP32-S3-DevKitM-1</t>
   </si>
   <si>
+    <t xml:space="preserve">ESP32-C3-Dev-Module</t>
+  </si>
+  <si>
     <t xml:space="preserve">ESP32-C3-DevKitM-1</t>
   </si>
   <si>
@@ -1405,13 +1408,13 @@
     <t xml:space="preserve">Read (ops/ms)</t>
   </si>
   <si>
-    <t xml:space="preserve">Flash Commit Min (μs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flash Commit Median (μs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flash Commit Max (μs)</t>
+    <t xml:space="preserve">Flash Commit Min (ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flash Commit Median (ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flash Commit Max (ms)</t>
   </si>
   <si>
     <t xml:space="preserve">Memory PSRAM</t>
@@ -1492,7 +1495,16 @@
     <t xml:space="preserve">8 MHz (KB/s)</t>
   </si>
   <si>
+    <t xml:space="preserve">10 MHz (KB/s)</t>
+  </si>
+  <si>
     <t xml:space="preserve">16 MHz (KB/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 MHz (KB/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 MHz (KB/s)</t>
   </si>
   <si>
     <t xml:space="preserve">Bulk throughput (KB/s)</t>
@@ -1889,12 +1901,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:PI58"/>
+  <dimension ref="A1:PJ61"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.2"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="425" min="3" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="426" min="3" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2325,6 +2337,7 @@
       <c r="PG1" s="2"/>
       <c r="PH1" s="2"/>
       <c r="PI1" s="2"/>
+      <c r="PJ1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
@@ -3602,13 +3615,16 @@
       <c r="PI3" s="3" t="s">
         <v>425</v>
       </c>
+      <c r="PJ3" s="3" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>399.74</v>
@@ -3698,7 +3714,9 @@
       <c r="BZ4" s="5"/>
       <c r="CA4" s="5"/>
       <c r="CB4" s="5"/>
-      <c r="CC4" s="5"/>
+      <c r="CC4" s="5" t="n">
+        <v>17985.61</v>
+      </c>
       <c r="CD4" s="5"/>
       <c r="CE4" s="5"/>
       <c r="CF4" s="5"/>
@@ -4031,29 +4049,30 @@
       <c r="OU4" s="5"/>
       <c r="OV4" s="5"/>
       <c r="OW4" s="5"/>
-      <c r="OX4" s="5" t="n">
+      <c r="OX4" s="5"/>
+      <c r="OY4" s="5" t="n">
         <v>674.99</v>
       </c>
-      <c r="OY4" s="5"/>
       <c r="OZ4" s="5"/>
       <c r="PA4" s="5"/>
       <c r="PB4" s="5"/>
       <c r="PC4" s="5"/>
       <c r="PD4" s="5"/>
       <c r="PE4" s="5"/>
-      <c r="PF4" s="5" t="n">
+      <c r="PF4" s="5"/>
+      <c r="PG4" s="5" t="n">
         <v>399.74</v>
       </c>
-      <c r="PG4" s="5"/>
       <c r="PH4" s="5"/>
       <c r="PI4" s="5"/>
+      <c r="PJ4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>137.9</v>
@@ -4143,7 +4162,9 @@
       <c r="BZ5" s="5"/>
       <c r="CA5" s="5"/>
       <c r="CB5" s="5"/>
-      <c r="CC5" s="5"/>
+      <c r="CC5" s="5" t="n">
+        <v>9398.12</v>
+      </c>
       <c r="CD5" s="5"/>
       <c r="CE5" s="5"/>
       <c r="CF5" s="5"/>
@@ -4476,29 +4497,30 @@
       <c r="OU5" s="5"/>
       <c r="OV5" s="5"/>
       <c r="OW5" s="5"/>
-      <c r="OX5" s="5" t="n">
+      <c r="OX5" s="5"/>
+      <c r="OY5" s="5" t="n">
         <v>231.39</v>
       </c>
-      <c r="OY5" s="5"/>
       <c r="OZ5" s="5"/>
       <c r="PA5" s="5"/>
       <c r="PB5" s="5"/>
       <c r="PC5" s="5"/>
       <c r="PD5" s="5"/>
       <c r="PE5" s="5"/>
-      <c r="PF5" s="5" t="n">
+      <c r="PF5" s="5"/>
+      <c r="PG5" s="5" t="n">
         <v>137.9</v>
       </c>
-      <c r="PG5" s="5"/>
       <c r="PH5" s="5"/>
       <c r="PI5" s="5"/>
+      <c r="PJ5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>25.24</v>
@@ -4588,7 +4610,9 @@
       <c r="BZ6" s="5"/>
       <c r="CA6" s="5"/>
       <c r="CB6" s="5"/>
-      <c r="CC6" s="5"/>
+      <c r="CC6" s="5" t="n">
+        <v>3451.03</v>
+      </c>
       <c r="CD6" s="5"/>
       <c r="CE6" s="5"/>
       <c r="CF6" s="5"/>
@@ -4921,39 +4945,40 @@
       <c r="OU6" s="5"/>
       <c r="OV6" s="5"/>
       <c r="OW6" s="5"/>
-      <c r="OX6" s="5" t="n">
+      <c r="OX6" s="5"/>
+      <c r="OY6" s="5" t="n">
         <v>38.5</v>
       </c>
-      <c r="OY6" s="5"/>
       <c r="OZ6" s="5"/>
       <c r="PA6" s="5"/>
       <c r="PB6" s="5"/>
       <c r="PC6" s="5"/>
       <c r="PD6" s="5"/>
       <c r="PE6" s="5"/>
-      <c r="PF6" s="5" t="n">
+      <c r="PF6" s="5"/>
+      <c r="PG6" s="5" t="n">
         <v>25.24</v>
       </c>
-      <c r="PG6" s="5"/>
       <c r="PH6" s="5"/>
       <c r="PI6" s="5"/>
+      <c r="PJ6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -4988,7 +5013,7 @@
       <c r="AI7" s="5"/>
       <c r="AJ7" s="5"/>
       <c r="AK7" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
@@ -5033,7 +5058,9 @@
       <c r="BZ7" s="5"/>
       <c r="CA7" s="5"/>
       <c r="CB7" s="5"/>
-      <c r="CC7" s="5"/>
+      <c r="CC7" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="CD7" s="5"/>
       <c r="CE7" s="5"/>
       <c r="CF7" s="5"/>
@@ -5366,39 +5393,40 @@
       <c r="OU7" s="5"/>
       <c r="OV7" s="5"/>
       <c r="OW7" s="5"/>
-      <c r="OX7" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY7" s="5"/>
+      <c r="OX7" s="5"/>
+      <c r="OY7" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ7" s="5"/>
       <c r="PA7" s="5"/>
       <c r="PB7" s="5"/>
       <c r="PC7" s="5"/>
       <c r="PD7" s="5"/>
       <c r="PE7" s="5"/>
-      <c r="PF7" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG7" s="5"/>
+      <c r="PF7" s="5"/>
+      <c r="PG7" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH7" s="5"/>
       <c r="PI7" s="5"/>
+      <c r="PJ7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>431</v>
-      </c>
       <c r="D8" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -5433,7 +5461,7 @@
       <c r="AI8" s="5"/>
       <c r="AJ8" s="5"/>
       <c r="AK8" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
@@ -5478,7 +5506,9 @@
       <c r="BZ8" s="5"/>
       <c r="CA8" s="5"/>
       <c r="CB8" s="5"/>
-      <c r="CC8" s="5"/>
+      <c r="CC8" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="CD8" s="5"/>
       <c r="CE8" s="5"/>
       <c r="CF8" s="5"/>
@@ -5811,39 +5841,40 @@
       <c r="OU8" s="5"/>
       <c r="OV8" s="5"/>
       <c r="OW8" s="5"/>
-      <c r="OX8" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY8" s="5"/>
+      <c r="OX8" s="5"/>
+      <c r="OY8" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ8" s="5"/>
       <c r="PA8" s="5"/>
       <c r="PB8" s="5"/>
       <c r="PC8" s="5"/>
       <c r="PD8" s="5"/>
       <c r="PE8" s="5"/>
-      <c r="PF8" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG8" s="5"/>
+      <c r="PF8" s="5"/>
+      <c r="PG8" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH8" s="5"/>
       <c r="PI8" s="5"/>
+      <c r="PJ8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -5878,7 +5909,7 @@
       <c r="AI9" s="5"/>
       <c r="AJ9" s="5"/>
       <c r="AK9" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL9" s="5"/>
       <c r="AM9" s="5"/>
@@ -5923,7 +5954,9 @@
       <c r="BZ9" s="5"/>
       <c r="CA9" s="5"/>
       <c r="CB9" s="5"/>
-      <c r="CC9" s="5"/>
+      <c r="CC9" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="CD9" s="5"/>
       <c r="CE9" s="5"/>
       <c r="CF9" s="5"/>
@@ -6256,39 +6289,40 @@
       <c r="OU9" s="5"/>
       <c r="OV9" s="5"/>
       <c r="OW9" s="5"/>
-      <c r="OX9" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY9" s="5"/>
+      <c r="OX9" s="5"/>
+      <c r="OY9" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ9" s="5"/>
       <c r="PA9" s="5"/>
       <c r="PB9" s="5"/>
       <c r="PC9" s="5"/>
       <c r="PD9" s="5"/>
       <c r="PE9" s="5"/>
-      <c r="PF9" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG9" s="5"/>
+      <c r="PF9" s="5"/>
+      <c r="PG9" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH9" s="5"/>
       <c r="PI9" s="5"/>
+      <c r="PJ9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -6323,7 +6357,7 @@
       <c r="AI10" s="5"/>
       <c r="AJ10" s="5"/>
       <c r="AK10" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
@@ -6368,7 +6402,9 @@
       <c r="BZ10" s="5"/>
       <c r="CA10" s="5"/>
       <c r="CB10" s="5"/>
-      <c r="CC10" s="5"/>
+      <c r="CC10" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="CD10" s="5"/>
       <c r="CE10" s="5"/>
       <c r="CF10" s="5"/>
@@ -6701,29 +6737,30 @@
       <c r="OU10" s="5"/>
       <c r="OV10" s="5"/>
       <c r="OW10" s="5"/>
-      <c r="OX10" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY10" s="5"/>
+      <c r="OX10" s="5"/>
+      <c r="OY10" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ10" s="5"/>
       <c r="PA10" s="5"/>
       <c r="PB10" s="5"/>
       <c r="PC10" s="5"/>
       <c r="PD10" s="5"/>
       <c r="PE10" s="5"/>
-      <c r="PF10" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG10" s="5"/>
+      <c r="PF10" s="5"/>
+      <c r="PG10" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH10" s="5"/>
       <c r="PI10" s="5"/>
+      <c r="PJ10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>101.17</v>
@@ -6813,7 +6850,9 @@
       <c r="BZ11" s="5"/>
       <c r="CA11" s="5"/>
       <c r="CB11" s="5"/>
-      <c r="CC11" s="5"/>
+      <c r="CC11" s="5" t="n">
+        <v>1607.72</v>
+      </c>
       <c r="CD11" s="5"/>
       <c r="CE11" s="5"/>
       <c r="CF11" s="5"/>
@@ -7146,29 +7185,30 @@
       <c r="OU11" s="5"/>
       <c r="OV11" s="5"/>
       <c r="OW11" s="5"/>
-      <c r="OX11" s="5" t="n">
+      <c r="OX11" s="5"/>
+      <c r="OY11" s="5" t="n">
         <v>166.28</v>
       </c>
-      <c r="OY11" s="5"/>
       <c r="OZ11" s="5"/>
       <c r="PA11" s="5"/>
       <c r="PB11" s="5"/>
       <c r="PC11" s="5"/>
       <c r="PD11" s="5"/>
       <c r="PE11" s="5"/>
-      <c r="PF11" s="5" t="n">
+      <c r="PF11" s="5"/>
+      <c r="PG11" s="5" t="n">
         <v>101.17</v>
       </c>
-      <c r="PG11" s="5"/>
       <c r="PH11" s="5"/>
       <c r="PI11" s="5"/>
+      <c r="PJ11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>90.65</v>
@@ -7258,7 +7298,9 @@
       <c r="BZ12" s="5"/>
       <c r="CA12" s="5"/>
       <c r="CB12" s="5"/>
-      <c r="CC12" s="5"/>
+      <c r="CC12" s="5" t="n">
+        <v>1168.22</v>
+      </c>
       <c r="CD12" s="5"/>
       <c r="CE12" s="5"/>
       <c r="CF12" s="5"/>
@@ -7591,29 +7633,30 @@
       <c r="OU12" s="5"/>
       <c r="OV12" s="5"/>
       <c r="OW12" s="5"/>
-      <c r="OX12" s="5" t="n">
+      <c r="OX12" s="5"/>
+      <c r="OY12" s="5" t="n">
         <v>145.14</v>
       </c>
-      <c r="OY12" s="5"/>
       <c r="OZ12" s="5"/>
       <c r="PA12" s="5"/>
       <c r="PB12" s="5"/>
       <c r="PC12" s="5"/>
       <c r="PD12" s="5"/>
       <c r="PE12" s="5"/>
-      <c r="PF12" s="5" t="n">
+      <c r="PF12" s="5"/>
+      <c r="PG12" s="5" t="n">
         <v>90.65</v>
       </c>
-      <c r="PG12" s="5"/>
       <c r="PH12" s="5"/>
       <c r="PI12" s="5"/>
+      <c r="PJ12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>30.91</v>
@@ -7703,7 +7746,9 @@
       <c r="BZ13" s="5"/>
       <c r="CA13" s="5"/>
       <c r="CB13" s="5"/>
-      <c r="CC13" s="5"/>
+      <c r="CC13" s="5" t="n">
+        <v>762.78</v>
+      </c>
       <c r="CD13" s="5"/>
       <c r="CE13" s="5"/>
       <c r="CF13" s="5"/>
@@ -8036,29 +8081,30 @@
       <c r="OU13" s="5"/>
       <c r="OV13" s="5"/>
       <c r="OW13" s="5"/>
-      <c r="OX13" s="5" t="n">
+      <c r="OX13" s="5"/>
+      <c r="OY13" s="5" t="n">
         <v>47.79</v>
       </c>
-      <c r="OY13" s="5"/>
       <c r="OZ13" s="5"/>
       <c r="PA13" s="5"/>
       <c r="PB13" s="5"/>
       <c r="PC13" s="5"/>
       <c r="PD13" s="5"/>
       <c r="PE13" s="5"/>
-      <c r="PF13" s="5" t="n">
+      <c r="PF13" s="5"/>
+      <c r="PG13" s="5" t="n">
         <v>30.91</v>
       </c>
-      <c r="PG13" s="5"/>
       <c r="PH13" s="5"/>
       <c r="PI13" s="5"/>
+      <c r="PJ13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>22.81</v>
@@ -8073,7 +8119,7 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -8148,7 +8194,9 @@
       <c r="BZ14" s="5"/>
       <c r="CA14" s="5"/>
       <c r="CB14" s="5"/>
-      <c r="CC14" s="5"/>
+      <c r="CC14" s="5" t="n">
+        <v>178.39</v>
+      </c>
       <c r="CD14" s="5"/>
       <c r="CE14" s="5"/>
       <c r="CF14" s="5"/>
@@ -8481,29 +8529,30 @@
       <c r="OU14" s="5"/>
       <c r="OV14" s="5"/>
       <c r="OW14" s="5"/>
-      <c r="OX14" s="5" t="n">
+      <c r="OX14" s="5"/>
+      <c r="OY14" s="5" t="n">
         <v>35.16</v>
       </c>
-      <c r="OY14" s="5"/>
       <c r="OZ14" s="5"/>
       <c r="PA14" s="5"/>
       <c r="PB14" s="5"/>
       <c r="PC14" s="5"/>
       <c r="PD14" s="5"/>
       <c r="PE14" s="5"/>
-      <c r="PF14" s="5" t="n">
+      <c r="PF14" s="5"/>
+      <c r="PG14" s="5" t="n">
         <v>22.81</v>
       </c>
-      <c r="PG14" s="5"/>
       <c r="PH14" s="5"/>
       <c r="PI14" s="5"/>
+      <c r="PJ14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>3.7</v>
@@ -8518,7 +8567,7 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -8593,7 +8642,9 @@
       <c r="BZ15" s="5"/>
       <c r="CA15" s="5"/>
       <c r="CB15" s="5"/>
-      <c r="CC15" s="5"/>
+      <c r="CC15" s="5" t="n">
+        <v>33.49</v>
+      </c>
       <c r="CD15" s="5"/>
       <c r="CE15" s="5"/>
       <c r="CF15" s="5"/>
@@ -8926,44 +8977,45 @@
       <c r="OU15" s="5"/>
       <c r="OV15" s="5"/>
       <c r="OW15" s="5"/>
-      <c r="OX15" s="5" t="n">
+      <c r="OX15" s="5"/>
+      <c r="OY15" s="5" t="n">
         <v>5.84</v>
       </c>
-      <c r="OY15" s="5"/>
       <c r="OZ15" s="5"/>
       <c r="PA15" s="5"/>
       <c r="PB15" s="5"/>
       <c r="PC15" s="5"/>
       <c r="PD15" s="5"/>
       <c r="PE15" s="5"/>
-      <c r="PF15" s="5" t="n">
+      <c r="PF15" s="5"/>
+      <c r="PG15" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="PG15" s="5"/>
       <c r="PH15" s="5"/>
       <c r="PI15" s="5"/>
+      <c r="PJ15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>542.3</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -8993,7 +9045,7 @@
       <c r="AI16" s="5"/>
       <c r="AJ16" s="5"/>
       <c r="AK16" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
@@ -9038,7 +9090,9 @@
       <c r="BZ16" s="5"/>
       <c r="CA16" s="5"/>
       <c r="CB16" s="5"/>
-      <c r="CC16" s="5"/>
+      <c r="CC16" s="5" t="n">
+        <v>658.33</v>
+      </c>
       <c r="CD16" s="5"/>
       <c r="CE16" s="5"/>
       <c r="CF16" s="5"/>
@@ -9371,44 +9425,45 @@
       <c r="OU16" s="5"/>
       <c r="OV16" s="5"/>
       <c r="OW16" s="5"/>
-      <c r="OX16" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY16" s="5"/>
+      <c r="OX16" s="5"/>
+      <c r="OY16" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ16" s="5"/>
       <c r="PA16" s="5"/>
       <c r="PB16" s="5"/>
       <c r="PC16" s="5"/>
       <c r="PD16" s="5"/>
       <c r="PE16" s="5"/>
-      <c r="PF16" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG16" s="5"/>
+      <c r="PF16" s="5"/>
+      <c r="PG16" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH16" s="5"/>
       <c r="PI16" s="5"/>
+      <c r="PJ16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>67.21</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -9438,7 +9493,7 @@
       <c r="AI17" s="5"/>
       <c r="AJ17" s="5"/>
       <c r="AK17" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
@@ -9483,7 +9538,9 @@
       <c r="BZ17" s="5"/>
       <c r="CA17" s="5"/>
       <c r="CB17" s="5"/>
-      <c r="CC17" s="5"/>
+      <c r="CC17" s="5" t="n">
+        <v>392.77</v>
+      </c>
       <c r="CD17" s="5"/>
       <c r="CE17" s="5"/>
       <c r="CF17" s="5"/>
@@ -9816,44 +9873,45 @@
       <c r="OU17" s="5"/>
       <c r="OV17" s="5"/>
       <c r="OW17" s="5"/>
-      <c r="OX17" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY17" s="5"/>
+      <c r="OX17" s="5"/>
+      <c r="OY17" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ17" s="5"/>
       <c r="PA17" s="5"/>
       <c r="PB17" s="5"/>
       <c r="PC17" s="5"/>
       <c r="PD17" s="5"/>
       <c r="PE17" s="5"/>
-      <c r="PF17" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG17" s="5"/>
+      <c r="PF17" s="5"/>
+      <c r="PG17" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH17" s="5"/>
       <c r="PI17" s="5"/>
+      <c r="PJ17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>39.31</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
@@ -9883,7 +9941,7 @@
       <c r="AI18" s="5"/>
       <c r="AJ18" s="5"/>
       <c r="AK18" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL18" s="5"/>
       <c r="AM18" s="5"/>
@@ -9928,7 +9986,9 @@
       <c r="BZ18" s="5"/>
       <c r="CA18" s="5"/>
       <c r="CB18" s="5"/>
-      <c r="CC18" s="5"/>
+      <c r="CC18" s="5" t="n">
+        <v>92.49</v>
+      </c>
       <c r="CD18" s="5"/>
       <c r="CE18" s="5"/>
       <c r="CF18" s="5"/>
@@ -10261,44 +10321,45 @@
       <c r="OU18" s="5"/>
       <c r="OV18" s="5"/>
       <c r="OW18" s="5"/>
-      <c r="OX18" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY18" s="5"/>
+      <c r="OX18" s="5"/>
+      <c r="OY18" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ18" s="5"/>
       <c r="PA18" s="5"/>
       <c r="PB18" s="5"/>
       <c r="PC18" s="5"/>
       <c r="PD18" s="5"/>
       <c r="PE18" s="5"/>
-      <c r="PF18" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG18" s="5"/>
+      <c r="PF18" s="5"/>
+      <c r="PG18" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH18" s="5"/>
       <c r="PI18" s="5"/>
+      <c r="PJ18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>10.59</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
@@ -10328,7 +10389,7 @@
       <c r="AI19" s="5"/>
       <c r="AJ19" s="5"/>
       <c r="AK19" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL19" s="5"/>
       <c r="AM19" s="5"/>
@@ -10373,7 +10434,9 @@
       <c r="BZ19" s="5"/>
       <c r="CA19" s="5"/>
       <c r="CB19" s="5"/>
-      <c r="CC19" s="5"/>
+      <c r="CC19" s="5" t="n">
+        <v>21.75</v>
+      </c>
       <c r="CD19" s="5"/>
       <c r="CE19" s="5"/>
       <c r="CF19" s="5"/>
@@ -10706,29 +10769,30 @@
       <c r="OU19" s="5"/>
       <c r="OV19" s="5"/>
       <c r="OW19" s="5"/>
-      <c r="OX19" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY19" s="5"/>
+      <c r="OX19" s="5"/>
+      <c r="OY19" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ19" s="5"/>
       <c r="PA19" s="5"/>
       <c r="PB19" s="5"/>
       <c r="PC19" s="5"/>
       <c r="PD19" s="5"/>
       <c r="PE19" s="5"/>
-      <c r="PF19" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG19" s="5"/>
+      <c r="PF19" s="5"/>
+      <c r="PG19" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH19" s="5"/>
       <c r="PI19" s="5"/>
+      <c r="PJ19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>126.95</v>
@@ -10818,7 +10882,9 @@
       <c r="BZ20" s="5"/>
       <c r="CA20" s="5"/>
       <c r="CB20" s="5"/>
-      <c r="CC20" s="5"/>
+      <c r="CC20" s="5" t="n">
+        <v>802.35</v>
+      </c>
       <c r="CD20" s="5"/>
       <c r="CE20" s="5"/>
       <c r="CF20" s="5"/>
@@ -11151,29 +11217,30 @@
       <c r="OU20" s="5"/>
       <c r="OV20" s="5"/>
       <c r="OW20" s="5"/>
-      <c r="OX20" s="5" t="n">
+      <c r="OX20" s="5"/>
+      <c r="OY20" s="5" t="n">
         <v>261.28</v>
       </c>
-      <c r="OY20" s="5"/>
       <c r="OZ20" s="5"/>
       <c r="PA20" s="5"/>
       <c r="PB20" s="5"/>
       <c r="PC20" s="5"/>
       <c r="PD20" s="5"/>
       <c r="PE20" s="5"/>
-      <c r="PF20" s="5" t="n">
+      <c r="PF20" s="5"/>
+      <c r="PG20" s="5" t="n">
         <v>126.95</v>
       </c>
-      <c r="PG20" s="5"/>
       <c r="PH20" s="5"/>
       <c r="PI20" s="5"/>
+      <c r="PJ20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>97.5</v>
@@ -11263,7 +11330,9 @@
       <c r="BZ21" s="5"/>
       <c r="CA21" s="5"/>
       <c r="CB21" s="5"/>
-      <c r="CC21" s="5"/>
+      <c r="CC21" s="5" t="n">
+        <v>1018.68</v>
+      </c>
       <c r="CD21" s="5"/>
       <c r="CE21" s="5"/>
       <c r="CF21" s="5"/>
@@ -11596,29 +11665,30 @@
       <c r="OU21" s="5"/>
       <c r="OV21" s="5"/>
       <c r="OW21" s="5"/>
-      <c r="OX21" s="5" t="n">
+      <c r="OX21" s="5"/>
+      <c r="OY21" s="5" t="n">
         <v>162.79</v>
       </c>
-      <c r="OY21" s="5"/>
       <c r="OZ21" s="5"/>
       <c r="PA21" s="5"/>
       <c r="PB21" s="5"/>
       <c r="PC21" s="5"/>
       <c r="PD21" s="5"/>
       <c r="PE21" s="5"/>
-      <c r="PF21" s="5" t="n">
+      <c r="PF21" s="5"/>
+      <c r="PG21" s="5" t="n">
         <v>97.5</v>
       </c>
-      <c r="PG21" s="5"/>
       <c r="PH21" s="5"/>
       <c r="PI21" s="5"/>
+      <c r="PJ21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>14.87</v>
@@ -11708,7 +11778,9 @@
       <c r="BZ22" s="5"/>
       <c r="CA22" s="5"/>
       <c r="CB22" s="5"/>
-      <c r="CC22" s="5"/>
+      <c r="CC22" s="5" t="n">
+        <v>175.72</v>
+      </c>
       <c r="CD22" s="5"/>
       <c r="CE22" s="5"/>
       <c r="CF22" s="5"/>
@@ -12041,29 +12113,30 @@
       <c r="OU22" s="5"/>
       <c r="OV22" s="5"/>
       <c r="OW22" s="5"/>
-      <c r="OX22" s="5" t="n">
+      <c r="OX22" s="5"/>
+      <c r="OY22" s="5" t="n">
         <v>25.13</v>
       </c>
-      <c r="OY22" s="5"/>
       <c r="OZ22" s="5"/>
       <c r="PA22" s="5"/>
       <c r="PB22" s="5"/>
       <c r="PC22" s="5"/>
       <c r="PD22" s="5"/>
       <c r="PE22" s="5"/>
-      <c r="PF22" s="5" t="n">
+      <c r="PF22" s="5"/>
+      <c r="PG22" s="5" t="n">
         <v>14.87</v>
       </c>
-      <c r="PG22" s="5"/>
       <c r="PH22" s="5"/>
       <c r="PI22" s="5"/>
+      <c r="PJ22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>29.95</v>
@@ -12153,7 +12226,9 @@
       <c r="BZ23" s="5"/>
       <c r="CA23" s="5"/>
       <c r="CB23" s="5"/>
-      <c r="CC23" s="5"/>
+      <c r="CC23" s="5" t="n">
+        <v>435.16</v>
+      </c>
       <c r="CD23" s="5"/>
       <c r="CE23" s="5"/>
       <c r="CF23" s="5"/>
@@ -12486,29 +12561,30 @@
       <c r="OU23" s="5"/>
       <c r="OV23" s="5"/>
       <c r="OW23" s="5"/>
-      <c r="OX23" s="5" t="n">
+      <c r="OX23" s="5"/>
+      <c r="OY23" s="5" t="n">
         <v>45.7</v>
       </c>
-      <c r="OY23" s="5"/>
       <c r="OZ23" s="5"/>
       <c r="PA23" s="5"/>
       <c r="PB23" s="5"/>
       <c r="PC23" s="5"/>
       <c r="PD23" s="5"/>
       <c r="PE23" s="5"/>
-      <c r="PF23" s="5" t="n">
+      <c r="PF23" s="5"/>
+      <c r="PG23" s="5" t="n">
         <v>29.95</v>
       </c>
-      <c r="PG23" s="5"/>
       <c r="PH23" s="5"/>
       <c r="PI23" s="5"/>
+      <c r="PJ23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>1536.79</v>
@@ -12598,7 +12674,9 @@
       <c r="BZ24" s="5"/>
       <c r="CA24" s="5"/>
       <c r="CB24" s="5"/>
-      <c r="CC24" s="5"/>
+      <c r="CC24" s="5" t="n">
+        <v>13777.16</v>
+      </c>
       <c r="CD24" s="5"/>
       <c r="CE24" s="5"/>
       <c r="CF24" s="5"/>
@@ -12931,29 +13009,30 @@
       <c r="OU24" s="5"/>
       <c r="OV24" s="5"/>
       <c r="OW24" s="5"/>
-      <c r="OX24" s="5" t="n">
+      <c r="OX24" s="5"/>
+      <c r="OY24" s="5" t="n">
         <v>2672.97</v>
       </c>
-      <c r="OY24" s="5"/>
       <c r="OZ24" s="5"/>
       <c r="PA24" s="5"/>
       <c r="PB24" s="5"/>
       <c r="PC24" s="5"/>
       <c r="PD24" s="5"/>
       <c r="PE24" s="5"/>
-      <c r="PF24" s="5" t="n">
+      <c r="PF24" s="5"/>
+      <c r="PG24" s="5" t="n">
         <v>1536.79</v>
       </c>
-      <c r="PG24" s="5"/>
       <c r="PH24" s="5"/>
       <c r="PI24" s="5"/>
+      <c r="PJ24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C25" s="5" t="n">
         <v>489.67</v>
@@ -13043,7 +13122,9 @@
       <c r="BZ25" s="5"/>
       <c r="CA25" s="5"/>
       <c r="CB25" s="5"/>
-      <c r="CC25" s="5"/>
+      <c r="CC25" s="5" t="n">
+        <v>12743.7</v>
+      </c>
       <c r="CD25" s="5"/>
       <c r="CE25" s="5"/>
       <c r="CF25" s="5"/>
@@ -13376,29 +13457,30 @@
       <c r="OU25" s="5"/>
       <c r="OV25" s="5"/>
       <c r="OW25" s="5"/>
-      <c r="OX25" s="5" t="n">
+      <c r="OX25" s="5"/>
+      <c r="OY25" s="5" t="n">
         <v>834.68</v>
       </c>
-      <c r="OY25" s="5"/>
       <c r="OZ25" s="5"/>
       <c r="PA25" s="5"/>
       <c r="PB25" s="5"/>
       <c r="PC25" s="5"/>
       <c r="PD25" s="5"/>
       <c r="PE25" s="5"/>
-      <c r="PF25" s="5" t="n">
+      <c r="PF25" s="5"/>
+      <c r="PG25" s="5" t="n">
         <v>489.67</v>
       </c>
-      <c r="PG25" s="5"/>
       <c r="PH25" s="5"/>
       <c r="PI25" s="5"/>
+      <c r="PJ25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C26" s="5" t="n">
         <v>376.19</v>
@@ -13488,7 +13570,9 @@
       <c r="BZ26" s="5"/>
       <c r="CA26" s="5"/>
       <c r="CB26" s="5"/>
-      <c r="CC26" s="5"/>
+      <c r="CC26" s="5" t="n">
+        <v>10285.03</v>
+      </c>
       <c r="CD26" s="5"/>
       <c r="CE26" s="5"/>
       <c r="CF26" s="5"/>
@@ -13821,29 +13905,30 @@
       <c r="OU26" s="5"/>
       <c r="OV26" s="5"/>
       <c r="OW26" s="5"/>
-      <c r="OX26" s="5" t="n">
+      <c r="OX26" s="5"/>
+      <c r="OY26" s="5" t="n">
         <v>621.48</v>
       </c>
-      <c r="OY26" s="5"/>
       <c r="OZ26" s="5"/>
       <c r="PA26" s="5"/>
       <c r="PB26" s="5"/>
       <c r="PC26" s="5"/>
       <c r="PD26" s="5"/>
       <c r="PE26" s="5"/>
-      <c r="PF26" s="5" t="n">
+      <c r="PF26" s="5"/>
+      <c r="PG26" s="5" t="n">
         <v>376.19</v>
       </c>
-      <c r="PG26" s="5"/>
       <c r="PH26" s="5"/>
       <c r="PI26" s="5"/>
+      <c r="PJ26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C27" s="5" t="n">
         <v>1.96</v>
@@ -13933,7 +14018,9 @@
       <c r="BZ27" s="5"/>
       <c r="CA27" s="5"/>
       <c r="CB27" s="5"/>
-      <c r="CC27" s="5"/>
+      <c r="CC27" s="5" t="n">
+        <v>239.09</v>
+      </c>
       <c r="CD27" s="5"/>
       <c r="CE27" s="5"/>
       <c r="CF27" s="5"/>
@@ -14266,29 +14353,30 @@
       <c r="OU27" s="5"/>
       <c r="OV27" s="5"/>
       <c r="OW27" s="5"/>
-      <c r="OX27" s="5" t="n">
+      <c r="OX27" s="5"/>
+      <c r="OY27" s="5" t="n">
         <v>3.42</v>
       </c>
-      <c r="OY27" s="5"/>
       <c r="OZ27" s="5"/>
       <c r="PA27" s="5"/>
       <c r="PB27" s="5"/>
       <c r="PC27" s="5"/>
       <c r="PD27" s="5"/>
       <c r="PE27" s="5"/>
-      <c r="PF27" s="5" t="n">
+      <c r="PF27" s="5"/>
+      <c r="PG27" s="5" t="n">
         <v>1.96</v>
       </c>
-      <c r="PG27" s="5"/>
       <c r="PH27" s="5"/>
       <c r="PI27" s="5"/>
+      <c r="PJ27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C28" s="5" t="n">
         <v>2.62</v>
@@ -14378,7 +14466,9 @@
       <c r="BZ28" s="5"/>
       <c r="CA28" s="5"/>
       <c r="CB28" s="5"/>
-      <c r="CC28" s="5"/>
+      <c r="CC28" s="5" t="n">
+        <v>317.52</v>
+      </c>
       <c r="CD28" s="5"/>
       <c r="CE28" s="5"/>
       <c r="CF28" s="5"/>
@@ -14711,29 +14801,30 @@
       <c r="OU28" s="5"/>
       <c r="OV28" s="5"/>
       <c r="OW28" s="5"/>
-      <c r="OX28" s="5" t="n">
+      <c r="OX28" s="5"/>
+      <c r="OY28" s="5" t="n">
         <v>4.79</v>
       </c>
-      <c r="OY28" s="5"/>
       <c r="OZ28" s="5"/>
       <c r="PA28" s="5"/>
       <c r="PB28" s="5"/>
       <c r="PC28" s="5"/>
       <c r="PD28" s="5"/>
       <c r="PE28" s="5"/>
-      <c r="PF28" s="5" t="n">
+      <c r="PF28" s="5"/>
+      <c r="PG28" s="5" t="n">
         <v>2.62</v>
       </c>
-      <c r="PG28" s="5"/>
       <c r="PH28" s="5"/>
       <c r="PI28" s="5"/>
+      <c r="PJ28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C29" s="5" t="n">
         <v>3.93</v>
@@ -14823,7 +14914,9 @@
       <c r="BZ29" s="5"/>
       <c r="CA29" s="5"/>
       <c r="CB29" s="5"/>
-      <c r="CC29" s="5"/>
+      <c r="CC29" s="5" t="n">
+        <v>79.5</v>
+      </c>
       <c r="CD29" s="5"/>
       <c r="CE29" s="5"/>
       <c r="CF29" s="5"/>
@@ -15156,29 +15249,30 @@
       <c r="OU29" s="5"/>
       <c r="OV29" s="5"/>
       <c r="OW29" s="5"/>
-      <c r="OX29" s="5" t="n">
+      <c r="OX29" s="5"/>
+      <c r="OY29" s="5" t="n">
         <v>7.98</v>
       </c>
-      <c r="OY29" s="5"/>
       <c r="OZ29" s="5"/>
       <c r="PA29" s="5"/>
       <c r="PB29" s="5"/>
       <c r="PC29" s="5"/>
       <c r="PD29" s="5"/>
       <c r="PE29" s="5"/>
-      <c r="PF29" s="5" t="n">
+      <c r="PF29" s="5"/>
+      <c r="PG29" s="5" t="n">
         <v>3.93</v>
       </c>
-      <c r="PG29" s="5"/>
       <c r="PH29" s="5"/>
       <c r="PI29" s="5"/>
+      <c r="PJ29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C30" s="5" t="n">
         <v>1.51</v>
@@ -15268,7 +15362,9 @@
       <c r="BZ30" s="5"/>
       <c r="CA30" s="5"/>
       <c r="CB30" s="5"/>
-      <c r="CC30" s="5"/>
+      <c r="CC30" s="5" t="n">
+        <v>63.6</v>
+      </c>
       <c r="CD30" s="5"/>
       <c r="CE30" s="5"/>
       <c r="CF30" s="5"/>
@@ -15601,29 +15697,30 @@
       <c r="OU30" s="5"/>
       <c r="OV30" s="5"/>
       <c r="OW30" s="5"/>
-      <c r="OX30" s="5" t="n">
+      <c r="OX30" s="5"/>
+      <c r="OY30" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="OY30" s="5"/>
       <c r="OZ30" s="5"/>
       <c r="PA30" s="5"/>
       <c r="PB30" s="5"/>
       <c r="PC30" s="5"/>
       <c r="PD30" s="5"/>
       <c r="PE30" s="5"/>
-      <c r="PF30" s="5" t="n">
+      <c r="PF30" s="5"/>
+      <c r="PG30" s="5" t="n">
         <v>1.51</v>
       </c>
-      <c r="PG30" s="5"/>
       <c r="PH30" s="5"/>
       <c r="PI30" s="5"/>
+      <c r="PJ30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C31" s="5" t="n">
         <v>0.3</v>
@@ -15638,7 +15735,7 @@
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
@@ -15713,7 +15810,9 @@
       <c r="BZ31" s="5"/>
       <c r="CA31" s="5"/>
       <c r="CB31" s="5"/>
-      <c r="CC31" s="5"/>
+      <c r="CC31" s="5" t="n">
+        <v>4266.67</v>
+      </c>
       <c r="CD31" s="5"/>
       <c r="CE31" s="5"/>
       <c r="CF31" s="5"/>
@@ -16046,29 +16145,30 @@
       <c r="OU31" s="5"/>
       <c r="OV31" s="5"/>
       <c r="OW31" s="5"/>
-      <c r="OX31" s="5" t="n">
+      <c r="OX31" s="5"/>
+      <c r="OY31" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="OY31" s="5"/>
       <c r="OZ31" s="5"/>
       <c r="PA31" s="5"/>
       <c r="PB31" s="5"/>
       <c r="PC31" s="5"/>
       <c r="PD31" s="5"/>
       <c r="PE31" s="5"/>
-      <c r="PF31" s="5" t="n">
+      <c r="PF31" s="5"/>
+      <c r="PG31" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="PG31" s="5"/>
       <c r="PH31" s="5"/>
       <c r="PI31" s="5"/>
+      <c r="PJ31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C32" s="5" t="n">
         <v>285.71</v>
@@ -16083,7 +16183,7 @@
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
@@ -16158,7 +16258,9 @@
       <c r="BZ32" s="5"/>
       <c r="CA32" s="5"/>
       <c r="CB32" s="5"/>
-      <c r="CC32" s="5"/>
+      <c r="CC32" s="5" t="n">
+        <v>5333.33</v>
+      </c>
       <c r="CD32" s="5"/>
       <c r="CE32" s="5"/>
       <c r="CF32" s="5"/>
@@ -16491,44 +16593,45 @@
       <c r="OU32" s="5"/>
       <c r="OV32" s="5"/>
       <c r="OW32" s="5"/>
-      <c r="OX32" s="5" t="n">
+      <c r="OX32" s="5"/>
+      <c r="OY32" s="5" t="n">
         <v>695.65</v>
       </c>
-      <c r="OY32" s="5"/>
       <c r="OZ32" s="5"/>
       <c r="PA32" s="5"/>
       <c r="PB32" s="5"/>
       <c r="PC32" s="5"/>
       <c r="PD32" s="5"/>
       <c r="PE32" s="5"/>
-      <c r="PF32" s="5" t="n">
+      <c r="PF32" s="5"/>
+      <c r="PG32" s="5" t="n">
         <v>285.71</v>
       </c>
-      <c r="PG32" s="5"/>
       <c r="PH32" s="5"/>
       <c r="PI32" s="5"/>
+      <c r="PJ32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
@@ -16558,7 +16661,7 @@
       <c r="AI33" s="5"/>
       <c r="AJ33" s="5"/>
       <c r="AK33" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
@@ -16603,7 +16706,9 @@
       <c r="BZ33" s="5"/>
       <c r="CA33" s="5"/>
       <c r="CB33" s="5"/>
-      <c r="CC33" s="5"/>
+      <c r="CC33" s="5" t="n">
+        <v>1.47</v>
+      </c>
       <c r="CD33" s="5"/>
       <c r="CE33" s="5"/>
       <c r="CF33" s="5"/>
@@ -16936,44 +17041,45 @@
       <c r="OU33" s="5"/>
       <c r="OV33" s="5"/>
       <c r="OW33" s="5"/>
-      <c r="OX33" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY33" s="5"/>
+      <c r="OX33" s="5"/>
+      <c r="OY33" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ33" s="5"/>
       <c r="PA33" s="5"/>
       <c r="PB33" s="5"/>
       <c r="PC33" s="5"/>
       <c r="PD33" s="5"/>
       <c r="PE33" s="5"/>
-      <c r="PF33" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG33" s="5"/>
+      <c r="PF33" s="5"/>
+      <c r="PG33" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH33" s="5"/>
       <c r="PI33" s="5"/>
+      <c r="PJ33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
@@ -17003,7 +17109,7 @@
       <c r="AI34" s="5"/>
       <c r="AJ34" s="5"/>
       <c r="AK34" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
@@ -17048,7 +17154,9 @@
       <c r="BZ34" s="5"/>
       <c r="CA34" s="5"/>
       <c r="CB34" s="5"/>
-      <c r="CC34" s="5"/>
+      <c r="CC34" s="5" t="n">
+        <v>1.62</v>
+      </c>
       <c r="CD34" s="5"/>
       <c r="CE34" s="5"/>
       <c r="CF34" s="5"/>
@@ -17381,44 +17489,45 @@
       <c r="OU34" s="5"/>
       <c r="OV34" s="5"/>
       <c r="OW34" s="5"/>
-      <c r="OX34" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY34" s="5"/>
+      <c r="OX34" s="5"/>
+      <c r="OY34" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ34" s="5"/>
       <c r="PA34" s="5"/>
       <c r="PB34" s="5"/>
       <c r="PC34" s="5"/>
       <c r="PD34" s="5"/>
       <c r="PE34" s="5"/>
-      <c r="PF34" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG34" s="5"/>
+      <c r="PF34" s="5"/>
+      <c r="PG34" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH34" s="5"/>
       <c r="PI34" s="5"/>
+      <c r="PJ34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
@@ -17448,7 +17557,7 @@
       <c r="AI35" s="5"/>
       <c r="AJ35" s="5"/>
       <c r="AK35" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
@@ -17493,7 +17602,9 @@
       <c r="BZ35" s="5"/>
       <c r="CA35" s="5"/>
       <c r="CB35" s="5"/>
-      <c r="CC35" s="5"/>
+      <c r="CC35" s="5" t="n">
+        <v>27.46</v>
+      </c>
       <c r="CD35" s="5"/>
       <c r="CE35" s="5"/>
       <c r="CF35" s="5"/>
@@ -17826,44 +17937,45 @@
       <c r="OU35" s="5"/>
       <c r="OV35" s="5"/>
       <c r="OW35" s="5"/>
-      <c r="OX35" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY35" s="5"/>
+      <c r="OX35" s="5"/>
+      <c r="OY35" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ35" s="5"/>
       <c r="PA35" s="5"/>
       <c r="PB35" s="5"/>
       <c r="PC35" s="5"/>
       <c r="PD35" s="5"/>
       <c r="PE35" s="5"/>
-      <c r="PF35" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG35" s="5"/>
+      <c r="PF35" s="5"/>
+      <c r="PG35" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH35" s="5"/>
       <c r="PI35" s="5"/>
+      <c r="PJ35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
@@ -17893,7 +18005,7 @@
       <c r="AI36" s="5"/>
       <c r="AJ36" s="5"/>
       <c r="AK36" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
@@ -17938,7 +18050,9 @@
       <c r="BZ36" s="5"/>
       <c r="CA36" s="5"/>
       <c r="CB36" s="5"/>
-      <c r="CC36" s="5"/>
+      <c r="CC36" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="CD36" s="5"/>
       <c r="CE36" s="5"/>
       <c r="CF36" s="5"/>
@@ -18271,44 +18385,45 @@
       <c r="OU36" s="5"/>
       <c r="OV36" s="5"/>
       <c r="OW36" s="5"/>
-      <c r="OX36" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY36" s="5"/>
+      <c r="OX36" s="5"/>
+      <c r="OY36" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ36" s="5"/>
       <c r="PA36" s="5"/>
       <c r="PB36" s="5"/>
       <c r="PC36" s="5"/>
       <c r="PD36" s="5"/>
       <c r="PE36" s="5"/>
-      <c r="PF36" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG36" s="5"/>
+      <c r="PF36" s="5"/>
+      <c r="PG36" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH36" s="5"/>
       <c r="PI36" s="5"/>
+      <c r="PJ36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
@@ -18338,7 +18453,7 @@
       <c r="AI37" s="5"/>
       <c r="AJ37" s="5"/>
       <c r="AK37" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
@@ -18383,7 +18498,9 @@
       <c r="BZ37" s="5"/>
       <c r="CA37" s="5"/>
       <c r="CB37" s="5"/>
-      <c r="CC37" s="5"/>
+      <c r="CC37" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="CD37" s="5"/>
       <c r="CE37" s="5"/>
       <c r="CF37" s="5"/>
@@ -18716,29 +18833,30 @@
       <c r="OU37" s="5"/>
       <c r="OV37" s="5"/>
       <c r="OW37" s="5"/>
-      <c r="OX37" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY37" s="5"/>
+      <c r="OX37" s="5"/>
+      <c r="OY37" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ37" s="5"/>
       <c r="PA37" s="5"/>
       <c r="PB37" s="5"/>
       <c r="PC37" s="5"/>
       <c r="PD37" s="5"/>
       <c r="PE37" s="5"/>
-      <c r="PF37" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG37" s="5"/>
+      <c r="PF37" s="5"/>
+      <c r="PG37" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH37" s="5"/>
       <c r="PI37" s="5"/>
+      <c r="PJ37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C38" s="5" t="n">
         <v>217.77</v>
@@ -18828,7 +18946,9 @@
       <c r="BZ38" s="5"/>
       <c r="CA38" s="5"/>
       <c r="CB38" s="5"/>
-      <c r="CC38" s="5"/>
+      <c r="CC38" s="5" t="n">
+        <v>13.32</v>
+      </c>
       <c r="CD38" s="5"/>
       <c r="CE38" s="5"/>
       <c r="CF38" s="5"/>
@@ -19161,35 +19281,36 @@
       <c r="OU38" s="5"/>
       <c r="OV38" s="5"/>
       <c r="OW38" s="5"/>
-      <c r="OX38" s="5" t="n">
+      <c r="OX38" s="5"/>
+      <c r="OY38" s="5" t="n">
         <v>235.85</v>
       </c>
-      <c r="OY38" s="5"/>
       <c r="OZ38" s="5"/>
       <c r="PA38" s="5"/>
       <c r="PB38" s="5"/>
       <c r="PC38" s="5"/>
       <c r="PD38" s="5"/>
       <c r="PE38" s="5"/>
-      <c r="PF38" s="5" t="n">
+      <c r="PF38" s="5"/>
+      <c r="PG38" s="5" t="n">
         <v>217.77</v>
       </c>
-      <c r="PG38" s="5"/>
       <c r="PH38" s="5"/>
       <c r="PI38" s="5"/>
+      <c r="PJ38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C39" s="5" t="n">
         <v>881.83</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5" t="n">
@@ -19198,7 +19319,7 @@
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
@@ -19273,7 +19394,9 @@
       <c r="BZ39" s="5"/>
       <c r="CA39" s="5"/>
       <c r="CB39" s="5"/>
-      <c r="CC39" s="5"/>
+      <c r="CC39" s="5" t="n">
+        <v>15225.45</v>
+      </c>
       <c r="CD39" s="5"/>
       <c r="CE39" s="5"/>
       <c r="CF39" s="5"/>
@@ -19606,35 +19729,36 @@
       <c r="OU39" s="5"/>
       <c r="OV39" s="5"/>
       <c r="OW39" s="5"/>
-      <c r="OX39" s="5" t="n">
+      <c r="OX39" s="5"/>
+      <c r="OY39" s="5" t="n">
         <v>2969.01</v>
       </c>
-      <c r="OY39" s="5"/>
       <c r="OZ39" s="5"/>
       <c r="PA39" s="5"/>
       <c r="PB39" s="5"/>
       <c r="PC39" s="5"/>
       <c r="PD39" s="5"/>
       <c r="PE39" s="5"/>
-      <c r="PF39" s="5" t="n">
+      <c r="PF39" s="5"/>
+      <c r="PG39" s="5" t="n">
         <v>881.32</v>
       </c>
-      <c r="PG39" s="5"/>
       <c r="PH39" s="5"/>
       <c r="PI39" s="5"/>
+      <c r="PJ39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C40" s="5" t="n">
         <v>4.05</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5" t="n">
@@ -19643,7 +19767,7 @@
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
@@ -19718,7 +19842,9 @@
       <c r="BZ40" s="5"/>
       <c r="CA40" s="5"/>
       <c r="CB40" s="5"/>
-      <c r="CC40" s="5"/>
+      <c r="CC40" s="5" t="n">
+        <v>1143.42</v>
+      </c>
       <c r="CD40" s="5"/>
       <c r="CE40" s="5"/>
       <c r="CF40" s="5"/>
@@ -20051,29 +20177,30 @@
       <c r="OU40" s="5"/>
       <c r="OV40" s="5"/>
       <c r="OW40" s="5"/>
-      <c r="OX40" s="5" t="n">
+      <c r="OX40" s="5"/>
+      <c r="OY40" s="5" t="n">
         <v>12.59</v>
       </c>
-      <c r="OY40" s="5"/>
       <c r="OZ40" s="5"/>
       <c r="PA40" s="5"/>
       <c r="PB40" s="5"/>
       <c r="PC40" s="5"/>
       <c r="PD40" s="5"/>
       <c r="PE40" s="5"/>
-      <c r="PF40" s="5" t="n">
+      <c r="PF40" s="5"/>
+      <c r="PG40" s="5" t="n">
         <v>4.05</v>
       </c>
-      <c r="PG40" s="5"/>
       <c r="PH40" s="5"/>
       <c r="PI40" s="5"/>
+      <c r="PJ40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C41" s="5" t="n">
         <v>8.32</v>
@@ -20163,7 +20290,9 @@
       <c r="BZ41" s="5"/>
       <c r="CA41" s="5"/>
       <c r="CB41" s="5"/>
-      <c r="CC41" s="5"/>
+      <c r="CC41" s="5" t="n">
+        <v>19.08</v>
+      </c>
       <c r="CD41" s="5"/>
       <c r="CE41" s="5"/>
       <c r="CF41" s="5"/>
@@ -20496,29 +20625,30 @@
       <c r="OU41" s="5"/>
       <c r="OV41" s="5"/>
       <c r="OW41" s="5"/>
-      <c r="OX41" s="5" t="n">
+      <c r="OX41" s="5"/>
+      <c r="OY41" s="5" t="n">
         <v>30.94</v>
       </c>
-      <c r="OY41" s="5"/>
       <c r="OZ41" s="5"/>
       <c r="PA41" s="5"/>
       <c r="PB41" s="5"/>
       <c r="PC41" s="5"/>
       <c r="PD41" s="5"/>
       <c r="PE41" s="5"/>
-      <c r="PF41" s="5" t="n">
+      <c r="PF41" s="5"/>
+      <c r="PG41" s="5" t="n">
         <v>8.32</v>
       </c>
-      <c r="PG41" s="5"/>
       <c r="PH41" s="5"/>
       <c r="PI41" s="5"/>
+      <c r="PJ41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C42" s="5" t="n">
         <v>78.28</v>
@@ -20533,7 +20663,7 @@
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
@@ -20608,7 +20738,9 @@
       <c r="BZ42" s="5"/>
       <c r="CA42" s="5"/>
       <c r="CB42" s="5"/>
-      <c r="CC42" s="5"/>
+      <c r="CC42" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="CD42" s="5"/>
       <c r="CE42" s="5"/>
       <c r="CF42" s="5"/>
@@ -20941,39 +21073,40 @@
       <c r="OU42" s="5"/>
       <c r="OV42" s="5"/>
       <c r="OW42" s="5"/>
-      <c r="OX42" s="5" t="n">
+      <c r="OX42" s="5"/>
+      <c r="OY42" s="5" t="n">
         <v>117.15</v>
       </c>
-      <c r="OY42" s="5"/>
       <c r="OZ42" s="5"/>
       <c r="PA42" s="5"/>
       <c r="PB42" s="5"/>
       <c r="PC42" s="5"/>
       <c r="PD42" s="5"/>
       <c r="PE42" s="5"/>
-      <c r="PF42" s="5" t="n">
+      <c r="PF42" s="5"/>
+      <c r="PG42" s="5" t="n">
         <v>78.22</v>
       </c>
-      <c r="PG42" s="5"/>
       <c r="PH42" s="5"/>
       <c r="PI42" s="5"/>
+      <c r="PJ42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -21008,7 +21141,7 @@
       <c r="AI43" s="5"/>
       <c r="AJ43" s="5"/>
       <c r="AK43" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL43" s="5"/>
       <c r="AM43" s="5"/>
@@ -21053,7 +21186,9 @@
       <c r="BZ43" s="5"/>
       <c r="CA43" s="5"/>
       <c r="CB43" s="5"/>
-      <c r="CC43" s="5"/>
+      <c r="CC43" s="5" t="n">
+        <v>4096</v>
+      </c>
       <c r="CD43" s="5"/>
       <c r="CE43" s="5"/>
       <c r="CF43" s="5"/>
@@ -21386,44 +21521,45 @@
       <c r="OU43" s="5"/>
       <c r="OV43" s="5"/>
       <c r="OW43" s="5"/>
-      <c r="OX43" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY43" s="5"/>
+      <c r="OX43" s="5"/>
+      <c r="OY43" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ43" s="5"/>
       <c r="PA43" s="5"/>
       <c r="PB43" s="5"/>
       <c r="PC43" s="5"/>
       <c r="PD43" s="5"/>
       <c r="PE43" s="5"/>
-      <c r="PF43" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG43" s="5"/>
+      <c r="PF43" s="5"/>
+      <c r="PG43" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH43" s="5"/>
       <c r="PI43" s="5"/>
+      <c r="PJ43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
@@ -21453,7 +21589,7 @@
       <c r="AI44" s="5"/>
       <c r="AJ44" s="5"/>
       <c r="AK44" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL44" s="5"/>
       <c r="AM44" s="5"/>
@@ -21498,7 +21634,9 @@
       <c r="BZ44" s="5"/>
       <c r="CA44" s="5"/>
       <c r="CB44" s="5"/>
-      <c r="CC44" s="5"/>
+      <c r="CC44" s="5" t="n">
+        <v>80</v>
+      </c>
       <c r="CD44" s="5"/>
       <c r="CE44" s="5"/>
       <c r="CF44" s="5"/>
@@ -21831,44 +21969,45 @@
       <c r="OU44" s="5"/>
       <c r="OV44" s="5"/>
       <c r="OW44" s="5"/>
-      <c r="OX44" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY44" s="5"/>
+      <c r="OX44" s="5"/>
+      <c r="OY44" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ44" s="5"/>
       <c r="PA44" s="5"/>
       <c r="PB44" s="5"/>
       <c r="PC44" s="5"/>
       <c r="PD44" s="5"/>
       <c r="PE44" s="5"/>
-      <c r="PF44" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG44" s="5"/>
+      <c r="PF44" s="5"/>
+      <c r="PG44" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH44" s="5"/>
       <c r="PI44" s="5"/>
+      <c r="PJ44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
@@ -21898,7 +22037,7 @@
       <c r="AI45" s="5"/>
       <c r="AJ45" s="5"/>
       <c r="AK45" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL45" s="5"/>
       <c r="AM45" s="5"/>
@@ -21943,7 +22082,9 @@
       <c r="BZ45" s="5"/>
       <c r="CA45" s="5"/>
       <c r="CB45" s="5"/>
-      <c r="CC45" s="5"/>
+      <c r="CC45" s="5" t="n">
+        <v>1001</v>
+      </c>
       <c r="CD45" s="5"/>
       <c r="CE45" s="5"/>
       <c r="CF45" s="5"/>
@@ -22276,44 +22417,45 @@
       <c r="OU45" s="5"/>
       <c r="OV45" s="5"/>
       <c r="OW45" s="5"/>
-      <c r="OX45" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY45" s="5"/>
+      <c r="OX45" s="5"/>
+      <c r="OY45" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ45" s="5"/>
       <c r="PA45" s="5"/>
       <c r="PB45" s="5"/>
       <c r="PC45" s="5"/>
       <c r="PD45" s="5"/>
       <c r="PE45" s="5"/>
-      <c r="PF45" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG45" s="5"/>
+      <c r="PF45" s="5"/>
+      <c r="PG45" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH45" s="5"/>
       <c r="PI45" s="5"/>
+      <c r="PJ45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
@@ -22343,7 +22485,7 @@
       <c r="AI46" s="5"/>
       <c r="AJ46" s="5"/>
       <c r="AK46" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
@@ -22388,7 +22530,9 @@
       <c r="BZ46" s="5"/>
       <c r="CA46" s="5"/>
       <c r="CB46" s="5"/>
-      <c r="CC46" s="5"/>
+      <c r="CC46" s="5" t="n">
+        <v>3072</v>
+      </c>
       <c r="CD46" s="5"/>
       <c r="CE46" s="5"/>
       <c r="CF46" s="5"/>
@@ -22721,29 +22865,30 @@
       <c r="OU46" s="5"/>
       <c r="OV46" s="5"/>
       <c r="OW46" s="5"/>
-      <c r="OX46" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY46" s="5"/>
+      <c r="OX46" s="5"/>
+      <c r="OY46" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ46" s="5"/>
       <c r="PA46" s="5"/>
       <c r="PB46" s="5"/>
       <c r="PC46" s="5"/>
       <c r="PD46" s="5"/>
       <c r="PE46" s="5"/>
-      <c r="PF46" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG46" s="5"/>
+      <c r="PF46" s="5"/>
+      <c r="PG46" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH46" s="5"/>
       <c r="PI46" s="5"/>
+      <c r="PJ46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C47" s="5" t="n">
         <v>118.62</v>
@@ -22833,7 +22978,9 @@
       <c r="BZ47" s="5"/>
       <c r="CA47" s="5"/>
       <c r="CB47" s="5"/>
-      <c r="CC47" s="5"/>
+      <c r="CC47" s="5" t="n">
+        <v>2090.3</v>
+      </c>
       <c r="CD47" s="5"/>
       <c r="CE47" s="5"/>
       <c r="CF47" s="5"/>
@@ -23166,29 +23313,30 @@
       <c r="OU47" s="5"/>
       <c r="OV47" s="5"/>
       <c r="OW47" s="5"/>
-      <c r="OX47" s="5" t="n">
+      <c r="OX47" s="5"/>
+      <c r="OY47" s="5" t="n">
         <v>357.64</v>
       </c>
-      <c r="OY47" s="5"/>
       <c r="OZ47" s="5"/>
       <c r="PA47" s="5"/>
       <c r="PB47" s="5"/>
       <c r="PC47" s="5"/>
       <c r="PD47" s="5"/>
       <c r="PE47" s="5"/>
-      <c r="PF47" s="5" t="n">
+      <c r="PF47" s="5"/>
+      <c r="PG47" s="5" t="n">
         <v>118.6</v>
       </c>
-      <c r="PG47" s="5"/>
       <c r="PH47" s="5"/>
       <c r="PI47" s="5"/>
+      <c r="PJ47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C48" s="5" t="n">
         <v>122.81</v>
@@ -23278,7 +23426,9 @@
       <c r="BZ48" s="5"/>
       <c r="CA48" s="5"/>
       <c r="CB48" s="5"/>
-      <c r="CC48" s="5"/>
+      <c r="CC48" s="5" t="n">
+        <v>2302.16</v>
+      </c>
       <c r="CD48" s="5"/>
       <c r="CE48" s="5"/>
       <c r="CF48" s="5"/>
@@ -23611,29 +23761,30 @@
       <c r="OU48" s="5"/>
       <c r="OV48" s="5"/>
       <c r="OW48" s="5"/>
-      <c r="OX48" s="5" t="n">
+      <c r="OX48" s="5"/>
+      <c r="OY48" s="5" t="n">
         <v>376.35</v>
       </c>
-      <c r="OY48" s="5"/>
       <c r="OZ48" s="5"/>
       <c r="PA48" s="5"/>
       <c r="PB48" s="5"/>
       <c r="PC48" s="5"/>
       <c r="PD48" s="5"/>
       <c r="PE48" s="5"/>
-      <c r="PF48" s="5" t="n">
+      <c r="PF48" s="5"/>
+      <c r="PG48" s="5" t="n">
         <v>122.81</v>
       </c>
-      <c r="PG48" s="5"/>
       <c r="PH48" s="5"/>
       <c r="PI48" s="5"/>
+      <c r="PJ48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C49" s="5" t="n">
         <v>8.143</v>
@@ -23723,7 +23874,9 @@
       <c r="BZ49" s="5"/>
       <c r="CA49" s="5"/>
       <c r="CB49" s="5"/>
-      <c r="CC49" s="5"/>
+      <c r="CC49" s="5" t="n">
+        <v>0.424</v>
+      </c>
       <c r="CD49" s="5"/>
       <c r="CE49" s="5"/>
       <c r="CF49" s="5"/>
@@ -24056,29 +24209,30 @@
       <c r="OU49" s="5"/>
       <c r="OV49" s="5"/>
       <c r="OW49" s="5"/>
-      <c r="OX49" s="5" t="n">
+      <c r="OX49" s="5"/>
+      <c r="OY49" s="5" t="n">
         <v>2.657</v>
       </c>
-      <c r="OY49" s="5"/>
       <c r="OZ49" s="5"/>
       <c r="PA49" s="5"/>
       <c r="PB49" s="5"/>
       <c r="PC49" s="5"/>
       <c r="PD49" s="5"/>
       <c r="PE49" s="5"/>
-      <c r="PF49" s="5" t="n">
+      <c r="PF49" s="5"/>
+      <c r="PG49" s="5" t="n">
         <v>8.143</v>
       </c>
-      <c r="PG49" s="5"/>
       <c r="PH49" s="5"/>
       <c r="PI49" s="5"/>
+      <c r="PJ49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C50" s="5" t="n">
         <v>11.04</v>
@@ -24168,7 +24322,9 @@
       <c r="BZ50" s="5"/>
       <c r="CA50" s="5"/>
       <c r="CB50" s="5"/>
-      <c r="CC50" s="5"/>
+      <c r="CC50" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="CD50" s="5"/>
       <c r="CE50" s="5"/>
       <c r="CF50" s="5"/>
@@ -24501,29 +24657,30 @@
       <c r="OU50" s="5"/>
       <c r="OV50" s="5"/>
       <c r="OW50" s="5"/>
-      <c r="OX50" s="5" t="n">
+      <c r="OX50" s="5"/>
+      <c r="OY50" s="5" t="n">
         <v>10.01</v>
       </c>
-      <c r="OY50" s="5"/>
       <c r="OZ50" s="5"/>
       <c r="PA50" s="5"/>
       <c r="PB50" s="5"/>
       <c r="PC50" s="5"/>
       <c r="PD50" s="5"/>
       <c r="PE50" s="5"/>
-      <c r="PF50" s="5" t="n">
+      <c r="PF50" s="5"/>
+      <c r="PG50" s="5" t="n">
         <v>11.2</v>
       </c>
-      <c r="PG50" s="5"/>
       <c r="PH50" s="5"/>
       <c r="PI50" s="5"/>
+      <c r="PJ50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C51" s="5" t="n">
         <v>7.24</v>
@@ -24613,7 +24770,9 @@
       <c r="BZ51" s="5"/>
       <c r="CA51" s="5"/>
       <c r="CB51" s="5"/>
-      <c r="CC51" s="5"/>
+      <c r="CC51" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="CD51" s="5"/>
       <c r="CE51" s="5"/>
       <c r="CF51" s="5"/>
@@ -24946,29 +25105,30 @@
       <c r="OU51" s="5"/>
       <c r="OV51" s="5"/>
       <c r="OW51" s="5"/>
-      <c r="OX51" s="5" t="n">
+      <c r="OX51" s="5"/>
+      <c r="OY51" s="5" t="n">
         <v>9.73</v>
       </c>
-      <c r="OY51" s="5"/>
       <c r="OZ51" s="5"/>
       <c r="PA51" s="5"/>
       <c r="PB51" s="5"/>
       <c r="PC51" s="5"/>
       <c r="PD51" s="5"/>
       <c r="PE51" s="5"/>
-      <c r="PF51" s="5" t="n">
+      <c r="PF51" s="5"/>
+      <c r="PG51" s="5" t="n">
         <v>7.4</v>
       </c>
-      <c r="PG51" s="5"/>
       <c r="PH51" s="5"/>
       <c r="PI51" s="5"/>
+      <c r="PJ51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C52" s="5" t="n">
         <v>3.8</v>
@@ -25058,7 +25218,9 @@
       <c r="BZ52" s="5"/>
       <c r="CA52" s="5"/>
       <c r="CB52" s="5"/>
-      <c r="CC52" s="5"/>
+      <c r="CC52" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="CD52" s="5"/>
       <c r="CE52" s="5"/>
       <c r="CF52" s="5"/>
@@ -25391,29 +25553,30 @@
       <c r="OU52" s="5"/>
       <c r="OV52" s="5"/>
       <c r="OW52" s="5"/>
-      <c r="OX52" s="5" t="n">
+      <c r="OX52" s="5"/>
+      <c r="OY52" s="5" t="n">
         <v>0.28</v>
       </c>
-      <c r="OY52" s="5"/>
       <c r="OZ52" s="5"/>
       <c r="PA52" s="5"/>
       <c r="PB52" s="5"/>
       <c r="PC52" s="5"/>
       <c r="PD52" s="5"/>
       <c r="PE52" s="5"/>
-      <c r="PF52" s="5" t="n">
+      <c r="PF52" s="5"/>
+      <c r="PG52" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="PG52" s="5"/>
       <c r="PH52" s="5"/>
       <c r="PI52" s="5"/>
+      <c r="PJ52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C53" s="5" t="n">
         <v>86.39</v>
@@ -25503,7 +25666,9 @@
       <c r="BZ53" s="5"/>
       <c r="CA53" s="5"/>
       <c r="CB53" s="5"/>
-      <c r="CC53" s="5"/>
+      <c r="CC53" s="5" t="n">
+        <v>60.81</v>
+      </c>
       <c r="CD53" s="5"/>
       <c r="CE53" s="5"/>
       <c r="CF53" s="5"/>
@@ -25836,35 +26001,36 @@
       <c r="OU53" s="5"/>
       <c r="OV53" s="5"/>
       <c r="OW53" s="5"/>
-      <c r="OX53" s="5" t="n">
+      <c r="OX53" s="5"/>
+      <c r="OY53" s="5" t="n">
         <v>72.73</v>
       </c>
-      <c r="OY53" s="5"/>
       <c r="OZ53" s="5"/>
       <c r="PA53" s="5"/>
       <c r="PB53" s="5"/>
       <c r="PC53" s="5"/>
       <c r="PD53" s="5"/>
       <c r="PE53" s="5"/>
-      <c r="PF53" s="5" t="n">
+      <c r="PF53" s="5"/>
+      <c r="PG53" s="5" t="n">
         <v>86.36</v>
       </c>
-      <c r="PG53" s="5"/>
       <c r="PH53" s="5"/>
       <c r="PI53" s="5"/>
+      <c r="PJ53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C54" s="5" t="n">
         <v>135.21</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5" t="n">
@@ -25873,7 +26039,7 @@
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
@@ -25948,7 +26114,9 @@
       <c r="BZ54" s="5"/>
       <c r="CA54" s="5"/>
       <c r="CB54" s="5"/>
-      <c r="CC54" s="5"/>
+      <c r="CC54" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="CD54" s="5"/>
       <c r="CE54" s="5"/>
       <c r="CF54" s="5"/>
@@ -26281,29 +26449,30 @@
       <c r="OU54" s="5"/>
       <c r="OV54" s="5"/>
       <c r="OW54" s="5"/>
-      <c r="OX54" s="5" t="n">
+      <c r="OX54" s="5"/>
+      <c r="OY54" s="5" t="n">
         <v>119.52</v>
       </c>
-      <c r="OY54" s="5"/>
       <c r="OZ54" s="5"/>
       <c r="PA54" s="5"/>
       <c r="PB54" s="5"/>
       <c r="PC54" s="5"/>
       <c r="PD54" s="5"/>
       <c r="PE54" s="5"/>
-      <c r="PF54" s="5" t="n">
+      <c r="PF54" s="5"/>
+      <c r="PG54" s="5" t="n">
         <v>134.99</v>
       </c>
-      <c r="PG54" s="5"/>
       <c r="PH54" s="5"/>
       <c r="PI54" s="5"/>
+      <c r="PJ54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C55" s="5" t="n">
         <v>185.19</v>
@@ -26393,7 +26562,9 @@
       <c r="BZ55" s="5"/>
       <c r="CA55" s="5"/>
       <c r="CB55" s="5"/>
-      <c r="CC55" s="5"/>
+      <c r="CC55" s="5" t="n">
+        <v>103.83</v>
+      </c>
       <c r="CD55" s="5"/>
       <c r="CE55" s="5"/>
       <c r="CF55" s="5"/>
@@ -26726,29 +26897,30 @@
       <c r="OU55" s="5"/>
       <c r="OV55" s="5"/>
       <c r="OW55" s="5"/>
-      <c r="OX55" s="5" t="n">
+      <c r="OX55" s="5"/>
+      <c r="OY55" s="5" t="n">
         <v>175.93</v>
       </c>
-      <c r="OY55" s="5"/>
       <c r="OZ55" s="5"/>
       <c r="PA55" s="5"/>
       <c r="PB55" s="5"/>
       <c r="PC55" s="5"/>
       <c r="PD55" s="5"/>
       <c r="PE55" s="5"/>
-      <c r="PF55" s="5" t="n">
+      <c r="PF55" s="5"/>
+      <c r="PG55" s="5" t="n">
         <v>184.91</v>
       </c>
-      <c r="PG55" s="5"/>
       <c r="PH55" s="5"/>
       <c r="PI55" s="5"/>
+      <c r="PJ55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C56" s="5" t="n">
         <v>226.65</v>
@@ -26838,7 +27010,9 @@
       <c r="BZ56" s="5"/>
       <c r="CA56" s="5"/>
       <c r="CB56" s="5"/>
-      <c r="CC56" s="5"/>
+      <c r="CC56" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="CD56" s="5"/>
       <c r="CE56" s="5"/>
       <c r="CF56" s="5"/>
@@ -27171,44 +27345,45 @@
       <c r="OU56" s="5"/>
       <c r="OV56" s="5"/>
       <c r="OW56" s="5"/>
-      <c r="OX56" s="5" t="n">
+      <c r="OX56" s="5"/>
+      <c r="OY56" s="5" t="n">
         <v>224.77</v>
       </c>
-      <c r="OY56" s="5"/>
       <c r="OZ56" s="5"/>
       <c r="PA56" s="5"/>
       <c r="PB56" s="5"/>
       <c r="PC56" s="5"/>
       <c r="PD56" s="5"/>
       <c r="PE56" s="5"/>
-      <c r="PF56" s="5" t="n">
+      <c r="PF56" s="5"/>
+      <c r="PG56" s="5" t="n">
         <v>226.86</v>
       </c>
-      <c r="PG56" s="5"/>
       <c r="PH56" s="5"/>
       <c r="PI56" s="5"/>
+      <c r="PJ56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="D57" s="5" t="n">
-        <v>318.07</v>
+        <v>432</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>432</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
-      <c r="I57" s="5" t="n">
-        <v>35.71</v>
+      <c r="I57" s="5" t="s">
+        <v>432</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
@@ -27238,7 +27413,7 @@
       <c r="AI57" s="5"/>
       <c r="AJ57" s="5"/>
       <c r="AK57" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL57" s="5"/>
       <c r="AM57" s="5"/>
@@ -27283,7 +27458,9 @@
       <c r="BZ57" s="5"/>
       <c r="CA57" s="5"/>
       <c r="CB57" s="5"/>
-      <c r="CC57" s="5"/>
+      <c r="CC57" s="5" t="n">
+        <v>121.76</v>
+      </c>
       <c r="CD57" s="5"/>
       <c r="CE57" s="5"/>
       <c r="CF57" s="5"/>
@@ -27616,44 +27793,45 @@
       <c r="OU57" s="5"/>
       <c r="OV57" s="5"/>
       <c r="OW57" s="5"/>
-      <c r="OX57" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="OY57" s="5"/>
+      <c r="OX57" s="5"/>
+      <c r="OY57" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ57" s="5"/>
       <c r="PA57" s="5"/>
       <c r="PB57" s="5"/>
       <c r="PC57" s="5"/>
       <c r="PD57" s="5"/>
       <c r="PE57" s="5"/>
-      <c r="PF57" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="PG57" s="5"/>
+      <c r="PF57" s="5"/>
+      <c r="PG57" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH57" s="5"/>
       <c r="PI57" s="5"/>
+      <c r="PJ57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>404.7</v>
+        <v>492</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>432</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>448</v>
+        <v>318.07</v>
       </c>
       <c r="E58" s="5"/>
-      <c r="F58" s="5" t="n">
-        <v>404.8</v>
+      <c r="F58" s="5" t="s">
+        <v>432</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5" t="n">
-        <v>51.4</v>
+        <v>35.71</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
@@ -27682,8 +27860,8 @@
       <c r="AH58" s="5"/>
       <c r="AI58" s="5"/>
       <c r="AJ58" s="5"/>
-      <c r="AK58" s="5" t="n">
-        <v>405.5</v>
+      <c r="AK58" s="5" t="s">
+        <v>432</v>
       </c>
       <c r="AL58" s="5"/>
       <c r="AM58" s="5"/>
@@ -27728,7 +27906,9 @@
       <c r="BZ58" s="5"/>
       <c r="CA58" s="5"/>
       <c r="CB58" s="5"/>
-      <c r="CC58" s="5"/>
+      <c r="CC58" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="CD58" s="5"/>
       <c r="CE58" s="5"/>
       <c r="CF58" s="5"/>
@@ -28061,26 +28241,1371 @@
       <c r="OU58" s="5"/>
       <c r="OV58" s="5"/>
       <c r="OW58" s="5"/>
-      <c r="OX58" s="5" t="n">
-        <v>248.5</v>
-      </c>
-      <c r="OY58" s="5"/>
+      <c r="OX58" s="5"/>
+      <c r="OY58" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OZ58" s="5"/>
       <c r="PA58" s="5"/>
       <c r="PB58" s="5"/>
       <c r="PC58" s="5"/>
       <c r="PD58" s="5"/>
       <c r="PE58" s="5"/>
-      <c r="PF58" s="5" t="n">
-        <v>404.7</v>
-      </c>
-      <c r="PG58" s="5"/>
+      <c r="PF58" s="5"/>
+      <c r="PG58" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PH58" s="5"/>
       <c r="PI58" s="5"/>
+      <c r="PJ58" s="5"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="5"/>
+      <c r="R59" s="5"/>
+      <c r="S59" s="5"/>
+      <c r="T59" s="5"/>
+      <c r="U59" s="5"/>
+      <c r="V59" s="5"/>
+      <c r="W59" s="5"/>
+      <c r="X59" s="5"/>
+      <c r="Y59" s="5"/>
+      <c r="Z59" s="5"/>
+      <c r="AA59" s="5"/>
+      <c r="AB59" s="5"/>
+      <c r="AC59" s="5"/>
+      <c r="AD59" s="5"/>
+      <c r="AE59" s="5"/>
+      <c r="AF59" s="5"/>
+      <c r="AG59" s="5"/>
+      <c r="AH59" s="5"/>
+      <c r="AI59" s="5"/>
+      <c r="AJ59" s="5"/>
+      <c r="AK59" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="AL59" s="5"/>
+      <c r="AM59" s="5"/>
+      <c r="AN59" s="5"/>
+      <c r="AO59" s="5"/>
+      <c r="AP59" s="5"/>
+      <c r="AQ59" s="5"/>
+      <c r="AR59" s="5"/>
+      <c r="AS59" s="5"/>
+      <c r="AT59" s="5"/>
+      <c r="AU59" s="5"/>
+      <c r="AV59" s="5"/>
+      <c r="AW59" s="5"/>
+      <c r="AX59" s="5"/>
+      <c r="AY59" s="5"/>
+      <c r="AZ59" s="5"/>
+      <c r="BA59" s="5"/>
+      <c r="BB59" s="5"/>
+      <c r="BC59" s="5"/>
+      <c r="BD59" s="5"/>
+      <c r="BE59" s="5"/>
+      <c r="BF59" s="5"/>
+      <c r="BG59" s="5"/>
+      <c r="BH59" s="5"/>
+      <c r="BI59" s="5"/>
+      <c r="BJ59" s="5"/>
+      <c r="BK59" s="5"/>
+      <c r="BL59" s="5"/>
+      <c r="BM59" s="5"/>
+      <c r="BN59" s="5"/>
+      <c r="BO59" s="5"/>
+      <c r="BP59" s="5"/>
+      <c r="BQ59" s="5"/>
+      <c r="BR59" s="5"/>
+      <c r="BS59" s="5"/>
+      <c r="BT59" s="5"/>
+      <c r="BU59" s="5"/>
+      <c r="BV59" s="5"/>
+      <c r="BW59" s="5"/>
+      <c r="BX59" s="5"/>
+      <c r="BY59" s="5"/>
+      <c r="BZ59" s="5"/>
+      <c r="CA59" s="5"/>
+      <c r="CB59" s="5"/>
+      <c r="CC59" s="5" t="n">
+        <v>128.82</v>
+      </c>
+      <c r="CD59" s="5"/>
+      <c r="CE59" s="5"/>
+      <c r="CF59" s="5"/>
+      <c r="CG59" s="5"/>
+      <c r="CH59" s="5"/>
+      <c r="CI59" s="5"/>
+      <c r="CJ59" s="5"/>
+      <c r="CK59" s="5"/>
+      <c r="CL59" s="5"/>
+      <c r="CM59" s="5"/>
+      <c r="CN59" s="5"/>
+      <c r="CO59" s="5"/>
+      <c r="CP59" s="5"/>
+      <c r="CQ59" s="5"/>
+      <c r="CR59" s="5"/>
+      <c r="CS59" s="5"/>
+      <c r="CT59" s="5"/>
+      <c r="CU59" s="5"/>
+      <c r="CV59" s="5"/>
+      <c r="CW59" s="5"/>
+      <c r="CX59" s="5"/>
+      <c r="CY59" s="5"/>
+      <c r="CZ59" s="5"/>
+      <c r="DA59" s="5"/>
+      <c r="DB59" s="5"/>
+      <c r="DC59" s="5"/>
+      <c r="DD59" s="5"/>
+      <c r="DE59" s="5"/>
+      <c r="DF59" s="5"/>
+      <c r="DG59" s="5"/>
+      <c r="DH59" s="5"/>
+      <c r="DI59" s="5"/>
+      <c r="DJ59" s="5"/>
+      <c r="DK59" s="5"/>
+      <c r="DL59" s="5"/>
+      <c r="DM59" s="5"/>
+      <c r="DN59" s="5"/>
+      <c r="DO59" s="5"/>
+      <c r="DP59" s="5"/>
+      <c r="DQ59" s="5"/>
+      <c r="DR59" s="5"/>
+      <c r="DS59" s="5"/>
+      <c r="DT59" s="5"/>
+      <c r="DU59" s="5"/>
+      <c r="DV59" s="5"/>
+      <c r="DW59" s="5"/>
+      <c r="DX59" s="5"/>
+      <c r="DY59" s="5"/>
+      <c r="DZ59" s="5"/>
+      <c r="EA59" s="5"/>
+      <c r="EB59" s="5"/>
+      <c r="EC59" s="5"/>
+      <c r="ED59" s="5"/>
+      <c r="EE59" s="5"/>
+      <c r="EF59" s="5"/>
+      <c r="EG59" s="5"/>
+      <c r="EH59" s="5"/>
+      <c r="EI59" s="5"/>
+      <c r="EJ59" s="5"/>
+      <c r="EK59" s="5"/>
+      <c r="EL59" s="5"/>
+      <c r="EM59" s="5"/>
+      <c r="EN59" s="5"/>
+      <c r="EO59" s="5"/>
+      <c r="EP59" s="5"/>
+      <c r="EQ59" s="5"/>
+      <c r="ER59" s="5"/>
+      <c r="ES59" s="5"/>
+      <c r="ET59" s="5"/>
+      <c r="EU59" s="5"/>
+      <c r="EV59" s="5"/>
+      <c r="EW59" s="5"/>
+      <c r="EX59" s="5"/>
+      <c r="EY59" s="5"/>
+      <c r="EZ59" s="5"/>
+      <c r="FA59" s="5"/>
+      <c r="FB59" s="5"/>
+      <c r="FC59" s="5"/>
+      <c r="FD59" s="5"/>
+      <c r="FE59" s="5"/>
+      <c r="FF59" s="5"/>
+      <c r="FG59" s="5"/>
+      <c r="FH59" s="5"/>
+      <c r="FI59" s="5"/>
+      <c r="FJ59" s="5"/>
+      <c r="FK59" s="5"/>
+      <c r="FL59" s="5"/>
+      <c r="FM59" s="5"/>
+      <c r="FN59" s="5"/>
+      <c r="FO59" s="5"/>
+      <c r="FP59" s="5"/>
+      <c r="FQ59" s="5"/>
+      <c r="FR59" s="5"/>
+      <c r="FS59" s="5"/>
+      <c r="FT59" s="5"/>
+      <c r="FU59" s="5"/>
+      <c r="FV59" s="5"/>
+      <c r="FW59" s="5"/>
+      <c r="FX59" s="5"/>
+      <c r="FY59" s="5"/>
+      <c r="FZ59" s="5"/>
+      <c r="GA59" s="5"/>
+      <c r="GB59" s="5"/>
+      <c r="GC59" s="5"/>
+      <c r="GD59" s="5"/>
+      <c r="GE59" s="5"/>
+      <c r="GF59" s="5"/>
+      <c r="GG59" s="5"/>
+      <c r="GH59" s="5"/>
+      <c r="GI59" s="5"/>
+      <c r="GJ59" s="5"/>
+      <c r="GK59" s="5"/>
+      <c r="GL59" s="5"/>
+      <c r="GM59" s="5"/>
+      <c r="GN59" s="5"/>
+      <c r="GO59" s="5"/>
+      <c r="GP59" s="5"/>
+      <c r="GQ59" s="5"/>
+      <c r="GR59" s="5"/>
+      <c r="GS59" s="5"/>
+      <c r="GT59" s="5"/>
+      <c r="GU59" s="5"/>
+      <c r="GV59" s="5"/>
+      <c r="GW59" s="5"/>
+      <c r="GX59" s="5"/>
+      <c r="GY59" s="5"/>
+      <c r="GZ59" s="5"/>
+      <c r="HA59" s="5"/>
+      <c r="HB59" s="5"/>
+      <c r="HC59" s="5"/>
+      <c r="HD59" s="5"/>
+      <c r="HE59" s="5"/>
+      <c r="HF59" s="5"/>
+      <c r="HG59" s="5"/>
+      <c r="HH59" s="5"/>
+      <c r="HI59" s="5"/>
+      <c r="HJ59" s="5"/>
+      <c r="HK59" s="5"/>
+      <c r="HL59" s="5"/>
+      <c r="HM59" s="5"/>
+      <c r="HN59" s="5"/>
+      <c r="HO59" s="5"/>
+      <c r="HP59" s="5"/>
+      <c r="HQ59" s="5"/>
+      <c r="HR59" s="5"/>
+      <c r="HS59" s="5"/>
+      <c r="HT59" s="5"/>
+      <c r="HU59" s="5"/>
+      <c r="HV59" s="5"/>
+      <c r="HW59" s="5"/>
+      <c r="HX59" s="5"/>
+      <c r="HY59" s="5"/>
+      <c r="HZ59" s="5"/>
+      <c r="IA59" s="5"/>
+      <c r="IB59" s="5"/>
+      <c r="IC59" s="5"/>
+      <c r="ID59" s="5"/>
+      <c r="IE59" s="5"/>
+      <c r="IF59" s="5"/>
+      <c r="IG59" s="5"/>
+      <c r="IH59" s="5"/>
+      <c r="II59" s="5"/>
+      <c r="IJ59" s="5"/>
+      <c r="IK59" s="5"/>
+      <c r="IL59" s="5"/>
+      <c r="IM59" s="5"/>
+      <c r="IN59" s="5"/>
+      <c r="IO59" s="5"/>
+      <c r="IP59" s="5"/>
+      <c r="IQ59" s="5"/>
+      <c r="IR59" s="5"/>
+      <c r="IS59" s="5"/>
+      <c r="IT59" s="5"/>
+      <c r="IU59" s="5"/>
+      <c r="IV59" s="5"/>
+      <c r="IW59" s="5"/>
+      <c r="IX59" s="5"/>
+      <c r="IY59" s="5"/>
+      <c r="IZ59" s="5"/>
+      <c r="JA59" s="5"/>
+      <c r="JB59" s="5"/>
+      <c r="JC59" s="5"/>
+      <c r="JD59" s="5"/>
+      <c r="JE59" s="5"/>
+      <c r="JF59" s="5"/>
+      <c r="JG59" s="5"/>
+      <c r="JH59" s="5"/>
+      <c r="JI59" s="5"/>
+      <c r="JJ59" s="5"/>
+      <c r="JK59" s="5"/>
+      <c r="JL59" s="5"/>
+      <c r="JM59" s="5"/>
+      <c r="JN59" s="5"/>
+      <c r="JO59" s="5"/>
+      <c r="JP59" s="5"/>
+      <c r="JQ59" s="5"/>
+      <c r="JR59" s="5"/>
+      <c r="JS59" s="5"/>
+      <c r="JT59" s="5"/>
+      <c r="JU59" s="5"/>
+      <c r="JV59" s="5"/>
+      <c r="JW59" s="5"/>
+      <c r="JX59" s="5"/>
+      <c r="JY59" s="5"/>
+      <c r="JZ59" s="5"/>
+      <c r="KA59" s="5"/>
+      <c r="KB59" s="5"/>
+      <c r="KC59" s="5"/>
+      <c r="KD59" s="5"/>
+      <c r="KE59" s="5"/>
+      <c r="KF59" s="5"/>
+      <c r="KG59" s="5"/>
+      <c r="KH59" s="5"/>
+      <c r="KI59" s="5"/>
+      <c r="KJ59" s="5"/>
+      <c r="KK59" s="5"/>
+      <c r="KL59" s="5"/>
+      <c r="KM59" s="5"/>
+      <c r="KN59" s="5"/>
+      <c r="KO59" s="5"/>
+      <c r="KP59" s="5"/>
+      <c r="KQ59" s="5"/>
+      <c r="KR59" s="5"/>
+      <c r="KS59" s="5"/>
+      <c r="KT59" s="5"/>
+      <c r="KU59" s="5"/>
+      <c r="KV59" s="5"/>
+      <c r="KW59" s="5"/>
+      <c r="KX59" s="5"/>
+      <c r="KY59" s="5"/>
+      <c r="KZ59" s="5"/>
+      <c r="LA59" s="5"/>
+      <c r="LB59" s="5"/>
+      <c r="LC59" s="5"/>
+      <c r="LD59" s="5"/>
+      <c r="LE59" s="5"/>
+      <c r="LF59" s="5"/>
+      <c r="LG59" s="5"/>
+      <c r="LH59" s="5"/>
+      <c r="LI59" s="5"/>
+      <c r="LJ59" s="5"/>
+      <c r="LK59" s="5"/>
+      <c r="LL59" s="5"/>
+      <c r="LM59" s="5"/>
+      <c r="LN59" s="5"/>
+      <c r="LO59" s="5"/>
+      <c r="LP59" s="5"/>
+      <c r="LQ59" s="5"/>
+      <c r="LR59" s="5"/>
+      <c r="LS59" s="5"/>
+      <c r="LT59" s="5"/>
+      <c r="LU59" s="5"/>
+      <c r="LV59" s="5"/>
+      <c r="LW59" s="5"/>
+      <c r="LX59" s="5"/>
+      <c r="LY59" s="5"/>
+      <c r="LZ59" s="5"/>
+      <c r="MA59" s="5"/>
+      <c r="MB59" s="5"/>
+      <c r="MC59" s="5"/>
+      <c r="MD59" s="5"/>
+      <c r="ME59" s="5"/>
+      <c r="MF59" s="5"/>
+      <c r="MG59" s="5"/>
+      <c r="MH59" s="5"/>
+      <c r="MI59" s="5"/>
+      <c r="MJ59" s="5"/>
+      <c r="MK59" s="5"/>
+      <c r="ML59" s="5"/>
+      <c r="MM59" s="5"/>
+      <c r="MN59" s="5"/>
+      <c r="MO59" s="5"/>
+      <c r="MP59" s="5"/>
+      <c r="MQ59" s="5"/>
+      <c r="MR59" s="5"/>
+      <c r="MS59" s="5"/>
+      <c r="MT59" s="5"/>
+      <c r="MU59" s="5"/>
+      <c r="MV59" s="5"/>
+      <c r="MW59" s="5"/>
+      <c r="MX59" s="5"/>
+      <c r="MY59" s="5"/>
+      <c r="MZ59" s="5"/>
+      <c r="NA59" s="5"/>
+      <c r="NB59" s="5"/>
+      <c r="NC59" s="5"/>
+      <c r="ND59" s="5"/>
+      <c r="NE59" s="5"/>
+      <c r="NF59" s="5"/>
+      <c r="NG59" s="5"/>
+      <c r="NH59" s="5"/>
+      <c r="NI59" s="5"/>
+      <c r="NJ59" s="5"/>
+      <c r="NK59" s="5"/>
+      <c r="NL59" s="5"/>
+      <c r="NM59" s="5"/>
+      <c r="NN59" s="5"/>
+      <c r="NO59" s="5"/>
+      <c r="NP59" s="5"/>
+      <c r="NQ59" s="5"/>
+      <c r="NR59" s="5"/>
+      <c r="NS59" s="5"/>
+      <c r="NT59" s="5"/>
+      <c r="NU59" s="5"/>
+      <c r="NV59" s="5"/>
+      <c r="NW59" s="5"/>
+      <c r="NX59" s="5"/>
+      <c r="NY59" s="5"/>
+      <c r="NZ59" s="5"/>
+      <c r="OA59" s="5"/>
+      <c r="OB59" s="5"/>
+      <c r="OC59" s="5"/>
+      <c r="OD59" s="5"/>
+      <c r="OE59" s="5"/>
+      <c r="OF59" s="5"/>
+      <c r="OG59" s="5"/>
+      <c r="OH59" s="5"/>
+      <c r="OI59" s="5"/>
+      <c r="OJ59" s="5"/>
+      <c r="OK59" s="5"/>
+      <c r="OL59" s="5"/>
+      <c r="OM59" s="5"/>
+      <c r="ON59" s="5"/>
+      <c r="OO59" s="5"/>
+      <c r="OP59" s="5"/>
+      <c r="OQ59" s="5"/>
+      <c r="OR59" s="5"/>
+      <c r="OS59" s="5"/>
+      <c r="OT59" s="5"/>
+      <c r="OU59" s="5"/>
+      <c r="OV59" s="5"/>
+      <c r="OW59" s="5"/>
+      <c r="OX59" s="5"/>
+      <c r="OY59" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="OZ59" s="5"/>
+      <c r="PA59" s="5"/>
+      <c r="PB59" s="5"/>
+      <c r="PC59" s="5"/>
+      <c r="PD59" s="5"/>
+      <c r="PE59" s="5"/>
+      <c r="PF59" s="5"/>
+      <c r="PG59" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="PH59" s="5"/>
+      <c r="PI59" s="5"/>
+      <c r="PJ59" s="5"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="5"/>
+      <c r="R60" s="5"/>
+      <c r="S60" s="5"/>
+      <c r="T60" s="5"/>
+      <c r="U60" s="5"/>
+      <c r="V60" s="5"/>
+      <c r="W60" s="5"/>
+      <c r="X60" s="5"/>
+      <c r="Y60" s="5"/>
+      <c r="Z60" s="5"/>
+      <c r="AA60" s="5"/>
+      <c r="AB60" s="5"/>
+      <c r="AC60" s="5"/>
+      <c r="AD60" s="5"/>
+      <c r="AE60" s="5"/>
+      <c r="AF60" s="5"/>
+      <c r="AG60" s="5"/>
+      <c r="AH60" s="5"/>
+      <c r="AI60" s="5"/>
+      <c r="AJ60" s="5"/>
+      <c r="AK60" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="AL60" s="5"/>
+      <c r="AM60" s="5"/>
+      <c r="AN60" s="5"/>
+      <c r="AO60" s="5"/>
+      <c r="AP60" s="5"/>
+      <c r="AQ60" s="5"/>
+      <c r="AR60" s="5"/>
+      <c r="AS60" s="5"/>
+      <c r="AT60" s="5"/>
+      <c r="AU60" s="5"/>
+      <c r="AV60" s="5"/>
+      <c r="AW60" s="5"/>
+      <c r="AX60" s="5"/>
+      <c r="AY60" s="5"/>
+      <c r="AZ60" s="5"/>
+      <c r="BA60" s="5"/>
+      <c r="BB60" s="5"/>
+      <c r="BC60" s="5"/>
+      <c r="BD60" s="5"/>
+      <c r="BE60" s="5"/>
+      <c r="BF60" s="5"/>
+      <c r="BG60" s="5"/>
+      <c r="BH60" s="5"/>
+      <c r="BI60" s="5"/>
+      <c r="BJ60" s="5"/>
+      <c r="BK60" s="5"/>
+      <c r="BL60" s="5"/>
+      <c r="BM60" s="5"/>
+      <c r="BN60" s="5"/>
+      <c r="BO60" s="5"/>
+      <c r="BP60" s="5"/>
+      <c r="BQ60" s="5"/>
+      <c r="BR60" s="5"/>
+      <c r="BS60" s="5"/>
+      <c r="BT60" s="5"/>
+      <c r="BU60" s="5"/>
+      <c r="BV60" s="5"/>
+      <c r="BW60" s="5"/>
+      <c r="BX60" s="5"/>
+      <c r="BY60" s="5"/>
+      <c r="BZ60" s="5"/>
+      <c r="CA60" s="5"/>
+      <c r="CB60" s="5"/>
+      <c r="CC60" s="5" t="n">
+        <v>132.57</v>
+      </c>
+      <c r="CD60" s="5"/>
+      <c r="CE60" s="5"/>
+      <c r="CF60" s="5"/>
+      <c r="CG60" s="5"/>
+      <c r="CH60" s="5"/>
+      <c r="CI60" s="5"/>
+      <c r="CJ60" s="5"/>
+      <c r="CK60" s="5"/>
+      <c r="CL60" s="5"/>
+      <c r="CM60" s="5"/>
+      <c r="CN60" s="5"/>
+      <c r="CO60" s="5"/>
+      <c r="CP60" s="5"/>
+      <c r="CQ60" s="5"/>
+      <c r="CR60" s="5"/>
+      <c r="CS60" s="5"/>
+      <c r="CT60" s="5"/>
+      <c r="CU60" s="5"/>
+      <c r="CV60" s="5"/>
+      <c r="CW60" s="5"/>
+      <c r="CX60" s="5"/>
+      <c r="CY60" s="5"/>
+      <c r="CZ60" s="5"/>
+      <c r="DA60" s="5"/>
+      <c r="DB60" s="5"/>
+      <c r="DC60" s="5"/>
+      <c r="DD60" s="5"/>
+      <c r="DE60" s="5"/>
+      <c r="DF60" s="5"/>
+      <c r="DG60" s="5"/>
+      <c r="DH60" s="5"/>
+      <c r="DI60" s="5"/>
+      <c r="DJ60" s="5"/>
+      <c r="DK60" s="5"/>
+      <c r="DL60" s="5"/>
+      <c r="DM60" s="5"/>
+      <c r="DN60" s="5"/>
+      <c r="DO60" s="5"/>
+      <c r="DP60" s="5"/>
+      <c r="DQ60" s="5"/>
+      <c r="DR60" s="5"/>
+      <c r="DS60" s="5"/>
+      <c r="DT60" s="5"/>
+      <c r="DU60" s="5"/>
+      <c r="DV60" s="5"/>
+      <c r="DW60" s="5"/>
+      <c r="DX60" s="5"/>
+      <c r="DY60" s="5"/>
+      <c r="DZ60" s="5"/>
+      <c r="EA60" s="5"/>
+      <c r="EB60" s="5"/>
+      <c r="EC60" s="5"/>
+      <c r="ED60" s="5"/>
+      <c r="EE60" s="5"/>
+      <c r="EF60" s="5"/>
+      <c r="EG60" s="5"/>
+      <c r="EH60" s="5"/>
+      <c r="EI60" s="5"/>
+      <c r="EJ60" s="5"/>
+      <c r="EK60" s="5"/>
+      <c r="EL60" s="5"/>
+      <c r="EM60" s="5"/>
+      <c r="EN60" s="5"/>
+      <c r="EO60" s="5"/>
+      <c r="EP60" s="5"/>
+      <c r="EQ60" s="5"/>
+      <c r="ER60" s="5"/>
+      <c r="ES60" s="5"/>
+      <c r="ET60" s="5"/>
+      <c r="EU60" s="5"/>
+      <c r="EV60" s="5"/>
+      <c r="EW60" s="5"/>
+      <c r="EX60" s="5"/>
+      <c r="EY60" s="5"/>
+      <c r="EZ60" s="5"/>
+      <c r="FA60" s="5"/>
+      <c r="FB60" s="5"/>
+      <c r="FC60" s="5"/>
+      <c r="FD60" s="5"/>
+      <c r="FE60" s="5"/>
+      <c r="FF60" s="5"/>
+      <c r="FG60" s="5"/>
+      <c r="FH60" s="5"/>
+      <c r="FI60" s="5"/>
+      <c r="FJ60" s="5"/>
+      <c r="FK60" s="5"/>
+      <c r="FL60" s="5"/>
+      <c r="FM60" s="5"/>
+      <c r="FN60" s="5"/>
+      <c r="FO60" s="5"/>
+      <c r="FP60" s="5"/>
+      <c r="FQ60" s="5"/>
+      <c r="FR60" s="5"/>
+      <c r="FS60" s="5"/>
+      <c r="FT60" s="5"/>
+      <c r="FU60" s="5"/>
+      <c r="FV60" s="5"/>
+      <c r="FW60" s="5"/>
+      <c r="FX60" s="5"/>
+      <c r="FY60" s="5"/>
+      <c r="FZ60" s="5"/>
+      <c r="GA60" s="5"/>
+      <c r="GB60" s="5"/>
+      <c r="GC60" s="5"/>
+      <c r="GD60" s="5"/>
+      <c r="GE60" s="5"/>
+      <c r="GF60" s="5"/>
+      <c r="GG60" s="5"/>
+      <c r="GH60" s="5"/>
+      <c r="GI60" s="5"/>
+      <c r="GJ60" s="5"/>
+      <c r="GK60" s="5"/>
+      <c r="GL60" s="5"/>
+      <c r="GM60" s="5"/>
+      <c r="GN60" s="5"/>
+      <c r="GO60" s="5"/>
+      <c r="GP60" s="5"/>
+      <c r="GQ60" s="5"/>
+      <c r="GR60" s="5"/>
+      <c r="GS60" s="5"/>
+      <c r="GT60" s="5"/>
+      <c r="GU60" s="5"/>
+      <c r="GV60" s="5"/>
+      <c r="GW60" s="5"/>
+      <c r="GX60" s="5"/>
+      <c r="GY60" s="5"/>
+      <c r="GZ60" s="5"/>
+      <c r="HA60" s="5"/>
+      <c r="HB60" s="5"/>
+      <c r="HC60" s="5"/>
+      <c r="HD60" s="5"/>
+      <c r="HE60" s="5"/>
+      <c r="HF60" s="5"/>
+      <c r="HG60" s="5"/>
+      <c r="HH60" s="5"/>
+      <c r="HI60" s="5"/>
+      <c r="HJ60" s="5"/>
+      <c r="HK60" s="5"/>
+      <c r="HL60" s="5"/>
+      <c r="HM60" s="5"/>
+      <c r="HN60" s="5"/>
+      <c r="HO60" s="5"/>
+      <c r="HP60" s="5"/>
+      <c r="HQ60" s="5"/>
+      <c r="HR60" s="5"/>
+      <c r="HS60" s="5"/>
+      <c r="HT60" s="5"/>
+      <c r="HU60" s="5"/>
+      <c r="HV60" s="5"/>
+      <c r="HW60" s="5"/>
+      <c r="HX60" s="5"/>
+      <c r="HY60" s="5"/>
+      <c r="HZ60" s="5"/>
+      <c r="IA60" s="5"/>
+      <c r="IB60" s="5"/>
+      <c r="IC60" s="5"/>
+      <c r="ID60" s="5"/>
+      <c r="IE60" s="5"/>
+      <c r="IF60" s="5"/>
+      <c r="IG60" s="5"/>
+      <c r="IH60" s="5"/>
+      <c r="II60" s="5"/>
+      <c r="IJ60" s="5"/>
+      <c r="IK60" s="5"/>
+      <c r="IL60" s="5"/>
+      <c r="IM60" s="5"/>
+      <c r="IN60" s="5"/>
+      <c r="IO60" s="5"/>
+      <c r="IP60" s="5"/>
+      <c r="IQ60" s="5"/>
+      <c r="IR60" s="5"/>
+      <c r="IS60" s="5"/>
+      <c r="IT60" s="5"/>
+      <c r="IU60" s="5"/>
+      <c r="IV60" s="5"/>
+      <c r="IW60" s="5"/>
+      <c r="IX60" s="5"/>
+      <c r="IY60" s="5"/>
+      <c r="IZ60" s="5"/>
+      <c r="JA60" s="5"/>
+      <c r="JB60" s="5"/>
+      <c r="JC60" s="5"/>
+      <c r="JD60" s="5"/>
+      <c r="JE60" s="5"/>
+      <c r="JF60" s="5"/>
+      <c r="JG60" s="5"/>
+      <c r="JH60" s="5"/>
+      <c r="JI60" s="5"/>
+      <c r="JJ60" s="5"/>
+      <c r="JK60" s="5"/>
+      <c r="JL60" s="5"/>
+      <c r="JM60" s="5"/>
+      <c r="JN60" s="5"/>
+      <c r="JO60" s="5"/>
+      <c r="JP60" s="5"/>
+      <c r="JQ60" s="5"/>
+      <c r="JR60" s="5"/>
+      <c r="JS60" s="5"/>
+      <c r="JT60" s="5"/>
+      <c r="JU60" s="5"/>
+      <c r="JV60" s="5"/>
+      <c r="JW60" s="5"/>
+      <c r="JX60" s="5"/>
+      <c r="JY60" s="5"/>
+      <c r="JZ60" s="5"/>
+      <c r="KA60" s="5"/>
+      <c r="KB60" s="5"/>
+      <c r="KC60" s="5"/>
+      <c r="KD60" s="5"/>
+      <c r="KE60" s="5"/>
+      <c r="KF60" s="5"/>
+      <c r="KG60" s="5"/>
+      <c r="KH60" s="5"/>
+      <c r="KI60" s="5"/>
+      <c r="KJ60" s="5"/>
+      <c r="KK60" s="5"/>
+      <c r="KL60" s="5"/>
+      <c r="KM60" s="5"/>
+      <c r="KN60" s="5"/>
+      <c r="KO60" s="5"/>
+      <c r="KP60" s="5"/>
+      <c r="KQ60" s="5"/>
+      <c r="KR60" s="5"/>
+      <c r="KS60" s="5"/>
+      <c r="KT60" s="5"/>
+      <c r="KU60" s="5"/>
+      <c r="KV60" s="5"/>
+      <c r="KW60" s="5"/>
+      <c r="KX60" s="5"/>
+      <c r="KY60" s="5"/>
+      <c r="KZ60" s="5"/>
+      <c r="LA60" s="5"/>
+      <c r="LB60" s="5"/>
+      <c r="LC60" s="5"/>
+      <c r="LD60" s="5"/>
+      <c r="LE60" s="5"/>
+      <c r="LF60" s="5"/>
+      <c r="LG60" s="5"/>
+      <c r="LH60" s="5"/>
+      <c r="LI60" s="5"/>
+      <c r="LJ60" s="5"/>
+      <c r="LK60" s="5"/>
+      <c r="LL60" s="5"/>
+      <c r="LM60" s="5"/>
+      <c r="LN60" s="5"/>
+      <c r="LO60" s="5"/>
+      <c r="LP60" s="5"/>
+      <c r="LQ60" s="5"/>
+      <c r="LR60" s="5"/>
+      <c r="LS60" s="5"/>
+      <c r="LT60" s="5"/>
+      <c r="LU60" s="5"/>
+      <c r="LV60" s="5"/>
+      <c r="LW60" s="5"/>
+      <c r="LX60" s="5"/>
+      <c r="LY60" s="5"/>
+      <c r="LZ60" s="5"/>
+      <c r="MA60" s="5"/>
+      <c r="MB60" s="5"/>
+      <c r="MC60" s="5"/>
+      <c r="MD60" s="5"/>
+      <c r="ME60" s="5"/>
+      <c r="MF60" s="5"/>
+      <c r="MG60" s="5"/>
+      <c r="MH60" s="5"/>
+      <c r="MI60" s="5"/>
+      <c r="MJ60" s="5"/>
+      <c r="MK60" s="5"/>
+      <c r="ML60" s="5"/>
+      <c r="MM60" s="5"/>
+      <c r="MN60" s="5"/>
+      <c r="MO60" s="5"/>
+      <c r="MP60" s="5"/>
+      <c r="MQ60" s="5"/>
+      <c r="MR60" s="5"/>
+      <c r="MS60" s="5"/>
+      <c r="MT60" s="5"/>
+      <c r="MU60" s="5"/>
+      <c r="MV60" s="5"/>
+      <c r="MW60" s="5"/>
+      <c r="MX60" s="5"/>
+      <c r="MY60" s="5"/>
+      <c r="MZ60" s="5"/>
+      <c r="NA60" s="5"/>
+      <c r="NB60" s="5"/>
+      <c r="NC60" s="5"/>
+      <c r="ND60" s="5"/>
+      <c r="NE60" s="5"/>
+      <c r="NF60" s="5"/>
+      <c r="NG60" s="5"/>
+      <c r="NH60" s="5"/>
+      <c r="NI60" s="5"/>
+      <c r="NJ60" s="5"/>
+      <c r="NK60" s="5"/>
+      <c r="NL60" s="5"/>
+      <c r="NM60" s="5"/>
+      <c r="NN60" s="5"/>
+      <c r="NO60" s="5"/>
+      <c r="NP60" s="5"/>
+      <c r="NQ60" s="5"/>
+      <c r="NR60" s="5"/>
+      <c r="NS60" s="5"/>
+      <c r="NT60" s="5"/>
+      <c r="NU60" s="5"/>
+      <c r="NV60" s="5"/>
+      <c r="NW60" s="5"/>
+      <c r="NX60" s="5"/>
+      <c r="NY60" s="5"/>
+      <c r="NZ60" s="5"/>
+      <c r="OA60" s="5"/>
+      <c r="OB60" s="5"/>
+      <c r="OC60" s="5"/>
+      <c r="OD60" s="5"/>
+      <c r="OE60" s="5"/>
+      <c r="OF60" s="5"/>
+      <c r="OG60" s="5"/>
+      <c r="OH60" s="5"/>
+      <c r="OI60" s="5"/>
+      <c r="OJ60" s="5"/>
+      <c r="OK60" s="5"/>
+      <c r="OL60" s="5"/>
+      <c r="OM60" s="5"/>
+      <c r="ON60" s="5"/>
+      <c r="OO60" s="5"/>
+      <c r="OP60" s="5"/>
+      <c r="OQ60" s="5"/>
+      <c r="OR60" s="5"/>
+      <c r="OS60" s="5"/>
+      <c r="OT60" s="5"/>
+      <c r="OU60" s="5"/>
+      <c r="OV60" s="5"/>
+      <c r="OW60" s="5"/>
+      <c r="OX60" s="5"/>
+      <c r="OY60" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="OZ60" s="5"/>
+      <c r="PA60" s="5"/>
+      <c r="PB60" s="5"/>
+      <c r="PC60" s="5"/>
+      <c r="PD60" s="5"/>
+      <c r="PE60" s="5"/>
+      <c r="PF60" s="5"/>
+      <c r="PG60" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="PH60" s="5"/>
+      <c r="PI60" s="5"/>
+      <c r="PJ60" s="5"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>404.7</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>448</v>
+      </c>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5" t="n">
+        <v>404.8</v>
+      </c>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="5"/>
+      <c r="R61" s="5"/>
+      <c r="S61" s="5"/>
+      <c r="T61" s="5"/>
+      <c r="U61" s="5"/>
+      <c r="V61" s="5"/>
+      <c r="W61" s="5"/>
+      <c r="X61" s="5"/>
+      <c r="Y61" s="5"/>
+      <c r="Z61" s="5"/>
+      <c r="AA61" s="5"/>
+      <c r="AB61" s="5"/>
+      <c r="AC61" s="5"/>
+      <c r="AD61" s="5"/>
+      <c r="AE61" s="5"/>
+      <c r="AF61" s="5"/>
+      <c r="AG61" s="5"/>
+      <c r="AH61" s="5"/>
+      <c r="AI61" s="5"/>
+      <c r="AJ61" s="5"/>
+      <c r="AK61" s="5" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="AL61" s="5"/>
+      <c r="AM61" s="5"/>
+      <c r="AN61" s="5"/>
+      <c r="AO61" s="5"/>
+      <c r="AP61" s="5"/>
+      <c r="AQ61" s="5"/>
+      <c r="AR61" s="5"/>
+      <c r="AS61" s="5"/>
+      <c r="AT61" s="5"/>
+      <c r="AU61" s="5"/>
+      <c r="AV61" s="5"/>
+      <c r="AW61" s="5"/>
+      <c r="AX61" s="5"/>
+      <c r="AY61" s="5"/>
+      <c r="AZ61" s="5"/>
+      <c r="BA61" s="5"/>
+      <c r="BB61" s="5"/>
+      <c r="BC61" s="5"/>
+      <c r="BD61" s="5"/>
+      <c r="BE61" s="5"/>
+      <c r="BF61" s="5"/>
+      <c r="BG61" s="5"/>
+      <c r="BH61" s="5"/>
+      <c r="BI61" s="5"/>
+      <c r="BJ61" s="5"/>
+      <c r="BK61" s="5"/>
+      <c r="BL61" s="5"/>
+      <c r="BM61" s="5"/>
+      <c r="BN61" s="5"/>
+      <c r="BO61" s="5"/>
+      <c r="BP61" s="5"/>
+      <c r="BQ61" s="5"/>
+      <c r="BR61" s="5"/>
+      <c r="BS61" s="5"/>
+      <c r="BT61" s="5"/>
+      <c r="BU61" s="5"/>
+      <c r="BV61" s="5"/>
+      <c r="BW61" s="5"/>
+      <c r="BX61" s="5"/>
+      <c r="BY61" s="5"/>
+      <c r="BZ61" s="5"/>
+      <c r="CA61" s="5"/>
+      <c r="CB61" s="5"/>
+      <c r="CC61" s="5" t="n">
+        <v>1082.5</v>
+      </c>
+      <c r="CD61" s="5"/>
+      <c r="CE61" s="5"/>
+      <c r="CF61" s="5"/>
+      <c r="CG61" s="5"/>
+      <c r="CH61" s="5"/>
+      <c r="CI61" s="5"/>
+      <c r="CJ61" s="5"/>
+      <c r="CK61" s="5"/>
+      <c r="CL61" s="5"/>
+      <c r="CM61" s="5"/>
+      <c r="CN61" s="5"/>
+      <c r="CO61" s="5"/>
+      <c r="CP61" s="5"/>
+      <c r="CQ61" s="5"/>
+      <c r="CR61" s="5"/>
+      <c r="CS61" s="5"/>
+      <c r="CT61" s="5"/>
+      <c r="CU61" s="5"/>
+      <c r="CV61" s="5"/>
+      <c r="CW61" s="5"/>
+      <c r="CX61" s="5"/>
+      <c r="CY61" s="5"/>
+      <c r="CZ61" s="5"/>
+      <c r="DA61" s="5"/>
+      <c r="DB61" s="5"/>
+      <c r="DC61" s="5"/>
+      <c r="DD61" s="5"/>
+      <c r="DE61" s="5"/>
+      <c r="DF61" s="5"/>
+      <c r="DG61" s="5"/>
+      <c r="DH61" s="5"/>
+      <c r="DI61" s="5"/>
+      <c r="DJ61" s="5"/>
+      <c r="DK61" s="5"/>
+      <c r="DL61" s="5"/>
+      <c r="DM61" s="5"/>
+      <c r="DN61" s="5"/>
+      <c r="DO61" s="5"/>
+      <c r="DP61" s="5"/>
+      <c r="DQ61" s="5"/>
+      <c r="DR61" s="5"/>
+      <c r="DS61" s="5"/>
+      <c r="DT61" s="5"/>
+      <c r="DU61" s="5"/>
+      <c r="DV61" s="5"/>
+      <c r="DW61" s="5"/>
+      <c r="DX61" s="5"/>
+      <c r="DY61" s="5"/>
+      <c r="DZ61" s="5"/>
+      <c r="EA61" s="5"/>
+      <c r="EB61" s="5"/>
+      <c r="EC61" s="5"/>
+      <c r="ED61" s="5"/>
+      <c r="EE61" s="5"/>
+      <c r="EF61" s="5"/>
+      <c r="EG61" s="5"/>
+      <c r="EH61" s="5"/>
+      <c r="EI61" s="5"/>
+      <c r="EJ61" s="5"/>
+      <c r="EK61" s="5"/>
+      <c r="EL61" s="5"/>
+      <c r="EM61" s="5"/>
+      <c r="EN61" s="5"/>
+      <c r="EO61" s="5"/>
+      <c r="EP61" s="5"/>
+      <c r="EQ61" s="5"/>
+      <c r="ER61" s="5"/>
+      <c r="ES61" s="5"/>
+      <c r="ET61" s="5"/>
+      <c r="EU61" s="5"/>
+      <c r="EV61" s="5"/>
+      <c r="EW61" s="5"/>
+      <c r="EX61" s="5"/>
+      <c r="EY61" s="5"/>
+      <c r="EZ61" s="5"/>
+      <c r="FA61" s="5"/>
+      <c r="FB61" s="5"/>
+      <c r="FC61" s="5"/>
+      <c r="FD61" s="5"/>
+      <c r="FE61" s="5"/>
+      <c r="FF61" s="5"/>
+      <c r="FG61" s="5"/>
+      <c r="FH61" s="5"/>
+      <c r="FI61" s="5"/>
+      <c r="FJ61" s="5"/>
+      <c r="FK61" s="5"/>
+      <c r="FL61" s="5"/>
+      <c r="FM61" s="5"/>
+      <c r="FN61" s="5"/>
+      <c r="FO61" s="5"/>
+      <c r="FP61" s="5"/>
+      <c r="FQ61" s="5"/>
+      <c r="FR61" s="5"/>
+      <c r="FS61" s="5"/>
+      <c r="FT61" s="5"/>
+      <c r="FU61" s="5"/>
+      <c r="FV61" s="5"/>
+      <c r="FW61" s="5"/>
+      <c r="FX61" s="5"/>
+      <c r="FY61" s="5"/>
+      <c r="FZ61" s="5"/>
+      <c r="GA61" s="5"/>
+      <c r="GB61" s="5"/>
+      <c r="GC61" s="5"/>
+      <c r="GD61" s="5"/>
+      <c r="GE61" s="5"/>
+      <c r="GF61" s="5"/>
+      <c r="GG61" s="5"/>
+      <c r="GH61" s="5"/>
+      <c r="GI61" s="5"/>
+      <c r="GJ61" s="5"/>
+      <c r="GK61" s="5"/>
+      <c r="GL61" s="5"/>
+      <c r="GM61" s="5"/>
+      <c r="GN61" s="5"/>
+      <c r="GO61" s="5"/>
+      <c r="GP61" s="5"/>
+      <c r="GQ61" s="5"/>
+      <c r="GR61" s="5"/>
+      <c r="GS61" s="5"/>
+      <c r="GT61" s="5"/>
+      <c r="GU61" s="5"/>
+      <c r="GV61" s="5"/>
+      <c r="GW61" s="5"/>
+      <c r="GX61" s="5"/>
+      <c r="GY61" s="5"/>
+      <c r="GZ61" s="5"/>
+      <c r="HA61" s="5"/>
+      <c r="HB61" s="5"/>
+      <c r="HC61" s="5"/>
+      <c r="HD61" s="5"/>
+      <c r="HE61" s="5"/>
+      <c r="HF61" s="5"/>
+      <c r="HG61" s="5"/>
+      <c r="HH61" s="5"/>
+      <c r="HI61" s="5"/>
+      <c r="HJ61" s="5"/>
+      <c r="HK61" s="5"/>
+      <c r="HL61" s="5"/>
+      <c r="HM61" s="5"/>
+      <c r="HN61" s="5"/>
+      <c r="HO61" s="5"/>
+      <c r="HP61" s="5"/>
+      <c r="HQ61" s="5"/>
+      <c r="HR61" s="5"/>
+      <c r="HS61" s="5"/>
+      <c r="HT61" s="5"/>
+      <c r="HU61" s="5"/>
+      <c r="HV61" s="5"/>
+      <c r="HW61" s="5"/>
+      <c r="HX61" s="5"/>
+      <c r="HY61" s="5"/>
+      <c r="HZ61" s="5"/>
+      <c r="IA61" s="5"/>
+      <c r="IB61" s="5"/>
+      <c r="IC61" s="5"/>
+      <c r="ID61" s="5"/>
+      <c r="IE61" s="5"/>
+      <c r="IF61" s="5"/>
+      <c r="IG61" s="5"/>
+      <c r="IH61" s="5"/>
+      <c r="II61" s="5"/>
+      <c r="IJ61" s="5"/>
+      <c r="IK61" s="5"/>
+      <c r="IL61" s="5"/>
+      <c r="IM61" s="5"/>
+      <c r="IN61" s="5"/>
+      <c r="IO61" s="5"/>
+      <c r="IP61" s="5"/>
+      <c r="IQ61" s="5"/>
+      <c r="IR61" s="5"/>
+      <c r="IS61" s="5"/>
+      <c r="IT61" s="5"/>
+      <c r="IU61" s="5"/>
+      <c r="IV61" s="5"/>
+      <c r="IW61" s="5"/>
+      <c r="IX61" s="5"/>
+      <c r="IY61" s="5"/>
+      <c r="IZ61" s="5"/>
+      <c r="JA61" s="5"/>
+      <c r="JB61" s="5"/>
+      <c r="JC61" s="5"/>
+      <c r="JD61" s="5"/>
+      <c r="JE61" s="5"/>
+      <c r="JF61" s="5"/>
+      <c r="JG61" s="5"/>
+      <c r="JH61" s="5"/>
+      <c r="JI61" s="5"/>
+      <c r="JJ61" s="5"/>
+      <c r="JK61" s="5"/>
+      <c r="JL61" s="5"/>
+      <c r="JM61" s="5"/>
+      <c r="JN61" s="5"/>
+      <c r="JO61" s="5"/>
+      <c r="JP61" s="5"/>
+      <c r="JQ61" s="5"/>
+      <c r="JR61" s="5"/>
+      <c r="JS61" s="5"/>
+      <c r="JT61" s="5"/>
+      <c r="JU61" s="5"/>
+      <c r="JV61" s="5"/>
+      <c r="JW61" s="5"/>
+      <c r="JX61" s="5"/>
+      <c r="JY61" s="5"/>
+      <c r="JZ61" s="5"/>
+      <c r="KA61" s="5"/>
+      <c r="KB61" s="5"/>
+      <c r="KC61" s="5"/>
+      <c r="KD61" s="5"/>
+      <c r="KE61" s="5"/>
+      <c r="KF61" s="5"/>
+      <c r="KG61" s="5"/>
+      <c r="KH61" s="5"/>
+      <c r="KI61" s="5"/>
+      <c r="KJ61" s="5"/>
+      <c r="KK61" s="5"/>
+      <c r="KL61" s="5"/>
+      <c r="KM61" s="5"/>
+      <c r="KN61" s="5"/>
+      <c r="KO61" s="5"/>
+      <c r="KP61" s="5"/>
+      <c r="KQ61" s="5"/>
+      <c r="KR61" s="5"/>
+      <c r="KS61" s="5"/>
+      <c r="KT61" s="5"/>
+      <c r="KU61" s="5"/>
+      <c r="KV61" s="5"/>
+      <c r="KW61" s="5"/>
+      <c r="KX61" s="5"/>
+      <c r="KY61" s="5"/>
+      <c r="KZ61" s="5"/>
+      <c r="LA61" s="5"/>
+      <c r="LB61" s="5"/>
+      <c r="LC61" s="5"/>
+      <c r="LD61" s="5"/>
+      <c r="LE61" s="5"/>
+      <c r="LF61" s="5"/>
+      <c r="LG61" s="5"/>
+      <c r="LH61" s="5"/>
+      <c r="LI61" s="5"/>
+      <c r="LJ61" s="5"/>
+      <c r="LK61" s="5"/>
+      <c r="LL61" s="5"/>
+      <c r="LM61" s="5"/>
+      <c r="LN61" s="5"/>
+      <c r="LO61" s="5"/>
+      <c r="LP61" s="5"/>
+      <c r="LQ61" s="5"/>
+      <c r="LR61" s="5"/>
+      <c r="LS61" s="5"/>
+      <c r="LT61" s="5"/>
+      <c r="LU61" s="5"/>
+      <c r="LV61" s="5"/>
+      <c r="LW61" s="5"/>
+      <c r="LX61" s="5"/>
+      <c r="LY61" s="5"/>
+      <c r="LZ61" s="5"/>
+      <c r="MA61" s="5"/>
+      <c r="MB61" s="5"/>
+      <c r="MC61" s="5"/>
+      <c r="MD61" s="5"/>
+      <c r="ME61" s="5"/>
+      <c r="MF61" s="5"/>
+      <c r="MG61" s="5"/>
+      <c r="MH61" s="5"/>
+      <c r="MI61" s="5"/>
+      <c r="MJ61" s="5"/>
+      <c r="MK61" s="5"/>
+      <c r="ML61" s="5"/>
+      <c r="MM61" s="5"/>
+      <c r="MN61" s="5"/>
+      <c r="MO61" s="5"/>
+      <c r="MP61" s="5"/>
+      <c r="MQ61" s="5"/>
+      <c r="MR61" s="5"/>
+      <c r="MS61" s="5"/>
+      <c r="MT61" s="5"/>
+      <c r="MU61" s="5"/>
+      <c r="MV61" s="5"/>
+      <c r="MW61" s="5"/>
+      <c r="MX61" s="5"/>
+      <c r="MY61" s="5"/>
+      <c r="MZ61" s="5"/>
+      <c r="NA61" s="5"/>
+      <c r="NB61" s="5"/>
+      <c r="NC61" s="5"/>
+      <c r="ND61" s="5"/>
+      <c r="NE61" s="5"/>
+      <c r="NF61" s="5"/>
+      <c r="NG61" s="5"/>
+      <c r="NH61" s="5"/>
+      <c r="NI61" s="5"/>
+      <c r="NJ61" s="5"/>
+      <c r="NK61" s="5"/>
+      <c r="NL61" s="5"/>
+      <c r="NM61" s="5"/>
+      <c r="NN61" s="5"/>
+      <c r="NO61" s="5"/>
+      <c r="NP61" s="5"/>
+      <c r="NQ61" s="5"/>
+      <c r="NR61" s="5"/>
+      <c r="NS61" s="5"/>
+      <c r="NT61" s="5"/>
+      <c r="NU61" s="5"/>
+      <c r="NV61" s="5"/>
+      <c r="NW61" s="5"/>
+      <c r="NX61" s="5"/>
+      <c r="NY61" s="5"/>
+      <c r="NZ61" s="5"/>
+      <c r="OA61" s="5"/>
+      <c r="OB61" s="5"/>
+      <c r="OC61" s="5"/>
+      <c r="OD61" s="5"/>
+      <c r="OE61" s="5"/>
+      <c r="OF61" s="5"/>
+      <c r="OG61" s="5"/>
+      <c r="OH61" s="5"/>
+      <c r="OI61" s="5"/>
+      <c r="OJ61" s="5"/>
+      <c r="OK61" s="5"/>
+      <c r="OL61" s="5"/>
+      <c r="OM61" s="5"/>
+      <c r="ON61" s="5"/>
+      <c r="OO61" s="5"/>
+      <c r="OP61" s="5"/>
+      <c r="OQ61" s="5"/>
+      <c r="OR61" s="5"/>
+      <c r="OS61" s="5"/>
+      <c r="OT61" s="5"/>
+      <c r="OU61" s="5"/>
+      <c r="OV61" s="5"/>
+      <c r="OW61" s="5"/>
+      <c r="OX61" s="5"/>
+      <c r="OY61" s="5" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="OZ61" s="5"/>
+      <c r="PA61" s="5"/>
+      <c r="PB61" s="5"/>
+      <c r="PC61" s="5"/>
+      <c r="PD61" s="5"/>
+      <c r="PE61" s="5"/>
+      <c r="PF61" s="5"/>
+      <c r="PG61" s="5" t="n">
+        <v>404.7</v>
+      </c>
+      <c r="PH61" s="5"/>
+      <c r="PI61" s="5"/>
+      <c r="PJ61" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:PI1"/>
+    <mergeCell ref="A1:PJ1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
+++ b/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="496">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 1: Core Benchmarks</t>
   </si>
@@ -4049,7 +4049,9 @@
       <c r="OU4" s="5"/>
       <c r="OV4" s="5"/>
       <c r="OW4" s="5"/>
-      <c r="OX4" s="5"/>
+      <c r="OX4" s="5" t="n">
+        <v>399.74</v>
+      </c>
       <c r="OY4" s="5" t="n">
         <v>674.99</v>
       </c>
@@ -4497,7 +4499,9 @@
       <c r="OU5" s="5"/>
       <c r="OV5" s="5"/>
       <c r="OW5" s="5"/>
-      <c r="OX5" s="5"/>
+      <c r="OX5" s="5" t="n">
+        <v>137.9</v>
+      </c>
       <c r="OY5" s="5" t="n">
         <v>231.39</v>
       </c>
@@ -4945,7 +4949,9 @@
       <c r="OU6" s="5"/>
       <c r="OV6" s="5"/>
       <c r="OW6" s="5"/>
-      <c r="OX6" s="5"/>
+      <c r="OX6" s="5" t="n">
+        <v>25.25</v>
+      </c>
       <c r="OY6" s="5" t="n">
         <v>38.5</v>
       </c>
@@ -5393,7 +5399,9 @@
       <c r="OU7" s="5"/>
       <c r="OV7" s="5"/>
       <c r="OW7" s="5"/>
-      <c r="OX7" s="5"/>
+      <c r="OX7" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY7" s="5" t="s">
         <v>432</v>
       </c>
@@ -5841,7 +5849,9 @@
       <c r="OU8" s="5"/>
       <c r="OV8" s="5"/>
       <c r="OW8" s="5"/>
-      <c r="OX8" s="5"/>
+      <c r="OX8" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY8" s="5" t="s">
         <v>432</v>
       </c>
@@ -6289,7 +6299,9 @@
       <c r="OU9" s="5"/>
       <c r="OV9" s="5"/>
       <c r="OW9" s="5"/>
-      <c r="OX9" s="5"/>
+      <c r="OX9" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY9" s="5" t="s">
         <v>432</v>
       </c>
@@ -6737,7 +6749,9 @@
       <c r="OU10" s="5"/>
       <c r="OV10" s="5"/>
       <c r="OW10" s="5"/>
-      <c r="OX10" s="5"/>
+      <c r="OX10" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY10" s="5" t="s">
         <v>432</v>
       </c>
@@ -7185,7 +7199,9 @@
       <c r="OU11" s="5"/>
       <c r="OV11" s="5"/>
       <c r="OW11" s="5"/>
-      <c r="OX11" s="5"/>
+      <c r="OX11" s="5" t="n">
+        <v>101.17</v>
+      </c>
       <c r="OY11" s="5" t="n">
         <v>166.28</v>
       </c>
@@ -7633,7 +7649,9 @@
       <c r="OU12" s="5"/>
       <c r="OV12" s="5"/>
       <c r="OW12" s="5"/>
-      <c r="OX12" s="5"/>
+      <c r="OX12" s="5" t="n">
+        <v>90.61</v>
+      </c>
       <c r="OY12" s="5" t="n">
         <v>145.14</v>
       </c>
@@ -8081,7 +8099,9 @@
       <c r="OU13" s="5"/>
       <c r="OV13" s="5"/>
       <c r="OW13" s="5"/>
-      <c r="OX13" s="5"/>
+      <c r="OX13" s="5" t="n">
+        <v>30.91</v>
+      </c>
       <c r="OY13" s="5" t="n">
         <v>47.79</v>
       </c>
@@ -8529,7 +8549,9 @@
       <c r="OU14" s="5"/>
       <c r="OV14" s="5"/>
       <c r="OW14" s="5"/>
-      <c r="OX14" s="5"/>
+      <c r="OX14" s="5" t="n">
+        <v>22.81</v>
+      </c>
       <c r="OY14" s="5" t="n">
         <v>35.16</v>
       </c>
@@ -8977,7 +8999,9 @@
       <c r="OU15" s="5"/>
       <c r="OV15" s="5"/>
       <c r="OW15" s="5"/>
-      <c r="OX15" s="5"/>
+      <c r="OX15" s="5" t="n">
+        <v>3.7</v>
+      </c>
       <c r="OY15" s="5" t="n">
         <v>5.84</v>
       </c>
@@ -9425,7 +9449,9 @@
       <c r="OU16" s="5"/>
       <c r="OV16" s="5"/>
       <c r="OW16" s="5"/>
-      <c r="OX16" s="5"/>
+      <c r="OX16" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY16" s="5" t="s">
         <v>432</v>
       </c>
@@ -9873,7 +9899,9 @@
       <c r="OU17" s="5"/>
       <c r="OV17" s="5"/>
       <c r="OW17" s="5"/>
-      <c r="OX17" s="5"/>
+      <c r="OX17" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY17" s="5" t="s">
         <v>432</v>
       </c>
@@ -10321,7 +10349,9 @@
       <c r="OU18" s="5"/>
       <c r="OV18" s="5"/>
       <c r="OW18" s="5"/>
-      <c r="OX18" s="5"/>
+      <c r="OX18" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY18" s="5" t="s">
         <v>432</v>
       </c>
@@ -10769,7 +10799,9 @@
       <c r="OU19" s="5"/>
       <c r="OV19" s="5"/>
       <c r="OW19" s="5"/>
-      <c r="OX19" s="5"/>
+      <c r="OX19" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY19" s="5" t="s">
         <v>432</v>
       </c>
@@ -11217,7 +11249,9 @@
       <c r="OU20" s="5"/>
       <c r="OV20" s="5"/>
       <c r="OW20" s="5"/>
-      <c r="OX20" s="5"/>
+      <c r="OX20" s="5" t="n">
+        <v>126.95</v>
+      </c>
       <c r="OY20" s="5" t="n">
         <v>261.28</v>
       </c>
@@ -11665,7 +11699,9 @@
       <c r="OU21" s="5"/>
       <c r="OV21" s="5"/>
       <c r="OW21" s="5"/>
-      <c r="OX21" s="5"/>
+      <c r="OX21" s="5" t="n">
+        <v>97.5</v>
+      </c>
       <c r="OY21" s="5" t="n">
         <v>162.79</v>
       </c>
@@ -12113,7 +12149,9 @@
       <c r="OU22" s="5"/>
       <c r="OV22" s="5"/>
       <c r="OW22" s="5"/>
-      <c r="OX22" s="5"/>
+      <c r="OX22" s="5" t="n">
+        <v>14.88</v>
+      </c>
       <c r="OY22" s="5" t="n">
         <v>25.13</v>
       </c>
@@ -12561,7 +12599,9 @@
       <c r="OU23" s="5"/>
       <c r="OV23" s="5"/>
       <c r="OW23" s="5"/>
-      <c r="OX23" s="5"/>
+      <c r="OX23" s="5" t="n">
+        <v>29.95</v>
+      </c>
       <c r="OY23" s="5" t="n">
         <v>45.7</v>
       </c>
@@ -13009,7 +13049,9 @@
       <c r="OU24" s="5"/>
       <c r="OV24" s="5"/>
       <c r="OW24" s="5"/>
-      <c r="OX24" s="5"/>
+      <c r="OX24" s="5" t="n">
+        <v>1536.79</v>
+      </c>
       <c r="OY24" s="5" t="n">
         <v>2672.97</v>
       </c>
@@ -13457,7 +13499,9 @@
       <c r="OU25" s="5"/>
       <c r="OV25" s="5"/>
       <c r="OW25" s="5"/>
-      <c r="OX25" s="5"/>
+      <c r="OX25" s="5" t="n">
+        <v>489.67</v>
+      </c>
       <c r="OY25" s="5" t="n">
         <v>834.68</v>
       </c>
@@ -13905,7 +13949,9 @@
       <c r="OU26" s="5"/>
       <c r="OV26" s="5"/>
       <c r="OW26" s="5"/>
-      <c r="OX26" s="5"/>
+      <c r="OX26" s="5" t="n">
+        <v>376.19</v>
+      </c>
       <c r="OY26" s="5" t="n">
         <v>621.48</v>
       </c>
@@ -14353,7 +14399,9 @@
       <c r="OU27" s="5"/>
       <c r="OV27" s="5"/>
       <c r="OW27" s="5"/>
-      <c r="OX27" s="5"/>
+      <c r="OX27" s="5" t="n">
+        <v>1.96</v>
+      </c>
       <c r="OY27" s="5" t="n">
         <v>3.42</v>
       </c>
@@ -14801,7 +14849,9 @@
       <c r="OU28" s="5"/>
       <c r="OV28" s="5"/>
       <c r="OW28" s="5"/>
-      <c r="OX28" s="5"/>
+      <c r="OX28" s="5" t="n">
+        <v>2.62</v>
+      </c>
       <c r="OY28" s="5" t="n">
         <v>4.79</v>
       </c>
@@ -15249,7 +15299,9 @@
       <c r="OU29" s="5"/>
       <c r="OV29" s="5"/>
       <c r="OW29" s="5"/>
-      <c r="OX29" s="5"/>
+      <c r="OX29" s="5" t="n">
+        <v>3.93</v>
+      </c>
       <c r="OY29" s="5" t="n">
         <v>7.98</v>
       </c>
@@ -15697,7 +15749,9 @@
       <c r="OU30" s="5"/>
       <c r="OV30" s="5"/>
       <c r="OW30" s="5"/>
-      <c r="OX30" s="5"/>
+      <c r="OX30" s="5" t="n">
+        <v>1.51</v>
+      </c>
       <c r="OY30" s="5" t="n">
         <v>1.6</v>
       </c>
@@ -16145,7 +16199,9 @@
       <c r="OU31" s="5"/>
       <c r="OV31" s="5"/>
       <c r="OW31" s="5"/>
-      <c r="OX31" s="5"/>
+      <c r="OX31" s="5" t="n">
+        <v>0.3</v>
+      </c>
       <c r="OY31" s="5" t="n">
         <v>0.1</v>
       </c>
@@ -16593,7 +16649,9 @@
       <c r="OU32" s="5"/>
       <c r="OV32" s="5"/>
       <c r="OW32" s="5"/>
-      <c r="OX32" s="5"/>
+      <c r="OX32" s="5" t="n">
+        <v>285.71</v>
+      </c>
       <c r="OY32" s="5" t="n">
         <v>695.65</v>
       </c>
@@ -17041,7 +17099,9 @@
       <c r="OU33" s="5"/>
       <c r="OV33" s="5"/>
       <c r="OW33" s="5"/>
-      <c r="OX33" s="5"/>
+      <c r="OX33" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY33" s="5" t="s">
         <v>432</v>
       </c>
@@ -17489,7 +17549,9 @@
       <c r="OU34" s="5"/>
       <c r="OV34" s="5"/>
       <c r="OW34" s="5"/>
-      <c r="OX34" s="5"/>
+      <c r="OX34" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY34" s="5" t="s">
         <v>432</v>
       </c>
@@ -17937,7 +17999,9 @@
       <c r="OU35" s="5"/>
       <c r="OV35" s="5"/>
       <c r="OW35" s="5"/>
-      <c r="OX35" s="5"/>
+      <c r="OX35" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY35" s="5" t="s">
         <v>432</v>
       </c>
@@ -18385,7 +18449,9 @@
       <c r="OU36" s="5"/>
       <c r="OV36" s="5"/>
       <c r="OW36" s="5"/>
-      <c r="OX36" s="5"/>
+      <c r="OX36" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY36" s="5" t="s">
         <v>432</v>
       </c>
@@ -18833,7 +18899,9 @@
       <c r="OU37" s="5"/>
       <c r="OV37" s="5"/>
       <c r="OW37" s="5"/>
-      <c r="OX37" s="5"/>
+      <c r="OX37" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY37" s="5" t="s">
         <v>432</v>
       </c>
@@ -19281,7 +19349,9 @@
       <c r="OU38" s="5"/>
       <c r="OV38" s="5"/>
       <c r="OW38" s="5"/>
-      <c r="OX38" s="5"/>
+      <c r="OX38" s="5" t="n">
+        <v>271.77</v>
+      </c>
       <c r="OY38" s="5" t="n">
         <v>235.85</v>
       </c>
@@ -19729,7 +19799,9 @@
       <c r="OU39" s="5"/>
       <c r="OV39" s="5"/>
       <c r="OW39" s="5"/>
-      <c r="OX39" s="5"/>
+      <c r="OX39" s="5" t="n">
+        <v>881.83</v>
+      </c>
       <c r="OY39" s="5" t="n">
         <v>2969.01</v>
       </c>
@@ -20177,7 +20249,9 @@
       <c r="OU40" s="5"/>
       <c r="OV40" s="5"/>
       <c r="OW40" s="5"/>
-      <c r="OX40" s="5"/>
+      <c r="OX40" s="5" t="n">
+        <v>4.05</v>
+      </c>
       <c r="OY40" s="5" t="n">
         <v>12.59</v>
       </c>
@@ -20625,7 +20699,9 @@
       <c r="OU41" s="5"/>
       <c r="OV41" s="5"/>
       <c r="OW41" s="5"/>
-      <c r="OX41" s="5"/>
+      <c r="OX41" s="5" t="n">
+        <v>8.32</v>
+      </c>
       <c r="OY41" s="5" t="n">
         <v>30.94</v>
       </c>
@@ -21073,7 +21149,9 @@
       <c r="OU42" s="5"/>
       <c r="OV42" s="5"/>
       <c r="OW42" s="5"/>
-      <c r="OX42" s="5"/>
+      <c r="OX42" s="5" t="n">
+        <v>78.28</v>
+      </c>
       <c r="OY42" s="5" t="n">
         <v>117.15</v>
       </c>
@@ -21521,7 +21599,9 @@
       <c r="OU43" s="5"/>
       <c r="OV43" s="5"/>
       <c r="OW43" s="5"/>
-      <c r="OX43" s="5"/>
+      <c r="OX43" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY43" s="5" t="s">
         <v>432</v>
       </c>
@@ -21969,7 +22049,9 @@
       <c r="OU44" s="5"/>
       <c r="OV44" s="5"/>
       <c r="OW44" s="5"/>
-      <c r="OX44" s="5"/>
+      <c r="OX44" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY44" s="5" t="s">
         <v>432</v>
       </c>
@@ -22417,7 +22499,9 @@
       <c r="OU45" s="5"/>
       <c r="OV45" s="5"/>
       <c r="OW45" s="5"/>
-      <c r="OX45" s="5"/>
+      <c r="OX45" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY45" s="5" t="s">
         <v>432</v>
       </c>
@@ -22865,7 +22949,9 @@
       <c r="OU46" s="5"/>
       <c r="OV46" s="5"/>
       <c r="OW46" s="5"/>
-      <c r="OX46" s="5"/>
+      <c r="OX46" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY46" s="5" t="s">
         <v>432</v>
       </c>
@@ -23313,7 +23399,9 @@
       <c r="OU47" s="5"/>
       <c r="OV47" s="5"/>
       <c r="OW47" s="5"/>
-      <c r="OX47" s="5"/>
+      <c r="OX47" s="5" t="n">
+        <v>118.61</v>
+      </c>
       <c r="OY47" s="5" t="n">
         <v>357.64</v>
       </c>
@@ -23761,7 +23849,9 @@
       <c r="OU48" s="5"/>
       <c r="OV48" s="5"/>
       <c r="OW48" s="5"/>
-      <c r="OX48" s="5"/>
+      <c r="OX48" s="5" t="n">
+        <v>122.81</v>
+      </c>
       <c r="OY48" s="5" t="n">
         <v>376.35</v>
       </c>
@@ -24209,7 +24299,9 @@
       <c r="OU49" s="5"/>
       <c r="OV49" s="5"/>
       <c r="OW49" s="5"/>
-      <c r="OX49" s="5"/>
+      <c r="OX49" s="5" t="n">
+        <v>8.143</v>
+      </c>
       <c r="OY49" s="5" t="n">
         <v>2.657</v>
       </c>
@@ -24657,7 +24749,9 @@
       <c r="OU50" s="5"/>
       <c r="OV50" s="5"/>
       <c r="OW50" s="5"/>
-      <c r="OX50" s="5"/>
+      <c r="OX50" s="5" t="n">
+        <v>23.38</v>
+      </c>
       <c r="OY50" s="5" t="n">
         <v>10.01</v>
       </c>
@@ -25105,7 +25199,9 @@
       <c r="OU51" s="5"/>
       <c r="OV51" s="5"/>
       <c r="OW51" s="5"/>
-      <c r="OX51" s="5"/>
+      <c r="OX51" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY51" s="5" t="n">
         <v>9.73</v>
       </c>
@@ -25553,7 +25649,9 @@
       <c r="OU52" s="5"/>
       <c r="OV52" s="5"/>
       <c r="OW52" s="5"/>
-      <c r="OX52" s="5"/>
+      <c r="OX52" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY52" s="5" t="n">
         <v>0.28</v>
       </c>
@@ -26001,7 +26099,9 @@
       <c r="OU53" s="5"/>
       <c r="OV53" s="5"/>
       <c r="OW53" s="5"/>
-      <c r="OX53" s="5"/>
+      <c r="OX53" s="5" t="n">
+        <v>86.36</v>
+      </c>
       <c r="OY53" s="5" t="n">
         <v>72.73</v>
       </c>
@@ -26449,7 +26549,9 @@
       <c r="OU54" s="5"/>
       <c r="OV54" s="5"/>
       <c r="OW54" s="5"/>
-      <c r="OX54" s="5"/>
+      <c r="OX54" s="5" t="n">
+        <v>134.92</v>
+      </c>
       <c r="OY54" s="5" t="n">
         <v>119.52</v>
       </c>
@@ -26897,7 +26999,9 @@
       <c r="OU55" s="5"/>
       <c r="OV55" s="5"/>
       <c r="OW55" s="5"/>
-      <c r="OX55" s="5"/>
+      <c r="OX55" s="5" t="n">
+        <v>185.46</v>
+      </c>
       <c r="OY55" s="5" t="n">
         <v>175.93</v>
       </c>
@@ -27345,7 +27449,9 @@
       <c r="OU56" s="5"/>
       <c r="OV56" s="5"/>
       <c r="OW56" s="5"/>
-      <c r="OX56" s="5"/>
+      <c r="OX56" s="5" t="n">
+        <v>226.86</v>
+      </c>
       <c r="OY56" s="5" t="n">
         <v>224.77</v>
       </c>
@@ -27793,7 +27899,9 @@
       <c r="OU57" s="5"/>
       <c r="OV57" s="5"/>
       <c r="OW57" s="5"/>
-      <c r="OX57" s="5"/>
+      <c r="OX57" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY57" s="5" t="s">
         <v>432</v>
       </c>
@@ -28241,7 +28349,9 @@
       <c r="OU58" s="5"/>
       <c r="OV58" s="5"/>
       <c r="OW58" s="5"/>
-      <c r="OX58" s="5"/>
+      <c r="OX58" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY58" s="5" t="s">
         <v>432</v>
       </c>
@@ -28689,7 +28799,9 @@
       <c r="OU59" s="5"/>
       <c r="OV59" s="5"/>
       <c r="OW59" s="5"/>
-      <c r="OX59" s="5"/>
+      <c r="OX59" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY59" s="5" t="s">
         <v>432</v>
       </c>
@@ -29137,7 +29249,9 @@
       <c r="OU60" s="5"/>
       <c r="OV60" s="5"/>
       <c r="OW60" s="5"/>
-      <c r="OX60" s="5"/>
+      <c r="OX60" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="OY60" s="5" t="s">
         <v>432</v>
       </c>
@@ -29585,7 +29699,9 @@
       <c r="OU61" s="5"/>
       <c r="OV61" s="5"/>
       <c r="OW61" s="5"/>
-      <c r="OX61" s="5"/>
+      <c r="OX61" s="5" t="n">
+        <v>404.7</v>
+      </c>
       <c r="OY61" s="5" t="n">
         <v>248.5</v>
       </c>

--- a/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
+++ b/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="496">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 1: Core Benchmarks</t>
   </si>
@@ -4061,7 +4061,9 @@
       <c r="PC4" s="5"/>
       <c r="PD4" s="5"/>
       <c r="PE4" s="5"/>
-      <c r="PF4" s="5"/>
+      <c r="PF4" s="5" t="n">
+        <v>399.62</v>
+      </c>
       <c r="PG4" s="5" t="n">
         <v>399.74</v>
       </c>
@@ -4511,7 +4513,9 @@
       <c r="PC5" s="5"/>
       <c r="PD5" s="5"/>
       <c r="PE5" s="5"/>
-      <c r="PF5" s="5"/>
+      <c r="PF5" s="5" t="n">
+        <v>137.9</v>
+      </c>
       <c r="PG5" s="5" t="n">
         <v>137.9</v>
       </c>
@@ -4961,7 +4965,9 @@
       <c r="PC6" s="5"/>
       <c r="PD6" s="5"/>
       <c r="PE6" s="5"/>
-      <c r="PF6" s="5"/>
+      <c r="PF6" s="5" t="n">
+        <v>25.28</v>
+      </c>
       <c r="PG6" s="5" t="n">
         <v>25.24</v>
       </c>
@@ -5411,7 +5417,9 @@
       <c r="PC7" s="5"/>
       <c r="PD7" s="5"/>
       <c r="PE7" s="5"/>
-      <c r="PF7" s="5"/>
+      <c r="PF7" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG7" s="5" t="s">
         <v>432</v>
       </c>
@@ -5861,7 +5869,9 @@
       <c r="PC8" s="5"/>
       <c r="PD8" s="5"/>
       <c r="PE8" s="5"/>
-      <c r="PF8" s="5"/>
+      <c r="PF8" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG8" s="5" t="s">
         <v>432</v>
       </c>
@@ -6311,7 +6321,9 @@
       <c r="PC9" s="5"/>
       <c r="PD9" s="5"/>
       <c r="PE9" s="5"/>
-      <c r="PF9" s="5"/>
+      <c r="PF9" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG9" s="5" t="s">
         <v>432</v>
       </c>
@@ -6761,7 +6773,9 @@
       <c r="PC10" s="5"/>
       <c r="PD10" s="5"/>
       <c r="PE10" s="5"/>
-      <c r="PF10" s="5"/>
+      <c r="PF10" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG10" s="5" t="s">
         <v>432</v>
       </c>
@@ -7211,7 +7225,9 @@
       <c r="PC11" s="5"/>
       <c r="PD11" s="5"/>
       <c r="PE11" s="5"/>
-      <c r="PF11" s="5"/>
+      <c r="PF11" s="5" t="n">
+        <v>101.17</v>
+      </c>
       <c r="PG11" s="5" t="n">
         <v>101.17</v>
       </c>
@@ -7661,7 +7677,9 @@
       <c r="PC12" s="5"/>
       <c r="PD12" s="5"/>
       <c r="PE12" s="5"/>
-      <c r="PF12" s="5"/>
+      <c r="PF12" s="5" t="n">
+        <v>90.61</v>
+      </c>
       <c r="PG12" s="5" t="n">
         <v>90.65</v>
       </c>
@@ -8111,7 +8129,9 @@
       <c r="PC13" s="5"/>
       <c r="PD13" s="5"/>
       <c r="PE13" s="5"/>
-      <c r="PF13" s="5"/>
+      <c r="PF13" s="5" t="n">
+        <v>30.91</v>
+      </c>
       <c r="PG13" s="5" t="n">
         <v>30.91</v>
       </c>
@@ -8561,7 +8581,9 @@
       <c r="PC14" s="5"/>
       <c r="PD14" s="5"/>
       <c r="PE14" s="5"/>
-      <c r="PF14" s="5"/>
+      <c r="PF14" s="5" t="n">
+        <v>22.81</v>
+      </c>
       <c r="PG14" s="5" t="n">
         <v>22.81</v>
       </c>
@@ -9011,7 +9033,9 @@
       <c r="PC15" s="5"/>
       <c r="PD15" s="5"/>
       <c r="PE15" s="5"/>
-      <c r="PF15" s="5"/>
+      <c r="PF15" s="5" t="n">
+        <v>3.7</v>
+      </c>
       <c r="PG15" s="5" t="n">
         <v>3.7</v>
       </c>
@@ -9461,7 +9485,9 @@
       <c r="PC16" s="5"/>
       <c r="PD16" s="5"/>
       <c r="PE16" s="5"/>
-      <c r="PF16" s="5"/>
+      <c r="PF16" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG16" s="5" t="s">
         <v>432</v>
       </c>
@@ -9911,7 +9937,9 @@
       <c r="PC17" s="5"/>
       <c r="PD17" s="5"/>
       <c r="PE17" s="5"/>
-      <c r="PF17" s="5"/>
+      <c r="PF17" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG17" s="5" t="s">
         <v>432</v>
       </c>
@@ -10361,7 +10389,9 @@
       <c r="PC18" s="5"/>
       <c r="PD18" s="5"/>
       <c r="PE18" s="5"/>
-      <c r="PF18" s="5"/>
+      <c r="PF18" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG18" s="5" t="s">
         <v>432</v>
       </c>
@@ -10811,7 +10841,9 @@
       <c r="PC19" s="5"/>
       <c r="PD19" s="5"/>
       <c r="PE19" s="5"/>
-      <c r="PF19" s="5"/>
+      <c r="PF19" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG19" s="5" t="s">
         <v>432</v>
       </c>
@@ -11261,7 +11293,9 @@
       <c r="PC20" s="5"/>
       <c r="PD20" s="5"/>
       <c r="PE20" s="5"/>
-      <c r="PF20" s="5"/>
+      <c r="PF20" s="5" t="n">
+        <v>126.95</v>
+      </c>
       <c r="PG20" s="5" t="n">
         <v>126.95</v>
       </c>
@@ -11711,7 +11745,9 @@
       <c r="PC21" s="5"/>
       <c r="PD21" s="5"/>
       <c r="PE21" s="5"/>
-      <c r="PF21" s="5"/>
+      <c r="PF21" s="5" t="n">
+        <v>97.5</v>
+      </c>
       <c r="PG21" s="5" t="n">
         <v>97.5</v>
       </c>
@@ -12161,7 +12197,9 @@
       <c r="PC22" s="5"/>
       <c r="PD22" s="5"/>
       <c r="PE22" s="5"/>
-      <c r="PF22" s="5"/>
+      <c r="PF22" s="5" t="n">
+        <v>14.87</v>
+      </c>
       <c r="PG22" s="5" t="n">
         <v>14.87</v>
       </c>
@@ -12611,7 +12649,9 @@
       <c r="PC23" s="5"/>
       <c r="PD23" s="5"/>
       <c r="PE23" s="5"/>
-      <c r="PF23" s="5"/>
+      <c r="PF23" s="5" t="n">
+        <v>29.95</v>
+      </c>
       <c r="PG23" s="5" t="n">
         <v>29.95</v>
       </c>
@@ -13061,7 +13101,9 @@
       <c r="PC24" s="5"/>
       <c r="PD24" s="5"/>
       <c r="PE24" s="5"/>
-      <c r="PF24" s="5"/>
+      <c r="PF24" s="5" t="n">
+        <v>1536.79</v>
+      </c>
       <c r="PG24" s="5" t="n">
         <v>1536.79</v>
       </c>
@@ -13511,7 +13553,9 @@
       <c r="PC25" s="5"/>
       <c r="PD25" s="5"/>
       <c r="PE25" s="5"/>
-      <c r="PF25" s="5"/>
+      <c r="PF25" s="5" t="n">
+        <v>489.67</v>
+      </c>
       <c r="PG25" s="5" t="n">
         <v>489.67</v>
       </c>
@@ -13961,7 +14005,9 @@
       <c r="PC26" s="5"/>
       <c r="PD26" s="5"/>
       <c r="PE26" s="5"/>
-      <c r="PF26" s="5"/>
+      <c r="PF26" s="5" t="n">
+        <v>376.19</v>
+      </c>
       <c r="PG26" s="5" t="n">
         <v>376.19</v>
       </c>
@@ -14411,7 +14457,9 @@
       <c r="PC27" s="5"/>
       <c r="PD27" s="5"/>
       <c r="PE27" s="5"/>
-      <c r="PF27" s="5"/>
+      <c r="PF27" s="5" t="n">
+        <v>1.96</v>
+      </c>
       <c r="PG27" s="5" t="n">
         <v>1.96</v>
       </c>
@@ -14861,7 +14909,9 @@
       <c r="PC28" s="5"/>
       <c r="PD28" s="5"/>
       <c r="PE28" s="5"/>
-      <c r="PF28" s="5"/>
+      <c r="PF28" s="5" t="n">
+        <v>2.62</v>
+      </c>
       <c r="PG28" s="5" t="n">
         <v>2.62</v>
       </c>
@@ -15311,7 +15361,9 @@
       <c r="PC29" s="5"/>
       <c r="PD29" s="5"/>
       <c r="PE29" s="5"/>
-      <c r="PF29" s="5"/>
+      <c r="PF29" s="5" t="n">
+        <v>3.93</v>
+      </c>
       <c r="PG29" s="5" t="n">
         <v>3.93</v>
       </c>
@@ -15761,7 +15813,9 @@
       <c r="PC30" s="5"/>
       <c r="PD30" s="5"/>
       <c r="PE30" s="5"/>
-      <c r="PF30" s="5"/>
+      <c r="PF30" s="5" t="n">
+        <v>1.51</v>
+      </c>
       <c r="PG30" s="5" t="n">
         <v>1.51</v>
       </c>
@@ -16211,7 +16265,9 @@
       <c r="PC31" s="5"/>
       <c r="PD31" s="5"/>
       <c r="PE31" s="5"/>
-      <c r="PF31" s="5"/>
+      <c r="PF31" s="5" t="n">
+        <v>0.32</v>
+      </c>
       <c r="PG31" s="5" t="n">
         <v>0.3</v>
       </c>
@@ -16661,7 +16717,9 @@
       <c r="PC32" s="5"/>
       <c r="PD32" s="5"/>
       <c r="PE32" s="5"/>
-      <c r="PF32" s="5"/>
+      <c r="PF32" s="5" t="n">
+        <v>285.71</v>
+      </c>
       <c r="PG32" s="5" t="n">
         <v>285.71</v>
       </c>
@@ -17111,7 +17169,9 @@
       <c r="PC33" s="5"/>
       <c r="PD33" s="5"/>
       <c r="PE33" s="5"/>
-      <c r="PF33" s="5"/>
+      <c r="PF33" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG33" s="5" t="s">
         <v>432</v>
       </c>
@@ -17561,7 +17621,9 @@
       <c r="PC34" s="5"/>
       <c r="PD34" s="5"/>
       <c r="PE34" s="5"/>
-      <c r="PF34" s="5"/>
+      <c r="PF34" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG34" s="5" t="s">
         <v>432</v>
       </c>
@@ -18011,7 +18073,9 @@
       <c r="PC35" s="5"/>
       <c r="PD35" s="5"/>
       <c r="PE35" s="5"/>
-      <c r="PF35" s="5"/>
+      <c r="PF35" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG35" s="5" t="s">
         <v>432</v>
       </c>
@@ -18461,7 +18525,9 @@
       <c r="PC36" s="5"/>
       <c r="PD36" s="5"/>
       <c r="PE36" s="5"/>
-      <c r="PF36" s="5"/>
+      <c r="PF36" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG36" s="5" t="s">
         <v>432</v>
       </c>
@@ -18911,7 +18977,9 @@
       <c r="PC37" s="5"/>
       <c r="PD37" s="5"/>
       <c r="PE37" s="5"/>
-      <c r="PF37" s="5"/>
+      <c r="PF37" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG37" s="5" t="s">
         <v>432</v>
       </c>
@@ -19361,7 +19429,9 @@
       <c r="PC38" s="5"/>
       <c r="PD38" s="5"/>
       <c r="PE38" s="5"/>
-      <c r="PF38" s="5"/>
+      <c r="PF38" s="5" t="n">
+        <v>217.77</v>
+      </c>
       <c r="PG38" s="5" t="n">
         <v>217.77</v>
       </c>
@@ -19811,7 +19881,9 @@
       <c r="PC39" s="5"/>
       <c r="PD39" s="5"/>
       <c r="PE39" s="5"/>
-      <c r="PF39" s="5"/>
+      <c r="PF39" s="5" t="n">
+        <v>881.83</v>
+      </c>
       <c r="PG39" s="5" t="n">
         <v>881.32</v>
       </c>
@@ -20261,7 +20333,9 @@
       <c r="PC40" s="5"/>
       <c r="PD40" s="5"/>
       <c r="PE40" s="5"/>
-      <c r="PF40" s="5"/>
+      <c r="PF40" s="5" t="n">
+        <v>4.05</v>
+      </c>
       <c r="PG40" s="5" t="n">
         <v>4.05</v>
       </c>
@@ -20711,7 +20785,9 @@
       <c r="PC41" s="5"/>
       <c r="PD41" s="5"/>
       <c r="PE41" s="5"/>
-      <c r="PF41" s="5"/>
+      <c r="PF41" s="5" t="n">
+        <v>8.32</v>
+      </c>
       <c r="PG41" s="5" t="n">
         <v>8.32</v>
       </c>
@@ -21161,7 +21237,9 @@
       <c r="PC42" s="5"/>
       <c r="PD42" s="5"/>
       <c r="PE42" s="5"/>
-      <c r="PF42" s="5"/>
+      <c r="PF42" s="5" t="n">
+        <v>78.25</v>
+      </c>
       <c r="PG42" s="5" t="n">
         <v>78.22</v>
       </c>
@@ -21611,7 +21689,9 @@
       <c r="PC43" s="5"/>
       <c r="PD43" s="5"/>
       <c r="PE43" s="5"/>
-      <c r="PF43" s="5"/>
+      <c r="PF43" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG43" s="5" t="s">
         <v>432</v>
       </c>
@@ -22061,7 +22141,9 @@
       <c r="PC44" s="5"/>
       <c r="PD44" s="5"/>
       <c r="PE44" s="5"/>
-      <c r="PF44" s="5"/>
+      <c r="PF44" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG44" s="5" t="s">
         <v>432</v>
       </c>
@@ -22511,7 +22593,9 @@
       <c r="PC45" s="5"/>
       <c r="PD45" s="5"/>
       <c r="PE45" s="5"/>
-      <c r="PF45" s="5"/>
+      <c r="PF45" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG45" s="5" t="s">
         <v>432</v>
       </c>
@@ -22961,7 +23045,9 @@
       <c r="PC46" s="5"/>
       <c r="PD46" s="5"/>
       <c r="PE46" s="5"/>
-      <c r="PF46" s="5"/>
+      <c r="PF46" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG46" s="5" t="s">
         <v>432</v>
       </c>
@@ -23411,7 +23497,9 @@
       <c r="PC47" s="5"/>
       <c r="PD47" s="5"/>
       <c r="PE47" s="5"/>
-      <c r="PF47" s="5"/>
+      <c r="PF47" s="5" t="n">
+        <v>118.61</v>
+      </c>
       <c r="PG47" s="5" t="n">
         <v>118.6</v>
       </c>
@@ -23861,7 +23949,9 @@
       <c r="PC48" s="5"/>
       <c r="PD48" s="5"/>
       <c r="PE48" s="5"/>
-      <c r="PF48" s="5"/>
+      <c r="PF48" s="5" t="n">
+        <v>122.81</v>
+      </c>
       <c r="PG48" s="5" t="n">
         <v>122.81</v>
       </c>
@@ -24311,7 +24401,9 @@
       <c r="PC49" s="5"/>
       <c r="PD49" s="5"/>
       <c r="PE49" s="5"/>
-      <c r="PF49" s="5"/>
+      <c r="PF49" s="5" t="n">
+        <v>8.143</v>
+      </c>
       <c r="PG49" s="5" t="n">
         <v>8.143</v>
       </c>
@@ -24761,7 +24853,9 @@
       <c r="PC50" s="5"/>
       <c r="PD50" s="5"/>
       <c r="PE50" s="5"/>
-      <c r="PF50" s="5"/>
+      <c r="PF50" s="5" t="n">
+        <v>10.92</v>
+      </c>
       <c r="PG50" s="5" t="n">
         <v>11.2</v>
       </c>
@@ -25211,7 +25305,9 @@
       <c r="PC51" s="5"/>
       <c r="PD51" s="5"/>
       <c r="PE51" s="5"/>
-      <c r="PF51" s="5"/>
+      <c r="PF51" s="5" t="n">
+        <v>7.4</v>
+      </c>
       <c r="PG51" s="5" t="n">
         <v>7.4</v>
       </c>
@@ -25661,7 +25757,9 @@
       <c r="PC52" s="5"/>
       <c r="PD52" s="5"/>
       <c r="PE52" s="5"/>
-      <c r="PF52" s="5"/>
+      <c r="PF52" s="5" t="n">
+        <v>3.52</v>
+      </c>
       <c r="PG52" s="5" t="n">
         <v>3.8</v>
       </c>
@@ -26111,7 +26209,9 @@
       <c r="PC53" s="5"/>
       <c r="PD53" s="5"/>
       <c r="PE53" s="5"/>
-      <c r="PF53" s="5"/>
+      <c r="PF53" s="5" t="n">
+        <v>86.42</v>
+      </c>
       <c r="PG53" s="5" t="n">
         <v>86.36</v>
       </c>
@@ -26561,7 +26661,9 @@
       <c r="PC54" s="5"/>
       <c r="PD54" s="5"/>
       <c r="PE54" s="5"/>
-      <c r="PF54" s="5"/>
+      <c r="PF54" s="5" t="n">
+        <v>134.99</v>
+      </c>
       <c r="PG54" s="5" t="n">
         <v>134.99</v>
       </c>
@@ -27011,7 +27113,9 @@
       <c r="PC55" s="5"/>
       <c r="PD55" s="5"/>
       <c r="PE55" s="5"/>
-      <c r="PF55" s="5"/>
+      <c r="PF55" s="5" t="n">
+        <v>185.19</v>
+      </c>
       <c r="PG55" s="5" t="n">
         <v>184.91</v>
       </c>
@@ -27461,7 +27565,9 @@
       <c r="PC56" s="5"/>
       <c r="PD56" s="5"/>
       <c r="PE56" s="5"/>
-      <c r="PF56" s="5"/>
+      <c r="PF56" s="5" t="n">
+        <v>226.45</v>
+      </c>
       <c r="PG56" s="5" t="n">
         <v>226.86</v>
       </c>
@@ -27911,7 +28017,9 @@
       <c r="PC57" s="5"/>
       <c r="PD57" s="5"/>
       <c r="PE57" s="5"/>
-      <c r="PF57" s="5"/>
+      <c r="PF57" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG57" s="5" t="s">
         <v>432</v>
       </c>
@@ -28361,7 +28469,9 @@
       <c r="PC58" s="5"/>
       <c r="PD58" s="5"/>
       <c r="PE58" s="5"/>
-      <c r="PF58" s="5"/>
+      <c r="PF58" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG58" s="5" t="s">
         <v>432</v>
       </c>
@@ -28811,7 +28921,9 @@
       <c r="PC59" s="5"/>
       <c r="PD59" s="5"/>
       <c r="PE59" s="5"/>
-      <c r="PF59" s="5"/>
+      <c r="PF59" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG59" s="5" t="s">
         <v>432</v>
       </c>
@@ -29261,7 +29373,9 @@
       <c r="PC60" s="5"/>
       <c r="PD60" s="5"/>
       <c r="PE60" s="5"/>
-      <c r="PF60" s="5"/>
+      <c r="PF60" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="PG60" s="5" t="s">
         <v>432</v>
       </c>
@@ -29711,7 +29825,9 @@
       <c r="PC61" s="5"/>
       <c r="PD61" s="5"/>
       <c r="PE61" s="5"/>
-      <c r="PF61" s="5"/>
+      <c r="PF61" s="5" t="n">
+        <v>404.8</v>
+      </c>
       <c r="PG61" s="5" t="n">
         <v>404.7</v>
       </c>

--- a/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
+++ b/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="496">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 1: Core Benchmarks</t>
   </si>
@@ -3647,7 +3647,9 @@
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
+      <c r="P4" s="5" t="n">
+        <v>22883.29</v>
+      </c>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
@@ -4099,7 +4101,9 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
+      <c r="P5" s="5" t="n">
+        <v>10640</v>
+      </c>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
@@ -4551,7 +4555,9 @@
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
+      <c r="P6" s="5" t="n">
+        <v>10283.55</v>
+      </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
@@ -5003,7 +5009,9 @@
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
+      <c r="P7" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
@@ -5455,7 +5463,9 @@
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
+      <c r="P8" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
@@ -5907,7 +5917,9 @@
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
+      <c r="P9" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
@@ -6359,7 +6371,9 @@
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
+      <c r="P10" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
       <c r="S10" s="5"/>
@@ -6811,7 +6825,9 @@
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
+      <c r="P11" s="5" t="n">
+        <v>11904.76</v>
+      </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
@@ -7263,7 +7279,9 @@
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
+      <c r="P12" s="5" t="n">
+        <v>8849.56</v>
+      </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
@@ -7715,7 +7733,9 @@
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
+      <c r="P13" s="5" t="n">
+        <v>3030.3</v>
+      </c>
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
@@ -8167,7 +8187,9 @@
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
+      <c r="P14" s="5" t="n">
+        <v>2323.73</v>
+      </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
       <c r="S14" s="5"/>
@@ -8619,7 +8641,9 @@
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
+      <c r="P15" s="5" t="n">
+        <v>717.13</v>
+      </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
@@ -9071,7 +9095,9 @@
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
+      <c r="P16" s="5" t="n">
+        <v>1848.43</v>
+      </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
@@ -9523,7 +9549,9 @@
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
+      <c r="P17" s="5" t="n">
+        <v>423.55</v>
+      </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
@@ -9975,7 +10003,9 @@
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
+      <c r="P18" s="5" t="n">
+        <v>222.43</v>
+      </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
@@ -10427,7 +10457,9 @@
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
+      <c r="P19" s="5" t="n">
+        <v>62.45</v>
+      </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
       <c r="S19" s="5"/>
@@ -10879,7 +10911,9 @@
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
+      <c r="P20" s="5" t="n">
+        <v>1027.46</v>
+      </c>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
       <c r="S20" s="5"/>
@@ -11331,7 +11365,9 @@
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
+      <c r="P21" s="5" t="n">
+        <v>1545.89</v>
+      </c>
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
@@ -11783,7 +11819,9 @@
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
+      <c r="P22" s="5" t="n">
+        <v>292.95</v>
+      </c>
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
@@ -12235,7 +12273,9 @@
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
+      <c r="P23" s="5" t="n">
+        <v>1260.58</v>
+      </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
       <c r="S23" s="5"/>
@@ -12687,7 +12727,9 @@
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
+      <c r="P24" s="5" t="n">
+        <v>30292.22</v>
+      </c>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
@@ -13139,7 +13181,9 @@
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
+      <c r="P25" s="5" t="n">
+        <v>16124.78</v>
+      </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
@@ -13591,7 +13635,9 @@
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
+      <c r="P26" s="5" t="n">
+        <v>16134.02</v>
+      </c>
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
@@ -14043,7 +14089,9 @@
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
+      <c r="P27" s="5" t="n">
+        <v>22.36</v>
+      </c>
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
@@ -14495,7 +14543,9 @@
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
+      <c r="P28" s="5" t="n">
+        <v>34.94</v>
+      </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
@@ -14947,7 +14997,9 @@
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
+      <c r="P29" s="5" t="n">
+        <v>34.93</v>
+      </c>
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
@@ -15399,7 +15451,9 @@
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
+      <c r="P30" s="5" t="n">
+        <v>44.7</v>
+      </c>
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
@@ -15851,7 +15905,9 @@
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
+      <c r="P31" s="5" t="n">
+        <v>3200</v>
+      </c>
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
@@ -16303,7 +16359,9 @@
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
+      <c r="P32" s="5" t="n">
+        <v>4571.43</v>
+      </c>
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
       <c r="S32" s="5"/>
@@ -16755,7 +16813,9 @@
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
+      <c r="P33" s="5" t="n">
+        <v>2.26</v>
+      </c>
       <c r="Q33" s="5"/>
       <c r="R33" s="5"/>
       <c r="S33" s="5"/>
@@ -17207,7 +17267,9 @@
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
+      <c r="P34" s="5" t="n">
+        <v>2.31</v>
+      </c>
       <c r="Q34" s="5"/>
       <c r="R34" s="5"/>
       <c r="S34" s="5"/>
@@ -17659,7 +17721,9 @@
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
+      <c r="P35" s="5" t="n">
+        <v>26.19</v>
+      </c>
       <c r="Q35" s="5"/>
       <c r="R35" s="5"/>
       <c r="S35" s="5"/>
@@ -18111,7 +18175,9 @@
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
+      <c r="P36" s="5" t="n">
+        <v>43574.47</v>
+      </c>
       <c r="Q36" s="5"/>
       <c r="R36" s="5"/>
       <c r="S36" s="5"/>
@@ -18563,7 +18629,9 @@
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
+      <c r="P37" s="5" t="n">
+        <v>23813.95</v>
+      </c>
       <c r="Q37" s="5"/>
       <c r="R37" s="5"/>
       <c r="S37" s="5"/>
@@ -19015,7 +19083,9 @@
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
+      <c r="P38" s="5" t="n">
+        <v>1724.14</v>
+      </c>
       <c r="Q38" s="5"/>
       <c r="R38" s="5"/>
       <c r="S38" s="5"/>
@@ -19467,7 +19537,9 @@
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
+      <c r="P39" s="5" t="n">
+        <v>15306.12</v>
+      </c>
       <c r="Q39" s="5"/>
       <c r="R39" s="5"/>
       <c r="S39" s="5"/>
@@ -19919,7 +19991,9 @@
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
+      <c r="P40" s="5" t="n">
+        <v>8.88</v>
+      </c>
       <c r="Q40" s="5"/>
       <c r="R40" s="5"/>
       <c r="S40" s="5"/>
@@ -20371,7 +20445,9 @@
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
       <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
+      <c r="P41" s="5" t="n">
+        <v>19.43</v>
+      </c>
       <c r="Q41" s="5"/>
       <c r="R41" s="5"/>
       <c r="S41" s="5"/>
@@ -20823,7 +20899,9 @@
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
+      <c r="P42" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="Q42" s="5"/>
       <c r="R42" s="5"/>
       <c r="S42" s="5"/>
@@ -21275,7 +21353,9 @@
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
       <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
+      <c r="P43" s="5" t="n">
+        <v>16384</v>
+      </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="5"/>
       <c r="S43" s="5"/>
@@ -21727,7 +21807,9 @@
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
       <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
+      <c r="P44" s="5" t="n">
+        <v>80</v>
+      </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="5"/>
       <c r="S44" s="5"/>
@@ -22179,7 +22261,9 @@
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
-      <c r="P45" s="5"/>
+      <c r="P45" s="5" t="n">
+        <v>981</v>
+      </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="5"/>
       <c r="S45" s="5"/>
@@ -22631,7 +22715,9 @@
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
+      <c r="P46" s="5" t="n">
+        <v>3072</v>
+      </c>
       <c r="Q46" s="5"/>
       <c r="R46" s="5"/>
       <c r="S46" s="5"/>
@@ -23083,7 +23169,9 @@
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
-      <c r="P47" s="5"/>
+      <c r="P47" s="5" t="n">
+        <v>2572.68</v>
+      </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="5"/>
       <c r="S47" s="5"/>
@@ -23535,7 +23623,9 @@
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
       <c r="O48" s="5"/>
-      <c r="P48" s="5"/>
+      <c r="P48" s="5" t="n">
+        <v>2899.86</v>
+      </c>
       <c r="Q48" s="5"/>
       <c r="R48" s="5"/>
       <c r="S48" s="5"/>
@@ -23987,7 +24077,9 @@
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
       <c r="O49" s="5"/>
-      <c r="P49" s="5"/>
+      <c r="P49" s="5" t="n">
+        <v>0.345</v>
+      </c>
       <c r="Q49" s="5"/>
       <c r="R49" s="5"/>
       <c r="S49" s="5"/>
@@ -24439,7 +24531,9 @@
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
       <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
+      <c r="P50" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="Q50" s="5"/>
       <c r="R50" s="5"/>
       <c r="S50" s="5"/>
@@ -24891,7 +24985,9 @@
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
       <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
+      <c r="P51" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="Q51" s="5"/>
       <c r="R51" s="5"/>
       <c r="S51" s="5"/>
@@ -25343,7 +25439,9 @@
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
       <c r="O52" s="5"/>
-      <c r="P52" s="5"/>
+      <c r="P52" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="Q52" s="5"/>
       <c r="R52" s="5"/>
       <c r="S52" s="5"/>
@@ -25795,7 +25893,9 @@
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
       <c r="O53" s="5"/>
-      <c r="P53" s="5"/>
+      <c r="P53" s="5" t="n">
+        <v>50.92</v>
+      </c>
       <c r="Q53" s="5"/>
       <c r="R53" s="5"/>
       <c r="S53" s="5"/>
@@ -26247,7 +26347,9 @@
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
       <c r="O54" s="5"/>
-      <c r="P54" s="5"/>
+      <c r="P54" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="Q54" s="5"/>
       <c r="R54" s="5"/>
       <c r="S54" s="5"/>
@@ -26699,7 +26801,9 @@
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
       <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
+      <c r="P55" s="5" t="n">
+        <v>77.63</v>
+      </c>
       <c r="Q55" s="5"/>
       <c r="R55" s="5"/>
       <c r="S55" s="5"/>
@@ -27151,7 +27255,9 @@
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
       <c r="O56" s="5"/>
-      <c r="P56" s="5"/>
+      <c r="P56" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="Q56" s="5"/>
       <c r="R56" s="5"/>
       <c r="S56" s="5"/>
@@ -27603,7 +27709,9 @@
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
       <c r="O57" s="5"/>
-      <c r="P57" s="5"/>
+      <c r="P57" s="5" t="n">
+        <v>87.3</v>
+      </c>
       <c r="Q57" s="5"/>
       <c r="R57" s="5"/>
       <c r="S57" s="5"/>
@@ -28055,7 +28163,9 @@
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
       <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
+      <c r="P58" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="Q58" s="5"/>
       <c r="R58" s="5"/>
       <c r="S58" s="5"/>
@@ -28507,7 +28617,9 @@
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
       <c r="O59" s="5"/>
-      <c r="P59" s="5"/>
+      <c r="P59" s="5" t="n">
+        <v>90.72</v>
+      </c>
       <c r="Q59" s="5"/>
       <c r="R59" s="5"/>
       <c r="S59" s="5"/>
@@ -28959,7 +29071,9 @@
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
       <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
+      <c r="P60" s="5" t="n">
+        <v>92.99</v>
+      </c>
       <c r="Q60" s="5"/>
       <c r="R60" s="5"/>
       <c r="S60" s="5"/>
@@ -29411,7 +29525,9 @@
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
       <c r="O61" s="5"/>
-      <c r="P61" s="5"/>
+      <c r="P61" s="5" t="n">
+        <v>1079.3</v>
+      </c>
       <c r="Q61" s="5"/>
       <c r="R61" s="5"/>
       <c r="S61" s="5"/>

--- a/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
+++ b/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="496">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 1: Core Benchmarks</t>
   </si>
@@ -3632,7 +3632,9 @@
       <c r="D4" s="5" t="n">
         <v>5959.48</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="5" t="n">
+        <v>5973.72</v>
+      </c>
       <c r="F4" s="5" t="n">
         <v>399.68</v>
       </c>
@@ -4086,7 +4088,9 @@
       <c r="D5" s="5" t="n">
         <v>4775.22</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="5" t="n">
+        <v>4750.5</v>
+      </c>
       <c r="F5" s="5" t="n">
         <v>137.9</v>
       </c>
@@ -4540,7 +4544,9 @@
       <c r="D6" s="5" t="n">
         <v>3223.88</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5" t="n">
+        <v>3229.67</v>
+      </c>
       <c r="F6" s="5" t="n">
         <v>25.25</v>
       </c>
@@ -4994,7 +5000,9 @@
       <c r="D7" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F7" s="5" t="s">
         <v>432</v>
       </c>
@@ -5448,7 +5456,9 @@
       <c r="D8" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F8" s="5" t="s">
         <v>432</v>
       </c>
@@ -5902,7 +5912,9 @@
       <c r="D9" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F9" s="5" t="s">
         <v>432</v>
       </c>
@@ -6356,7 +6368,9 @@
       <c r="D10" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F10" s="5" t="s">
         <v>432</v>
       </c>
@@ -6810,7 +6824,9 @@
       <c r="D11" s="5" t="n">
         <v>6493.51</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="5" t="n">
+        <v>6756.76</v>
+      </c>
       <c r="F11" s="5" t="n">
         <v>101.21</v>
       </c>
@@ -7264,7 +7280,9 @@
       <c r="D12" s="5" t="n">
         <v>5813.95</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="5" t="n">
+        <v>5882.35</v>
+      </c>
       <c r="F12" s="5" t="n">
         <v>90.65</v>
       </c>
@@ -7718,7 +7736,9 @@
       <c r="D13" s="5" t="n">
         <v>2257.34</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="5" t="n">
+        <v>2272.73</v>
+      </c>
       <c r="F13" s="5" t="n">
         <v>30.91</v>
       </c>
@@ -8172,7 +8192,9 @@
       <c r="D14" s="5" t="n">
         <v>782.93</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5" t="n">
+        <v>837.49</v>
+      </c>
       <c r="F14" s="5" t="n">
         <v>22.8</v>
       </c>
@@ -8626,7 +8648,9 @@
       <c r="D15" s="5" t="n">
         <v>179.43</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5" t="n">
+        <v>179.5</v>
+      </c>
       <c r="F15" s="5" t="n">
         <v>3.7</v>
       </c>
@@ -9080,7 +9104,9 @@
       <c r="D16" s="5" t="n">
         <v>542.3</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5" t="n">
+        <v>531.35</v>
+      </c>
       <c r="F16" s="5" t="s">
         <v>432</v>
       </c>
@@ -9534,7 +9560,9 @@
       <c r="D17" s="5" t="n">
         <v>67.21</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5" t="n">
+        <v>67.03</v>
+      </c>
       <c r="F17" s="5" t="s">
         <v>432</v>
       </c>
@@ -9988,7 +10016,9 @@
       <c r="D18" s="5" t="n">
         <v>39.31</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="5" t="n">
+        <v>39.33</v>
+      </c>
       <c r="F18" s="5" t="s">
         <v>432</v>
       </c>
@@ -10442,7 +10472,9 @@
       <c r="D19" s="5" t="n">
         <v>10.59</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="5" t="n">
+        <v>10.59</v>
+      </c>
       <c r="F19" s="5" t="s">
         <v>432</v>
       </c>
@@ -10896,7 +10928,9 @@
       <c r="D20" s="5" t="n">
         <v>328.99</v>
       </c>
-      <c r="E20" s="5"/>
+      <c r="E20" s="5" t="n">
+        <v>320.26</v>
+      </c>
       <c r="F20" s="5" t="n">
         <v>126.95</v>
       </c>
@@ -11350,7 +11384,9 @@
       <c r="D21" s="5" t="n">
         <v>295.29</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5" t="n">
+        <v>327.62</v>
+      </c>
       <c r="F21" s="5" t="n">
         <v>97.48</v>
       </c>
@@ -11804,7 +11840,9 @@
       <c r="D22" s="5" t="n">
         <v>76.38</v>
       </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="5" t="n">
+        <v>76.5</v>
+      </c>
       <c r="F22" s="5" t="n">
         <v>14.87</v>
       </c>
@@ -12258,7 +12296,9 @@
       <c r="D23" s="5" t="n">
         <v>342.75</v>
       </c>
-      <c r="E23" s="5"/>
+      <c r="E23" s="5" t="n">
+        <v>337.89</v>
+      </c>
       <c r="F23" s="5" t="n">
         <v>29.96</v>
       </c>
@@ -12712,7 +12752,9 @@
       <c r="D24" s="5" t="n">
         <v>7467.73</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="5" t="n">
+        <v>7473.71</v>
+      </c>
       <c r="F24" s="5" t="n">
         <v>1536.79</v>
       </c>
@@ -13166,7 +13208,9 @@
       <c r="D25" s="5" t="n">
         <v>5085.42</v>
       </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="5" t="n">
+        <v>5089.46</v>
+      </c>
       <c r="F25" s="5" t="n">
         <v>489.3</v>
       </c>
@@ -13620,7 +13664,9 @@
       <c r="D26" s="5" t="n">
         <v>4590.56</v>
       </c>
-      <c r="E26" s="5"/>
+      <c r="E26" s="5" t="n">
+        <v>4589.64</v>
+      </c>
       <c r="F26" s="5" t="n">
         <v>376.19</v>
       </c>
@@ -14074,7 +14120,9 @@
       <c r="D27" s="5" t="n">
         <v>6.83</v>
       </c>
-      <c r="E27" s="5"/>
+      <c r="E27" s="5" t="n">
+        <v>6.83</v>
+      </c>
       <c r="F27" s="5" t="n">
         <v>1.96</v>
       </c>
@@ -14528,7 +14576,9 @@
       <c r="D28" s="5" t="n">
         <v>6.84</v>
       </c>
-      <c r="E28" s="5"/>
+      <c r="E28" s="5" t="n">
+        <v>7.98</v>
+      </c>
       <c r="F28" s="5" t="n">
         <v>2.62</v>
       </c>
@@ -14982,7 +15032,9 @@
       <c r="D29" s="5" t="n">
         <v>27.35</v>
       </c>
-      <c r="E29" s="5"/>
+      <c r="E29" s="5" t="n">
+        <v>27.35</v>
+      </c>
       <c r="F29" s="5" t="n">
         <v>3.93</v>
       </c>
@@ -15436,7 +15488,9 @@
       <c r="D30" s="5" t="n">
         <v>21.27</v>
       </c>
-      <c r="E30" s="5"/>
+      <c r="E30" s="5" t="n">
+        <v>21.27</v>
+      </c>
       <c r="F30" s="5" t="n">
         <v>1.51</v>
       </c>
@@ -15890,7 +15944,9 @@
       <c r="D31" s="5" t="n">
         <v>1.58</v>
       </c>
-      <c r="E31" s="5"/>
+      <c r="E31" s="5" t="n">
+        <v>1.58</v>
+      </c>
       <c r="F31" s="5" t="n">
         <v>0.3</v>
       </c>
@@ -16344,7 +16400,9 @@
       <c r="D32" s="5" t="n">
         <v>37.98</v>
       </c>
-      <c r="E32" s="5"/>
+      <c r="E32" s="5" t="n">
+        <v>37.87</v>
+      </c>
       <c r="F32" s="5" t="n">
         <v>285.71</v>
       </c>
@@ -16798,7 +16856,9 @@
       <c r="D33" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E33" s="5"/>
+      <c r="E33" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F33" s="5" t="s">
         <v>432</v>
       </c>
@@ -17252,7 +17312,9 @@
       <c r="D34" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E34" s="5"/>
+      <c r="E34" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F34" s="5" t="s">
         <v>432</v>
       </c>
@@ -17706,7 +17768,9 @@
       <c r="D35" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E35" s="5"/>
+      <c r="E35" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F35" s="5" t="s">
         <v>432</v>
       </c>
@@ -18160,7 +18224,9 @@
       <c r="D36" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E36" s="5"/>
+      <c r="E36" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F36" s="5" t="s">
         <v>432</v>
       </c>
@@ -18614,7 +18680,9 @@
       <c r="D37" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E37" s="5"/>
+      <c r="E37" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F37" s="5" t="s">
         <v>432</v>
       </c>
@@ -19068,7 +19136,9 @@
       <c r="D38" s="5" t="n">
         <v>1194.03</v>
       </c>
-      <c r="E38" s="5"/>
+      <c r="E38" s="5" t="n">
+        <v>1165.5</v>
+      </c>
       <c r="F38" s="5" t="n">
         <v>217.77</v>
       </c>
@@ -19522,7 +19592,9 @@
       <c r="D39" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E39" s="5"/>
+      <c r="E39" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F39" s="5" t="n">
         <v>881.83</v>
       </c>
@@ -19976,7 +20048,9 @@
       <c r="D40" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E40" s="5"/>
+      <c r="E40" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F40" s="5" t="n">
         <v>4.05</v>
       </c>
@@ -20430,7 +20504,9 @@
       <c r="D41" s="5" t="n">
         <v>42.08</v>
       </c>
-      <c r="E41" s="5"/>
+      <c r="E41" s="5" t="n">
+        <v>41.98</v>
+      </c>
       <c r="F41" s="5" t="n">
         <v>8.32</v>
       </c>
@@ -20884,7 +20960,9 @@
       <c r="D42" s="5" t="n">
         <v>36.14</v>
       </c>
-      <c r="E42" s="5"/>
+      <c r="E42" s="5" t="n">
+        <v>36.36</v>
+      </c>
       <c r="F42" s="5" t="n">
         <v>78.22</v>
       </c>
@@ -21338,7 +21416,9 @@
       <c r="D43" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E43" s="5"/>
+      <c r="E43" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F43" s="5" t="s">
         <v>432</v>
       </c>
@@ -21792,7 +21872,9 @@
       <c r="D44" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E44" s="5"/>
+      <c r="E44" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F44" s="5" t="s">
         <v>432</v>
       </c>
@@ -22246,7 +22328,9 @@
       <c r="D45" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E45" s="5"/>
+      <c r="E45" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F45" s="5" t="s">
         <v>432</v>
       </c>
@@ -22700,7 +22784,9 @@
       <c r="D46" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E46" s="5"/>
+      <c r="E46" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F46" s="5" t="s">
         <v>432</v>
       </c>
@@ -23154,7 +23240,9 @@
       <c r="D47" s="5" t="n">
         <v>39.05</v>
       </c>
-      <c r="E47" s="5"/>
+      <c r="E47" s="5" t="n">
+        <v>39.3</v>
+      </c>
       <c r="F47" s="5" t="n">
         <v>118.61</v>
       </c>
@@ -23608,7 +23696,9 @@
       <c r="D48" s="5" t="n">
         <v>39.18</v>
       </c>
-      <c r="E48" s="5"/>
+      <c r="E48" s="5" t="n">
+        <v>39.41</v>
+      </c>
       <c r="F48" s="5" t="n">
         <v>122.81</v>
       </c>
@@ -24062,7 +24152,9 @@
       <c r="D49" s="5" t="n">
         <v>25.52</v>
       </c>
-      <c r="E49" s="5"/>
+      <c r="E49" s="5" t="n">
+        <v>25.374</v>
+      </c>
       <c r="F49" s="5" t="n">
         <v>8.143</v>
       </c>
@@ -24516,7 +24608,9 @@
       <c r="D50" s="5" t="n">
         <v>5.49</v>
       </c>
-      <c r="E50" s="5"/>
+      <c r="E50" s="5" t="n">
+        <v>5.59</v>
+      </c>
       <c r="F50" s="5" t="n">
         <v>11.32</v>
       </c>
@@ -24970,7 +25064,9 @@
       <c r="D51" s="5" t="n">
         <v>5.53</v>
       </c>
-      <c r="E51" s="5"/>
+      <c r="E51" s="5" t="n">
+        <v>5.63</v>
+      </c>
       <c r="F51" s="5" t="n">
         <v>7.4</v>
       </c>
@@ -25424,7 +25520,9 @@
       <c r="D52" s="5" t="n">
         <v>-0.04</v>
       </c>
-      <c r="E52" s="5"/>
+      <c r="E52" s="5" t="n">
+        <v>-0.04</v>
+      </c>
       <c r="F52" s="5" t="n">
         <v>3.92</v>
       </c>
@@ -25878,7 +25976,9 @@
       <c r="D53" s="5" t="n">
         <v>94.78</v>
       </c>
-      <c r="E53" s="5"/>
+      <c r="E53" s="5" t="n">
+        <v>94.79</v>
+      </c>
       <c r="F53" s="5" t="n">
         <v>86.42</v>
       </c>
@@ -26332,7 +26432,9 @@
       <c r="D54" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E54" s="5"/>
+      <c r="E54" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F54" s="5" t="n">
         <v>134.92</v>
       </c>
@@ -26786,7 +26888,9 @@
       <c r="D55" s="5" t="n">
         <v>227.27</v>
       </c>
-      <c r="E55" s="5"/>
+      <c r="E55" s="5" t="n">
+        <v>227.53</v>
+      </c>
       <c r="F55" s="5" t="n">
         <v>185.05</v>
       </c>
@@ -27240,7 +27344,9 @@
       <c r="D56" s="5" t="n">
         <v>294.55</v>
       </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="5" t="n">
+        <v>294.81</v>
+      </c>
       <c r="F56" s="5" t="n">
         <v>226.86</v>
       </c>
@@ -27694,7 +27800,9 @@
       <c r="D57" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E57" s="5"/>
+      <c r="E57" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F57" s="5" t="s">
         <v>432</v>
       </c>
@@ -28148,7 +28256,9 @@
       <c r="D58" s="5" t="n">
         <v>318.07</v>
       </c>
-      <c r="E58" s="5"/>
+      <c r="E58" s="5" t="n">
+        <v>318.27</v>
+      </c>
       <c r="F58" s="5" t="s">
         <v>432</v>
       </c>
@@ -28602,7 +28712,9 @@
       <c r="D59" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E59" s="5"/>
+      <c r="E59" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F59" s="5" t="s">
         <v>432</v>
       </c>
@@ -29056,7 +29168,9 @@
       <c r="D60" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E60" s="5"/>
+      <c r="E60" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="F60" s="5" t="s">
         <v>432</v>
       </c>
@@ -29510,7 +29624,9 @@
       <c r="D61" s="5" t="n">
         <v>448</v>
       </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="5" t="n">
+        <v>448.1</v>
+      </c>
       <c r="F61" s="5" t="n">
         <v>404.8</v>
       </c>

--- a/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
+++ b/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="496">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 1: Core Benchmarks</t>
   </si>
@@ -3655,7 +3655,9 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
+      <c r="T4" s="5" t="n">
+        <v>399.04</v>
+      </c>
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
@@ -4111,7 +4113,9 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
+      <c r="T5" s="5" t="n">
+        <v>130.89</v>
+      </c>
       <c r="U5" s="5"/>
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
@@ -4567,7 +4571,9 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
+      <c r="T6" s="5" t="n">
+        <v>25.16</v>
+      </c>
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
       <c r="W6" s="5"/>
@@ -5023,7 +5029,9 @@
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
+      <c r="T7" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
       <c r="W7" s="5"/>
@@ -5479,7 +5487,9 @@
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
+      <c r="T8" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
       <c r="W8" s="5"/>
@@ -5935,7 +5945,9 @@
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
+      <c r="T9" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U9" s="5"/>
       <c r="V9" s="5"/>
       <c r="W9" s="5"/>
@@ -6391,7 +6403,9 @@
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
       <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
+      <c r="T10" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
       <c r="W10" s="5"/>
@@ -6847,7 +6861,9 @@
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
+      <c r="T11" s="5" t="n">
+        <v>97.13</v>
+      </c>
       <c r="U11" s="5"/>
       <c r="V11" s="5"/>
       <c r="W11" s="5"/>
@@ -7303,7 +7319,9 @@
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
+      <c r="T12" s="5" t="n">
+        <v>87.66</v>
+      </c>
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
       <c r="W12" s="5"/>
@@ -7759,7 +7777,9 @@
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
+      <c r="T13" s="5" t="n">
+        <v>30.19</v>
+      </c>
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
       <c r="W13" s="5"/>
@@ -8215,7 +8235,9 @@
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
       <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
+      <c r="T14" s="5" t="n">
+        <v>22.39</v>
+      </c>
       <c r="U14" s="5"/>
       <c r="V14" s="5"/>
       <c r="W14" s="5"/>
@@ -8671,7 +8693,9 @@
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
+      <c r="T15" s="5" t="n">
+        <v>3.57</v>
+      </c>
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
       <c r="W15" s="5"/>
@@ -9127,7 +9151,9 @@
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
+      <c r="T16" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U16" s="5"/>
       <c r="V16" s="5"/>
       <c r="W16" s="5"/>
@@ -9583,7 +9609,9 @@
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
+      <c r="T17" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U17" s="5"/>
       <c r="V17" s="5"/>
       <c r="W17" s="5"/>
@@ -10039,7 +10067,9 @@
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
+      <c r="T18" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U18" s="5"/>
       <c r="V18" s="5"/>
       <c r="W18" s="5"/>
@@ -10495,7 +10525,9 @@
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
       <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
+      <c r="T19" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
       <c r="W19" s="5"/>
@@ -10951,7 +10983,9 @@
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
       <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
+      <c r="T20" s="5" t="n">
+        <v>123.23</v>
+      </c>
       <c r="U20" s="5"/>
       <c r="V20" s="5"/>
       <c r="W20" s="5"/>
@@ -11407,7 +11441,9 @@
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
+      <c r="T21" s="5" t="n">
+        <v>101.2</v>
+      </c>
       <c r="U21" s="5"/>
       <c r="V21" s="5"/>
       <c r="W21" s="5"/>
@@ -11863,7 +11899,9 @@
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
+      <c r="T22" s="5" t="n">
+        <v>15.23</v>
+      </c>
       <c r="U22" s="5"/>
       <c r="V22" s="5"/>
       <c r="W22" s="5"/>
@@ -12319,7 +12357,9 @@
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
       <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
+      <c r="T23" s="5" t="n">
+        <v>29.84</v>
+      </c>
       <c r="U23" s="5"/>
       <c r="V23" s="5"/>
       <c r="W23" s="5"/>
@@ -12775,7 +12815,9 @@
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
+      <c r="T24" s="5" t="n">
+        <v>1520.19</v>
+      </c>
       <c r="U24" s="5"/>
       <c r="V24" s="5"/>
       <c r="W24" s="5"/>
@@ -13231,7 +13273,9 @@
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
+      <c r="T25" s="5" t="n">
+        <v>488.55</v>
+      </c>
       <c r="U25" s="5"/>
       <c r="V25" s="5"/>
       <c r="W25" s="5"/>
@@ -13687,7 +13731,9 @@
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
+      <c r="T26" s="5" t="n">
+        <v>376.19</v>
+      </c>
       <c r="U26" s="5"/>
       <c r="V26" s="5"/>
       <c r="W26" s="5"/>
@@ -14143,7 +14189,9 @@
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
+      <c r="T27" s="5" t="n">
+        <v>1.98</v>
+      </c>
       <c r="U27" s="5"/>
       <c r="V27" s="5"/>
       <c r="W27" s="5"/>
@@ -14599,7 +14647,9 @@
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
+      <c r="T28" s="5" t="n">
+        <v>2.64</v>
+      </c>
       <c r="U28" s="5"/>
       <c r="V28" s="5"/>
       <c r="W28" s="5"/>
@@ -15055,7 +15105,9 @@
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
+      <c r="T29" s="5" t="n">
+        <v>3.97</v>
+      </c>
       <c r="U29" s="5"/>
       <c r="V29" s="5"/>
       <c r="W29" s="5"/>
@@ -15511,7 +15563,9 @@
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
+      <c r="T30" s="5" t="n">
+        <v>1.51</v>
+      </c>
       <c r="U30" s="5"/>
       <c r="V30" s="5"/>
       <c r="W30" s="5"/>
@@ -15967,7 +16021,9 @@
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
+      <c r="T31" s="5" t="n">
+        <v>0.3</v>
+      </c>
       <c r="U31" s="5"/>
       <c r="V31" s="5"/>
       <c r="W31" s="5"/>
@@ -16423,7 +16479,9 @@
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
       <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
+      <c r="T32" s="5" t="n">
+        <v>271.19</v>
+      </c>
       <c r="U32" s="5"/>
       <c r="V32" s="5"/>
       <c r="W32" s="5"/>
@@ -16879,7 +16937,9 @@
       <c r="Q33" s="5"/>
       <c r="R33" s="5"/>
       <c r="S33" s="5"/>
-      <c r="T33" s="5"/>
+      <c r="T33" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U33" s="5"/>
       <c r="V33" s="5"/>
       <c r="W33" s="5"/>
@@ -17335,7 +17395,9 @@
       <c r="Q34" s="5"/>
       <c r="R34" s="5"/>
       <c r="S34" s="5"/>
-      <c r="T34" s="5"/>
+      <c r="T34" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U34" s="5"/>
       <c r="V34" s="5"/>
       <c r="W34" s="5"/>
@@ -17791,7 +17853,9 @@
       <c r="Q35" s="5"/>
       <c r="R35" s="5"/>
       <c r="S35" s="5"/>
-      <c r="T35" s="5"/>
+      <c r="T35" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U35" s="5"/>
       <c r="V35" s="5"/>
       <c r="W35" s="5"/>
@@ -18247,7 +18311,9 @@
       <c r="Q36" s="5"/>
       <c r="R36" s="5"/>
       <c r="S36" s="5"/>
-      <c r="T36" s="5"/>
+      <c r="T36" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U36" s="5"/>
       <c r="V36" s="5"/>
       <c r="W36" s="5"/>
@@ -18703,7 +18769,9 @@
       <c r="Q37" s="5"/>
       <c r="R37" s="5"/>
       <c r="S37" s="5"/>
-      <c r="T37" s="5"/>
+      <c r="T37" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U37" s="5"/>
       <c r="V37" s="5"/>
       <c r="W37" s="5"/>
@@ -19159,7 +19227,9 @@
       <c r="Q38" s="5"/>
       <c r="R38" s="5"/>
       <c r="S38" s="5"/>
-      <c r="T38" s="5"/>
+      <c r="T38" s="5" t="n">
+        <v>148.59</v>
+      </c>
       <c r="U38" s="5"/>
       <c r="V38" s="5"/>
       <c r="W38" s="5"/>
@@ -19615,7 +19685,9 @@
       <c r="Q39" s="5"/>
       <c r="R39" s="5"/>
       <c r="S39" s="5"/>
-      <c r="T39" s="5"/>
+      <c r="T39" s="5" t="n">
+        <v>1132.93</v>
+      </c>
       <c r="U39" s="5"/>
       <c r="V39" s="5"/>
       <c r="W39" s="5"/>
@@ -20071,7 +20143,9 @@
       <c r="Q40" s="5"/>
       <c r="R40" s="5"/>
       <c r="S40" s="5"/>
-      <c r="T40" s="5"/>
+      <c r="T40" s="5" t="n">
+        <v>7.62</v>
+      </c>
       <c r="U40" s="5"/>
       <c r="V40" s="5"/>
       <c r="W40" s="5"/>
@@ -20527,7 +20601,9 @@
       <c r="Q41" s="5"/>
       <c r="R41" s="5"/>
       <c r="S41" s="5"/>
-      <c r="T41" s="5"/>
+      <c r="T41" s="5" t="n">
+        <v>8.32</v>
+      </c>
       <c r="U41" s="5"/>
       <c r="V41" s="5"/>
       <c r="W41" s="5"/>
@@ -20983,7 +21059,9 @@
       <c r="Q42" s="5"/>
       <c r="R42" s="5"/>
       <c r="S42" s="5"/>
-      <c r="T42" s="5"/>
+      <c r="T42" s="5" t="n">
+        <v>69.09</v>
+      </c>
       <c r="U42" s="5"/>
       <c r="V42" s="5"/>
       <c r="W42" s="5"/>
@@ -21439,7 +21517,9 @@
       <c r="Q43" s="5"/>
       <c r="R43" s="5"/>
       <c r="S43" s="5"/>
-      <c r="T43" s="5"/>
+      <c r="T43" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U43" s="5"/>
       <c r="V43" s="5"/>
       <c r="W43" s="5"/>
@@ -21895,7 +21975,9 @@
       <c r="Q44" s="5"/>
       <c r="R44" s="5"/>
       <c r="S44" s="5"/>
-      <c r="T44" s="5"/>
+      <c r="T44" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U44" s="5"/>
       <c r="V44" s="5"/>
       <c r="W44" s="5"/>
@@ -22351,7 +22433,9 @@
       <c r="Q45" s="5"/>
       <c r="R45" s="5"/>
       <c r="S45" s="5"/>
-      <c r="T45" s="5"/>
+      <c r="T45" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U45" s="5"/>
       <c r="V45" s="5"/>
       <c r="W45" s="5"/>
@@ -22807,7 +22891,9 @@
       <c r="Q46" s="5"/>
       <c r="R46" s="5"/>
       <c r="S46" s="5"/>
-      <c r="T46" s="5"/>
+      <c r="T46" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U46" s="5"/>
       <c r="V46" s="5"/>
       <c r="W46" s="5"/>
@@ -23263,7 +23349,9 @@
       <c r="Q47" s="5"/>
       <c r="R47" s="5"/>
       <c r="S47" s="5"/>
-      <c r="T47" s="5"/>
+      <c r="T47" s="5" t="n">
+        <v>100.51</v>
+      </c>
       <c r="U47" s="5"/>
       <c r="V47" s="5"/>
       <c r="W47" s="5"/>
@@ -23719,7 +23807,9 @@
       <c r="Q48" s="5"/>
       <c r="R48" s="5"/>
       <c r="S48" s="5"/>
-      <c r="T48" s="5"/>
+      <c r="T48" s="5" t="n">
+        <v>103.55</v>
+      </c>
       <c r="U48" s="5"/>
       <c r="V48" s="5"/>
       <c r="W48" s="5"/>
@@ -24175,7 +24265,9 @@
       <c r="Q49" s="5"/>
       <c r="R49" s="5"/>
       <c r="S49" s="5"/>
-      <c r="T49" s="5"/>
+      <c r="T49" s="5" t="n">
+        <v>9.657</v>
+      </c>
       <c r="U49" s="5"/>
       <c r="V49" s="5"/>
       <c r="W49" s="5"/>
@@ -24631,7 +24723,9 @@
       <c r="Q50" s="5"/>
       <c r="R50" s="5"/>
       <c r="S50" s="5"/>
-      <c r="T50" s="5"/>
+      <c r="T50" s="5" t="n">
+        <v>13.12</v>
+      </c>
       <c r="U50" s="5"/>
       <c r="V50" s="5"/>
       <c r="W50" s="5"/>
@@ -25087,7 +25181,9 @@
       <c r="Q51" s="5"/>
       <c r="R51" s="5"/>
       <c r="S51" s="5"/>
-      <c r="T51" s="5"/>
+      <c r="T51" s="5" t="n">
+        <v>7.84</v>
+      </c>
       <c r="U51" s="5"/>
       <c r="V51" s="5"/>
       <c r="W51" s="5"/>
@@ -25543,7 +25639,9 @@
       <c r="Q52" s="5"/>
       <c r="R52" s="5"/>
       <c r="S52" s="5"/>
-      <c r="T52" s="5"/>
+      <c r="T52" s="5" t="n">
+        <v>5.28</v>
+      </c>
       <c r="U52" s="5"/>
       <c r="V52" s="5"/>
       <c r="W52" s="5"/>
@@ -25999,7 +26097,9 @@
       <c r="Q53" s="5"/>
       <c r="R53" s="5"/>
       <c r="S53" s="5"/>
-      <c r="T53" s="5"/>
+      <c r="T53" s="5" t="n">
+        <v>85.82</v>
+      </c>
       <c r="U53" s="5"/>
       <c r="V53" s="5"/>
       <c r="W53" s="5"/>
@@ -26455,7 +26555,9 @@
       <c r="Q54" s="5"/>
       <c r="R54" s="5"/>
       <c r="S54" s="5"/>
-      <c r="T54" s="5"/>
+      <c r="T54" s="5" t="n">
+        <v>133.62</v>
+      </c>
       <c r="U54" s="5"/>
       <c r="V54" s="5"/>
       <c r="W54" s="5"/>
@@ -26911,7 +27013,9 @@
       <c r="Q55" s="5"/>
       <c r="R55" s="5"/>
       <c r="S55" s="5"/>
-      <c r="T55" s="5"/>
+      <c r="T55" s="5" t="n">
+        <v>180.9</v>
+      </c>
       <c r="U55" s="5"/>
       <c r="V55" s="5"/>
       <c r="W55" s="5"/>
@@ -27367,7 +27471,9 @@
       <c r="Q56" s="5"/>
       <c r="R56" s="5"/>
       <c r="S56" s="5"/>
-      <c r="T56" s="5"/>
+      <c r="T56" s="5" t="n">
+        <v>219.11</v>
+      </c>
       <c r="U56" s="5"/>
       <c r="V56" s="5"/>
       <c r="W56" s="5"/>
@@ -27823,7 +27929,9 @@
       <c r="Q57" s="5"/>
       <c r="R57" s="5"/>
       <c r="S57" s="5"/>
-      <c r="T57" s="5"/>
+      <c r="T57" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U57" s="5"/>
       <c r="V57" s="5"/>
       <c r="W57" s="5"/>
@@ -28279,7 +28387,9 @@
       <c r="Q58" s="5"/>
       <c r="R58" s="5"/>
       <c r="S58" s="5"/>
-      <c r="T58" s="5"/>
+      <c r="T58" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U58" s="5"/>
       <c r="V58" s="5"/>
       <c r="W58" s="5"/>
@@ -28735,7 +28845,9 @@
       <c r="Q59" s="5"/>
       <c r="R59" s="5"/>
       <c r="S59" s="5"/>
-      <c r="T59" s="5"/>
+      <c r="T59" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U59" s="5"/>
       <c r="V59" s="5"/>
       <c r="W59" s="5"/>
@@ -29191,7 +29303,9 @@
       <c r="Q60" s="5"/>
       <c r="R60" s="5"/>
       <c r="S60" s="5"/>
-      <c r="T60" s="5"/>
+      <c r="T60" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="U60" s="5"/>
       <c r="V60" s="5"/>
       <c r="W60" s="5"/>
@@ -29647,7 +29761,9 @@
       <c r="Q61" s="5"/>
       <c r="R61" s="5"/>
       <c r="S61" s="5"/>
-      <c r="T61" s="5"/>
+      <c r="T61" s="5" t="n">
+        <v>404.3</v>
+      </c>
       <c r="U61" s="5"/>
       <c r="V61" s="5"/>
       <c r="W61" s="5"/>

--- a/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
+++ b/Part1_CoreBenchmarks_Results_v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="496">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 1: Core Benchmarks</t>
   </si>
@@ -3680,7 +3680,9 @@
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
       <c r="AN4" s="5"/>
-      <c r="AO4" s="5"/>
+      <c r="AO4" s="5" t="n">
+        <v>3984.06</v>
+      </c>
       <c r="AP4" s="5"/>
       <c r="AQ4" s="5"/>
       <c r="AR4" s="5"/>
@@ -4138,7 +4140,9 @@
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
       <c r="AN5" s="5"/>
-      <c r="AO5" s="5"/>
+      <c r="AO5" s="5" t="n">
+        <v>2399.04</v>
+      </c>
       <c r="AP5" s="5"/>
       <c r="AQ5" s="5"/>
       <c r="AR5" s="5"/>
@@ -4596,7 +4600,9 @@
       <c r="AL6" s="5"/>
       <c r="AM6" s="5"/>
       <c r="AN6" s="5"/>
-      <c r="AO6" s="5"/>
+      <c r="AO6" s="5" t="n">
+        <v>379.32</v>
+      </c>
       <c r="AP6" s="5"/>
       <c r="AQ6" s="5"/>
       <c r="AR6" s="5"/>
@@ -5054,7 +5060,9 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
       <c r="AN7" s="5"/>
-      <c r="AO7" s="5"/>
+      <c r="AO7" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP7" s="5"/>
       <c r="AQ7" s="5"/>
       <c r="AR7" s="5"/>
@@ -5512,7 +5520,9 @@
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
       <c r="AN8" s="5"/>
-      <c r="AO8" s="5"/>
+      <c r="AO8" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP8" s="5"/>
       <c r="AQ8" s="5"/>
       <c r="AR8" s="5"/>
@@ -5970,7 +5980,9 @@
       <c r="AL9" s="5"/>
       <c r="AM9" s="5"/>
       <c r="AN9" s="5"/>
-      <c r="AO9" s="5"/>
+      <c r="AO9" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP9" s="5"/>
       <c r="AQ9" s="5"/>
       <c r="AR9" s="5"/>
@@ -6428,7 +6440,9 @@
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
       <c r="AN10" s="5"/>
-      <c r="AO10" s="5"/>
+      <c r="AO10" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP10" s="5"/>
       <c r="AQ10" s="5"/>
       <c r="AR10" s="5"/>
@@ -6886,7 +6900,9 @@
       <c r="AL11" s="5"/>
       <c r="AM11" s="5"/>
       <c r="AN11" s="5"/>
-      <c r="AO11" s="5"/>
+      <c r="AO11" s="5" t="n">
+        <v>2890.17</v>
+      </c>
       <c r="AP11" s="5"/>
       <c r="AQ11" s="5"/>
       <c r="AR11" s="5"/>
@@ -7344,7 +7360,9 @@
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
       <c r="AN12" s="5"/>
-      <c r="AO12" s="5"/>
+      <c r="AO12" s="5" t="n">
+        <v>3460.21</v>
+      </c>
       <c r="AP12" s="5"/>
       <c r="AQ12" s="5"/>
       <c r="AR12" s="5"/>
@@ -7802,7 +7820,9 @@
       <c r="AL13" s="5"/>
       <c r="AM13" s="5"/>
       <c r="AN13" s="5"/>
-      <c r="AO13" s="5"/>
+      <c r="AO13" s="5" t="n">
+        <v>3533.57</v>
+      </c>
       <c r="AP13" s="5"/>
       <c r="AQ13" s="5"/>
       <c r="AR13" s="5"/>
@@ -8260,7 +8280,9 @@
       <c r="AL14" s="5"/>
       <c r="AM14" s="5"/>
       <c r="AN14" s="5"/>
-      <c r="AO14" s="5"/>
+      <c r="AO14" s="5" t="n">
+        <v>5.83</v>
+      </c>
       <c r="AP14" s="5"/>
       <c r="AQ14" s="5"/>
       <c r="AR14" s="5"/>
@@ -8718,7 +8740,9 @@
       <c r="AL15" s="5"/>
       <c r="AM15" s="5"/>
       <c r="AN15" s="5"/>
-      <c r="AO15" s="5"/>
+      <c r="AO15" s="5" t="n">
+        <v>24.73</v>
+      </c>
       <c r="AP15" s="5"/>
       <c r="AQ15" s="5"/>
       <c r="AR15" s="5"/>
@@ -9176,7 +9200,9 @@
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
       <c r="AN16" s="5"/>
-      <c r="AO16" s="5"/>
+      <c r="AO16" s="5" t="n">
+        <v>1373.63</v>
+      </c>
       <c r="AP16" s="5"/>
       <c r="AQ16" s="5"/>
       <c r="AR16" s="5"/>
@@ -9634,7 +9660,9 @@
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
       <c r="AN17" s="5"/>
-      <c r="AO17" s="5"/>
+      <c r="AO17" s="5" t="n">
+        <v>388.2</v>
+      </c>
       <c r="AP17" s="5"/>
       <c r="AQ17" s="5"/>
       <c r="AR17" s="5"/>
@@ -10092,7 +10120,9 @@
       <c r="AL18" s="5"/>
       <c r="AM18" s="5"/>
       <c r="AN18" s="5"/>
-      <c r="AO18" s="5"/>
+      <c r="AO18" s="5" t="n">
+        <v>5.87</v>
+      </c>
       <c r="AP18" s="5"/>
       <c r="AQ18" s="5"/>
       <c r="AR18" s="5"/>
@@ -10550,7 +10580,9 @@
       <c r="AL19" s="5"/>
       <c r="AM19" s="5"/>
       <c r="AN19" s="5"/>
-      <c r="AO19" s="5"/>
+      <c r="AO19" s="5" t="n">
+        <v>24.09</v>
+      </c>
       <c r="AP19" s="5"/>
       <c r="AQ19" s="5"/>
       <c r="AR19" s="5"/>
@@ -11008,7 +11040,9 @@
       <c r="AL20" s="5"/>
       <c r="AM20" s="5"/>
       <c r="AN20" s="5"/>
-      <c r="AO20" s="5"/>
+      <c r="AO20" s="5" t="n">
+        <v>151.23</v>
+      </c>
       <c r="AP20" s="5"/>
       <c r="AQ20" s="5"/>
       <c r="AR20" s="5"/>
@@ -11466,7 +11500,9 @@
       <c r="AL21" s="5"/>
       <c r="AM21" s="5"/>
       <c r="AN21" s="5"/>
-      <c r="AO21" s="5"/>
+      <c r="AO21" s="5" t="n">
+        <v>134.28</v>
+      </c>
       <c r="AP21" s="5"/>
       <c r="AQ21" s="5"/>
       <c r="AR21" s="5"/>
@@ -11924,7 +11960,9 @@
       <c r="AL22" s="5"/>
       <c r="AM22" s="5"/>
       <c r="AN22" s="5"/>
-      <c r="AO22" s="5"/>
+      <c r="AO22" s="5" t="n">
+        <v>25.09</v>
+      </c>
       <c r="AP22" s="5"/>
       <c r="AQ22" s="5"/>
       <c r="AR22" s="5"/>
@@ -12382,7 +12420,9 @@
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
       <c r="AN23" s="5"/>
-      <c r="AO23" s="5"/>
+      <c r="AO23" s="5" t="n">
+        <v>102.93</v>
+      </c>
       <c r="AP23" s="5"/>
       <c r="AQ23" s="5"/>
       <c r="AR23" s="5"/>
@@ -12840,7 +12880,9 @@
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
       <c r="AN24" s="5"/>
-      <c r="AO24" s="5"/>
+      <c r="AO24" s="5" t="n">
+        <v>3506.15</v>
+      </c>
       <c r="AP24" s="5"/>
       <c r="AQ24" s="5"/>
       <c r="AR24" s="5"/>
@@ -13298,7 +13340,9 @@
       <c r="AL25" s="5"/>
       <c r="AM25" s="5"/>
       <c r="AN25" s="5"/>
-      <c r="AO25" s="5"/>
+      <c r="AO25" s="5" t="n">
+        <v>2111.55</v>
+      </c>
       <c r="AP25" s="5"/>
       <c r="AQ25" s="5"/>
       <c r="AR25" s="5"/>
@@ -13756,7 +13800,9 @@
       <c r="AL26" s="5"/>
       <c r="AM26" s="5"/>
       <c r="AN26" s="5"/>
-      <c r="AO26" s="5"/>
+      <c r="AO26" s="5" t="n">
+        <v>1513.9</v>
+      </c>
       <c r="AP26" s="5"/>
       <c r="AQ26" s="5"/>
       <c r="AR26" s="5"/>
@@ -14214,7 +14260,9 @@
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
       <c r="AN27" s="5"/>
-      <c r="AO27" s="5"/>
+      <c r="AO27" s="5" t="n">
+        <v>27.49</v>
+      </c>
       <c r="AP27" s="5"/>
       <c r="AQ27" s="5"/>
       <c r="AR27" s="5"/>
@@ -14672,7 +14720,9 @@
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
       <c r="AN28" s="5"/>
-      <c r="AO28" s="5"/>
+      <c r="AO28" s="5" t="n">
+        <v>115.25</v>
+      </c>
       <c r="AP28" s="5"/>
       <c r="AQ28" s="5"/>
       <c r="AR28" s="5"/>
@@ -15130,7 +15180,9 @@
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
       <c r="AN29" s="5"/>
-      <c r="AO29" s="5"/>
+      <c r="AO29" s="5" t="n">
+        <v>31.9</v>
+      </c>
       <c r="AP29" s="5"/>
       <c r="AQ29" s="5"/>
       <c r="AR29" s="5"/>
@@ -15588,7 +15640,9 @@
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
       <c r="AN30" s="5"/>
-      <c r="AO30" s="5"/>
+      <c r="AO30" s="5" t="n">
+        <v>9.12</v>
+      </c>
       <c r="AP30" s="5"/>
       <c r="AQ30" s="5"/>
       <c r="AR30" s="5"/>
@@ -16046,7 +16100,9 @@
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
       <c r="AN31" s="5"/>
-      <c r="AO31" s="5"/>
+      <c r="AO31" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP31" s="5"/>
       <c r="AQ31" s="5"/>
       <c r="AR31" s="5"/>
@@ -16504,7 +16560,9 @@
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
       <c r="AN32" s="5"/>
-      <c r="AO32" s="5"/>
+      <c r="AO32" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP32" s="5"/>
       <c r="AQ32" s="5"/>
       <c r="AR32" s="5"/>
@@ -16962,7 +17020,9 @@
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
       <c r="AN33" s="5"/>
-      <c r="AO33" s="5"/>
+      <c r="AO33" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP33" s="5"/>
       <c r="AQ33" s="5"/>
       <c r="AR33" s="5"/>
@@ -17420,7 +17480,9 @@
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
       <c r="AN34" s="5"/>
-      <c r="AO34" s="5"/>
+      <c r="AO34" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP34" s="5"/>
       <c r="AQ34" s="5"/>
       <c r="AR34" s="5"/>
@@ -17878,7 +17940,9 @@
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
       <c r="AN35" s="5"/>
-      <c r="AO35" s="5"/>
+      <c r="AO35" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP35" s="5"/>
       <c r="AQ35" s="5"/>
       <c r="AR35" s="5"/>
@@ -18336,7 +18400,9 @@
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
       <c r="AN36" s="5"/>
-      <c r="AO36" s="5"/>
+      <c r="AO36" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP36" s="5"/>
       <c r="AQ36" s="5"/>
       <c r="AR36" s="5"/>
@@ -18794,7 +18860,9 @@
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
       <c r="AN37" s="5"/>
-      <c r="AO37" s="5"/>
+      <c r="AO37" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP37" s="5"/>
       <c r="AQ37" s="5"/>
       <c r="AR37" s="5"/>
@@ -19252,7 +19320,9 @@
       <c r="AL38" s="5"/>
       <c r="AM38" s="5"/>
       <c r="AN38" s="5"/>
-      <c r="AO38" s="5"/>
+      <c r="AO38" s="5" t="n">
+        <v>453.72</v>
+      </c>
       <c r="AP38" s="5"/>
       <c r="AQ38" s="5"/>
       <c r="AR38" s="5"/>
@@ -19710,7 +19780,9 @@
       <c r="AL39" s="5"/>
       <c r="AM39" s="5"/>
       <c r="AN39" s="5"/>
-      <c r="AO39" s="5"/>
+      <c r="AO39" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP39" s="5"/>
       <c r="AQ39" s="5"/>
       <c r="AR39" s="5"/>
@@ -20168,7 +20240,9 @@
       <c r="AL40" s="5"/>
       <c r="AM40" s="5"/>
       <c r="AN40" s="5"/>
-      <c r="AO40" s="5"/>
+      <c r="AO40" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP40" s="5"/>
       <c r="AQ40" s="5"/>
       <c r="AR40" s="5"/>
@@ -20626,7 +20700,9 @@
       <c r="AL41" s="5"/>
       <c r="AM41" s="5"/>
       <c r="AN41" s="5"/>
-      <c r="AO41" s="5"/>
+      <c r="AO41" s="5" t="n">
+        <v>35.71</v>
+      </c>
       <c r="AP41" s="5"/>
       <c r="AQ41" s="5"/>
       <c r="AR41" s="5"/>
@@ -21084,7 +21160,9 @@
       <c r="AL42" s="5"/>
       <c r="AM42" s="5"/>
       <c r="AN42" s="5"/>
-      <c r="AO42" s="5"/>
+      <c r="AO42" s="5" t="n">
+        <v>230.31</v>
+      </c>
       <c r="AP42" s="5"/>
       <c r="AQ42" s="5"/>
       <c r="AR42" s="5"/>
@@ -21542,7 +21620,9 @@
       <c r="AL43" s="5"/>
       <c r="AM43" s="5"/>
       <c r="AN43" s="5"/>
-      <c r="AO43" s="5"/>
+      <c r="AO43" s="5" t="n">
+        <v>384</v>
+      </c>
       <c r="AP43" s="5"/>
       <c r="AQ43" s="5"/>
       <c r="AR43" s="5"/>
@@ -22000,7 +22080,9 @@
       <c r="AL44" s="5"/>
       <c r="AM44" s="5"/>
       <c r="AN44" s="5"/>
-      <c r="AO44" s="5"/>
+      <c r="AO44" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP44" s="5"/>
       <c r="AQ44" s="5"/>
       <c r="AR44" s="5"/>
@@ -22458,7 +22540,9 @@
       <c r="AL45" s="5"/>
       <c r="AM45" s="5"/>
       <c r="AN45" s="5"/>
-      <c r="AO45" s="5"/>
+      <c r="AO45" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP45" s="5"/>
       <c r="AQ45" s="5"/>
       <c r="AR45" s="5"/>
@@ -22916,7 +23000,9 @@
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
       <c r="AN46" s="5"/>
-      <c r="AO46" s="5"/>
+      <c r="AO46" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP46" s="5"/>
       <c r="AQ46" s="5"/>
       <c r="AR46" s="5"/>
@@ -23374,7 +23460,9 @@
       <c r="AL47" s="5"/>
       <c r="AM47" s="5"/>
       <c r="AN47" s="5"/>
-      <c r="AO47" s="5"/>
+      <c r="AO47" s="5" t="n">
+        <v>262.81</v>
+      </c>
       <c r="AP47" s="5"/>
       <c r="AQ47" s="5"/>
       <c r="AR47" s="5"/>
@@ -23832,7 +23920,9 @@
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
       <c r="AN48" s="5"/>
-      <c r="AO48" s="5"/>
+      <c r="AO48" s="5" t="n">
+        <v>278.94</v>
+      </c>
       <c r="AP48" s="5"/>
       <c r="AQ48" s="5"/>
       <c r="AR48" s="5"/>
@@ -24290,7 +24380,9 @@
       <c r="AL49" s="5"/>
       <c r="AM49" s="5"/>
       <c r="AN49" s="5"/>
-      <c r="AO49" s="5"/>
+      <c r="AO49" s="5" t="n">
+        <v>3.585</v>
+      </c>
       <c r="AP49" s="5"/>
       <c r="AQ49" s="5"/>
       <c r="AR49" s="5"/>
@@ -24748,7 +24840,9 @@
       <c r="AL50" s="5"/>
       <c r="AM50" s="5"/>
       <c r="AN50" s="5"/>
-      <c r="AO50" s="5"/>
+      <c r="AO50" s="5" t="n">
+        <v>11.78</v>
+      </c>
       <c r="AP50" s="5"/>
       <c r="AQ50" s="5"/>
       <c r="AR50" s="5"/>
@@ -25206,7 +25300,9 @@
       <c r="AL51" s="5"/>
       <c r="AM51" s="5"/>
       <c r="AN51" s="5"/>
-      <c r="AO51" s="5"/>
+      <c r="AO51" s="5" t="n">
+        <v>11.76</v>
+      </c>
       <c r="AP51" s="5"/>
       <c r="AQ51" s="5"/>
       <c r="AR51" s="5"/>
@@ -25664,7 +25760,9 @@
       <c r="AL52" s="5"/>
       <c r="AM52" s="5"/>
       <c r="AN52" s="5"/>
-      <c r="AO52" s="5"/>
+      <c r="AO52" s="5" t="n">
+        <v>0.02</v>
+      </c>
       <c r="AP52" s="5"/>
       <c r="AQ52" s="5"/>
       <c r="AR52" s="5"/>
@@ -26122,7 +26220,9 @@
       <c r="AL53" s="5"/>
       <c r="AM53" s="5"/>
       <c r="AN53" s="5"/>
-      <c r="AO53" s="5"/>
+      <c r="AO53" s="5" t="n">
+        <v>68.48</v>
+      </c>
       <c r="AP53" s="5"/>
       <c r="AQ53" s="5"/>
       <c r="AR53" s="5"/>
@@ -26580,7 +26680,9 @@
       <c r="AL54" s="5"/>
       <c r="AM54" s="5"/>
       <c r="AN54" s="5"/>
-      <c r="AO54" s="5"/>
+      <c r="AO54" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP54" s="5"/>
       <c r="AQ54" s="5"/>
       <c r="AR54" s="5"/>
@@ -27038,7 +27140,9 @@
       <c r="AL55" s="5"/>
       <c r="AM55" s="5"/>
       <c r="AN55" s="5"/>
-      <c r="AO55" s="5"/>
+      <c r="AO55" s="5" t="n">
+        <v>130.14</v>
+      </c>
       <c r="AP55" s="5"/>
       <c r="AQ55" s="5"/>
       <c r="AR55" s="5"/>
@@ -27496,7 +27600,9 @@
       <c r="AL56" s="5"/>
       <c r="AM56" s="5"/>
       <c r="AN56" s="5"/>
-      <c r="AO56" s="5"/>
+      <c r="AO56" s="5" t="n">
+        <v>164.23</v>
+      </c>
       <c r="AP56" s="5"/>
       <c r="AQ56" s="5"/>
       <c r="AR56" s="5"/>
@@ -27954,7 +28060,9 @@
       <c r="AL57" s="5"/>
       <c r="AM57" s="5"/>
       <c r="AN57" s="5"/>
-      <c r="AO57" s="5"/>
+      <c r="AO57" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP57" s="5"/>
       <c r="AQ57" s="5"/>
       <c r="AR57" s="5"/>
@@ -28412,7 +28520,9 @@
       <c r="AL58" s="5"/>
       <c r="AM58" s="5"/>
       <c r="AN58" s="5"/>
-      <c r="AO58" s="5"/>
+      <c r="AO58" s="5" t="n">
+        <v>174.25</v>
+      </c>
       <c r="AP58" s="5"/>
       <c r="AQ58" s="5"/>
       <c r="AR58" s="5"/>
@@ -28870,7 +28980,9 @@
       <c r="AL59" s="5"/>
       <c r="AM59" s="5"/>
       <c r="AN59" s="5"/>
-      <c r="AO59" s="5"/>
+      <c r="AO59" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP59" s="5"/>
       <c r="AQ59" s="5"/>
       <c r="AR59" s="5"/>
@@ -29328,7 +29440,9 @@
       <c r="AL60" s="5"/>
       <c r="AM60" s="5"/>
       <c r="AN60" s="5"/>
-      <c r="AO60" s="5"/>
+      <c r="AO60" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="AP60" s="5"/>
       <c r="AQ60" s="5"/>
       <c r="AR60" s="5"/>
@@ -29786,7 +29900,9 @@
       <c r="AL61" s="5"/>
       <c r="AM61" s="5"/>
       <c r="AN61" s="5"/>
-      <c r="AO61" s="5"/>
+      <c r="AO61" s="5" t="n">
+        <v>354</v>
+      </c>
       <c r="AP61" s="5"/>
       <c r="AQ61" s="5"/>
       <c r="AR61" s="5"/>
